--- a/lessonmap.xlsx
+++ b/lessonmap.xlsx
@@ -10344,7 +10344,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="M123" s="15" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10354,12 +10354,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O123" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="P123" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_01_index_laws_product_quotient_power_v2.html</t>
         </is>
@@ -10437,17 +10437,17 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="O124" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="P124" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_02_zero_and_negative_indices_v2.html</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="Q124" s="15" t="inlineStr">
         <is>
           <t>Built 2026-05-31 (remote batch y9-alg-01). Covers planned-01 negative_integer_exponents content.</t>
         </is>
@@ -10510,7 +10510,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M125" s="15" t="inlineStr">
         <is>
           <t>y9_alg_02</t>
         </is>
@@ -10520,12 +10520,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O125" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="P125" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_03_index_laws_with_variables_v2.html</t>
         </is>
@@ -10603,12 +10603,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O126" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P126" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_04_expanding_binomial_products_v2.html</t>
         </is>
@@ -10686,12 +10686,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O127" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="P127" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_05_special_products_v2.html</t>
         </is>
@@ -10759,7 +10759,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="M128" s="15" t="inlineStr">
         <is>
           <t>y9_alg_05</t>
         </is>
@@ -10769,12 +10769,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O128" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P128" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_06_factorising_monic_quadratics_v2.html</t>
         </is>
@@ -10804,12 +10804,12 @@
       </c>
       <c r="E129" s="15" t="inlineStr">
         <is>
-          <t>distance_and_midpoint_between_points</t>
+          <t>gradient_of_a_line_segment</t>
         </is>
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_07_distance_and_midpoint_between_points_v2.html</t>
+          <t>y9_alg_07_gradient_of_a_line_segment_v2.html</t>
         </is>
       </c>
       <c r="G129" s="15" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="H129" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers finding the gradient of a line segment</t>
         </is>
       </c>
       <c r="J129" s="15" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="K129" s="15" t="inlineStr">
         <is>
-          <t>Use Pythagoras' theorem to derive the distance formula d = √[(x₂ − x₁)² + (y₂ − y₁)²]; find the midpoint of a line segment using the average of coordinates; apply both to coordinate-geometry problems.</t>
+          <t>Gradient as rise over run, derived from two plotted points with a rise/run right triangle; positive, negative and zero gradients; real contexts (ramps, escalators, skateboard ramps); Slider widget to drag endpoints and watch the gradient update.</t>
         </is>
       </c>
       <c r="L129" s="15" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="Q129" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand link: M03 elaboration 2 covers the same distance content from a measurement angle. Builds on Y8 mea_11 Pythagoras.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03. Gradient given its own lesson under the 18-plan.</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="E130" s="15" t="inlineStr">
         <is>
-          <t>parallel_and_perpendicular_lines</t>
+          <t>midpoint_and_distance</t>
         </is>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_08_parallel_and_perpendicular_lines_v2.html</t>
+          <t>y9_alg_08_midpoint_and_distance_v2.html</t>
         </is>
       </c>
       <c r="G130" s="15" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers the midpoint of a line interval and the distance between two points</t>
         </is>
       </c>
       <c r="J130" s="15" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="K130" s="15" t="inlineStr">
         <is>
-          <t>Use gradients to test whether two lines are parallel (m₁ = m₂) or perpendicular (m₁ × m₂ = −1); apply to coordinate-geometry problems; investigate gradients in real contexts using superimposed photos.</t>
+          <t>Midpoint as the average of coordinates; distance as Pythagoras on the coordinate differences; Cartesian SVG with midpoint marked and the right-triangle legs drawn; errors targeted - subtracting vs averaging, and forgetting the final square root.</t>
         </is>
       </c>
       <c r="L130" s="15" t="inlineStr">
@@ -10917,12 +10917,17 @@
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_06</t>
+          <t>y9_alg_07</t>
         </is>
       </c>
       <c r="N130" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03. Builds on Y8 Pythagoras (y8_mea_11).</t>
         </is>
       </c>
     </row>
@@ -10945,37 +10950,37 @@
       </c>
       <c r="E131" s="15" t="inlineStr">
         <is>
-          <t>graphing_quadratic_functions</t>
+          <t>parallel_and_perpendicular_lines</t>
         </is>
       </c>
       <c r="F131" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_09_graphing_quadratic_functions_v2.html</t>
+          <t>y9_alg_09_parallel_and_perpendicular_lines_v2.html</t>
         </is>
       </c>
       <c r="G131" s="15" t="inlineStr">
         <is>
-          <t>AC9M9A04</t>
+          <t>AC9M9A03</t>
         </is>
       </c>
       <c r="H131" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers parallel and perpendicular lines via their gradients</t>
         </is>
       </c>
       <c r="J131" s="15" t="inlineStr">
         <is>
-          <t>The parameters of quadratics and other functions determine the features of the related graph and can be adjusted depending on the purpose, context and application</t>
+          <t>On a Cartesian plane, the coordinates of 2 distinct points can be used to determine a range of measures of their orientation in relation to each other</t>
         </is>
       </c>
       <c r="K131" s="15" t="inlineStr">
         <is>
-          <t>Identify quadratic relations from tables of values (constant second difference); plot quadratic functions y = x², y = x² + c, y = ax²; describe features — turning point, axis of symmetry, y-intercept, direction of opening; explore with graphing software.</t>
+          <t>Parallel lines have equal gradients; perpendicular gradients multiply to -1 (negative reciprocal); classify line pairs; SVG showing a parallel pair and a perpendicular pair labelled with gradients; Card Sort (parallel/perpendicular/neither); trap named - perpendicular is not merely a negative gradient.</t>
         </is>
       </c>
       <c r="L131" s="15" t="inlineStr">
@@ -10985,7 +10990,7 @@
       </c>
       <c r="M131" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_03</t>
+          <t>y9_alg_07</t>
         </is>
       </c>
       <c r="N131" s="15" t="inlineStr">
@@ -10995,7 +11000,7 @@
       </c>
       <c r="Q131" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: first formal non-linear function. Constant second-difference diagnostic is a key thinking tool.</t>
+          <t>NEW gap-fill: A03 elaboration 2 (parallel/perpendicular) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03.</t>
         </is>
       </c>
     </row>
@@ -11018,12 +11023,12 @@
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>factorised_form_and_x_intercepts</t>
+          <t>graphing_quadratic_functions</t>
         </is>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_10_factorised_form_and_x_intercepts_v2.html</t>
+          <t>y9_alg_10_graphing_quadratic_functions_v2.html</t>
         </is>
       </c>
       <c r="G132" s="15" t="inlineStr">
@@ -11033,12 +11038,12 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>4,5,7</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers identifying and graphing quadratic functions</t>
         </is>
       </c>
       <c r="J132" s="15" t="inlineStr">
@@ -11048,7 +11053,7 @@
       </c>
       <c r="K132" s="15" t="inlineStr">
         <is>
-          <t>Connect the factorised form y = (x − a)(x − b) with x-intercepts at a and b via the null factor law; sketch quadratic graphs given their factorised form; recognise when a quadratic has no real x-intercepts; relate moon-phase illumination to a quadratic-shaped curve.</t>
+          <t>Recognise a quadratic from a constant second difference; plot y=x^2, y=x^2-4, y=(x-2)^2, y=x^2+2x-3; read vertex, axis of symmetry, y-intercept and x-intercepts; Multiple Representations matching (rule/table/graph/features).</t>
         </is>
       </c>
       <c r="L132" s="15" t="inlineStr">
@@ -11058,7 +11063,7 @@
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_04,y9_alg_09</t>
+          <t>y9_alg_06</t>
         </is>
       </c>
       <c r="N132" s="15" t="inlineStr">
@@ -11068,7 +11073,7 @@
       </c>
       <c r="Q132" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: null factor law is THE key threshold concept connecting algebra and geometry of quadratics.</t>
+          <t>Watershed: first formal non-linear function. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03.</t>
         </is>
       </c>
     </row>
@@ -11091,12 +11096,12 @@
       </c>
       <c r="E133" s="15" t="inlineStr">
         <is>
-          <t>solving_monic_quadratic_equations</t>
+          <t>solving_quadratics_graphically</t>
         </is>
       </c>
       <c r="F133" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_11_solving_monic_quadratic_equations_v2.html</t>
+          <t>y9_alg_11_solving_quadratics_graphically_v2.html</t>
         </is>
       </c>
       <c r="G133" s="15" t="inlineStr">
@@ -11106,12 +11111,12 @@
       </c>
       <c r="H133" s="15" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>4,6,7</t>
         </is>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers solving quadratic equations graphically and numerically</t>
         </is>
       </c>
       <c r="J133" s="15" t="inlineStr">
@@ -11121,7 +11126,7 @@
       </c>
       <c r="K133" s="15" t="inlineStr">
         <is>
-          <t>Solve monic quadratic equations x² + bx + c = 0 algebraically by factorising and applying the null factor law; verify solutions by substitution and compare with graphical solutions; include the x² = a case with solutions ±√a.</t>
+          <t>Solutions are the x-values where y=0 (the x-intercepts); numerical route via a table sign-change; x^2=39 gives +/-6.245; x^2=a has two solutions; recognising no real solutions; moon-phase illumination context (First Nations, elaboration 7).</t>
         </is>
       </c>
       <c r="L133" s="15" t="inlineStr">
@@ -11141,7 +11146,7 @@
       </c>
       <c r="Q133" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson. The x² = a case is the simplest pre-completed-square; full completing-the-square is Y10.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Moon-phase elaboration 7 added. Batch y9-alg-04.</t>
         </is>
       </c>
     </row>
@@ -11164,47 +11169,47 @@
       </c>
       <c r="E134" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_linear_functions</t>
+          <t>solving_monic_quadratics_algebraically</t>
         </is>
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_12_modelling_with_linear_functions_v2.html</t>
+          <t>y9_alg_12_solving_monic_quadratics_algebraically_v2.html</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>AC9M9A05</t>
+          <t>AC9M9A04</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>1,2,5</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers solving monic quadratic equations with integer roots algebraically</t>
         </is>
       </c>
       <c r="J134" s="15" t="inlineStr">
         <is>
-          <t>Mathematical modelling can be used to represent and solve problems involving changes, including financial contexts</t>
+          <t>The parameters of quadratics and other functions determine the features of the related graph and can be adjusted depending on the purpose, context and application</t>
         </is>
       </c>
       <c r="K134" s="15" t="inlineStr">
         <is>
-          <t>Model practical contexts using linear functions — cooking with resting times, water tank drainage, trade quotes with call-out fees, change-modelling for temperature and speed; interpret slope and y-intercept in context; check validity of the model.</t>
+          <t>Rearrange to equal zero, factorise, apply the null factor law to read the two roots; connect roots to the x-intercepts of the factorised form; small parabola figure per example; Order the Steps strategy; errors named - not setting to zero, dropping the second root.</t>
         </is>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_06</t>
+          <t>y9_alg_06,y9_alg_11</t>
         </is>
       </c>
       <c r="N134" s="15" t="inlineStr">
@@ -11214,7 +11219,7 @@
       </c>
       <c r="Q134" s="15" t="inlineStr">
         <is>
-          <t>Extends Y8 alg_10. Y9 emphasis is on full modelling cycle including evaluation and reporting.</t>
+          <t>Parabola figure added (fix - was the one solving lesson with no figure). Null factor law folded in here. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-04.</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11242,12 @@
       </c>
       <c r="E135" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_quadratic_functions</t>
+          <t>modelling_with_linear_functions</t>
         </is>
       </c>
       <c r="F135" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_13_modelling_with_quadratic_functions_v2.html</t>
+          <t>y9_alg_13_modelling_with_linear_functions_v2.html</t>
         </is>
       </c>
       <c r="G135" s="15" t="inlineStr">
@@ -11252,12 +11257,12 @@
       </c>
       <c r="H135" s="15" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I135" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers modelling change with linear functions</t>
         </is>
       </c>
       <c r="J135" s="15" t="inlineStr">
@@ -11267,7 +11272,7 @@
       </c>
       <c r="K135" s="15" t="inlineStr">
         <is>
-          <t>Model practical contexts using quadratic functions — projectile paths, parabolic mirrors and satellite dishes, area problems where one dimension is a linear function of another; identify and interpret turning point and intercepts in context; First Nations hunting techniques as a quadratic modelling context.</t>
+          <t>The modelling cycle with linear functions; cooking time with a resting period plus a per-kg rate, tank drainage, perimeter where length is a linear function of width; interpret gradient as a constant rate of change and the y-intercept as the start value; SVG line graphs; Estimation Ladder.</t>
         </is>
       </c>
       <c r="L135" s="15" t="inlineStr">
@@ -11277,7 +11282,7 @@
       </c>
       <c r="M135" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_09,y9_alg_10</t>
+          <t>y9_alg_07</t>
         </is>
       </c>
       <c r="N135" s="15" t="inlineStr">
@@ -11287,7 +11292,7 @@
       </c>
       <c r="Q135" s="15" t="inlineStr">
         <is>
-          <t>New in Y9 — quadratic modelling is the major addition over Y8.</t>
+          <t>A05 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11315,12 @@
       </c>
       <c r="E136" s="15" t="inlineStr">
         <is>
-          <t>choosing_linear_or_quadratic_models</t>
+          <t>modelling_with_quadratic_functions</t>
         </is>
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_14_choosing_linear_or_quadratic_models_v2.html</t>
+          <t>y9_alg_14_modelling_with_quadratic_functions_v2.html</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
@@ -11325,12 +11330,12 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers modelling with quadratic functions</t>
         </is>
       </c>
       <c r="J136" s="15" t="inlineStr">
@@ -11340,7 +11345,7 @@
       </c>
       <c r="K136" s="15" t="inlineStr">
         <is>
-          <t>Choose between linear and quadratic models for financial contexts — combinations of purchases under a budget, profit/loss curves, trade quotes; justify the choice with reference to constant first-difference (linear) or constant second-difference (quadratic) patterns in data.</t>
+          <t>Parabola models; projectile maximum height, fixed-fence area maximisation, parabolic dish/mirror; turning point as a maximum or minimum in context; First Nations hunting-technique quadratic context (elaboration 6); SVG parabolas with turning point and intercepts; Estimation Ladder.</t>
         </is>
       </c>
       <c r="L136" s="15" t="inlineStr">
@@ -11350,7 +11355,7 @@
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_12,y9_alg_13</t>
+          <t>y9_alg_10,y9_alg_13</t>
         </is>
       </c>
       <c r="N136" s="15" t="inlineStr">
@@ -11360,7 +11365,7 @@
       </c>
       <c r="Q136" s="15" t="inlineStr">
         <is>
-          <t>Finance context per house preference. Choice-of-model is the new skill — synthesises the prior two modelling lessons.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11383,37 +11388,37 @@
       </c>
       <c r="E137" s="15" t="inlineStr">
         <is>
-          <t>transformations_of_linear_graphs</t>
+          <t>choosing_linear_or_quadratic_models</t>
         </is>
       </c>
       <c r="F137" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_15_transformations_of_linear_graphs_v2.html</t>
+          <t>y9_alg_15_choosing_linear_or_quadratic_models_v2.html</t>
         </is>
       </c>
       <c r="G137" s="15" t="inlineStr">
         <is>
-          <t>AC9M9A06</t>
+          <t>AC9M9A05</t>
         </is>
       </c>
       <c r="H137" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers choosing and justifying a linear or quadratic model in financial contexts</t>
         </is>
       </c>
       <c r="J137" s="15" t="inlineStr">
         <is>
-          <t>The parameters of quadratics and other functions determine the features of the related graph and can be adjusted depending on the purpose, context and application</t>
+          <t>Mathematical modelling can be used to represent and solve problems involving changes, including financial contexts</t>
         </is>
       </c>
       <c r="K137" s="15" t="inlineStr">
         <is>
-          <t>Investigate transformations of the linear graph y = x — vertical enlargement (y = 2x), vertical compression (y = x/2), reflection (y = −x), vertical translation (y = 2x − 1); formalise the slope-intercept form y = mx + c.</t>
+          <t>Decide linear vs quadratic from the difference pattern (constant first difference = linear, constant second difference = quadratic); financial contexts - budget combinations, a profit parabola, a trade quote with call-out fee; table plus SVG graph for each; Compare Two Solutions strategy.</t>
         </is>
       </c>
       <c r="L137" s="15" t="inlineStr">
@@ -11423,7 +11428,7 @@
       </c>
       <c r="M137" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_06</t>
+          <t>y9_alg_13,y9_alg_14</t>
         </is>
       </c>
       <c r="N137" s="15" t="inlineStr">
@@ -11433,7 +11438,7 @@
       </c>
       <c r="Q137" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 alg_12 informal investigation; Y9 introduces formal transformation language — dilation, translation, reflection.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11456,12 +11461,12 @@
       </c>
       <c r="E138" s="15" t="inlineStr">
         <is>
-          <t>transformations_of_quadratic_graphs</t>
+          <t>transformations_of_linear_graphs</t>
         </is>
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_16_transformations_of_quadratic_graphs_v2.html</t>
+          <t>y9_alg_16_transformations_of_linear_graphs_v2.html</t>
         </is>
       </c>
       <c r="G138" s="15" t="inlineStr">
@@ -11471,12 +11476,12 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers transformations of the linear graph y = x</t>
         </is>
       </c>
       <c r="J138" s="15" t="inlineStr">
@@ -11486,7 +11491,7 @@
       </c>
       <c r="K138" s="15" t="inlineStr">
         <is>
-          <t>Investigate transformations of the parabola y = x² in completed-square form y = a(x − h)² + k; identify how a controls dilation/reflection, h controls horizontal translation, k controls vertical translation; locate the turning point at (h, k).</t>
+          <t>Systematic one-parameter variation from y=x to y=2x, y=x/2, y=-x, y=2x-1; build the slope-intercept form y=mx+c, m as gradient and c as intercept; base vs transformed line in contrasting colours (SVG); Slider widget as the spine.</t>
         </is>
       </c>
       <c r="L138" s="15" t="inlineStr">
@@ -11496,7 +11501,7 @@
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_09,y9_alg_15</t>
+          <t>y9_alg_07</t>
         </is>
       </c>
       <c r="N138" s="15" t="inlineStr">
@@ -11506,7 +11511,7 @@
       </c>
       <c r="Q138" s="15" t="inlineStr">
         <is>
-          <t>Completed-square form introduced here as a parameter-variation tool, not as a solving technique (that's Y10).</t>
+          <t>A06 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
@@ -11529,12 +11534,12 @@
       </c>
       <c r="E139" s="15" t="inlineStr">
         <is>
-          <t>families_of_functions</t>
+          <t>transformations_of_quadratic_graphs</t>
         </is>
       </c>
       <c r="F139" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_17_families_of_functions_v2.html</t>
+          <t>y9_alg_17_transformations_of_quadratic_graphs_v2.html</t>
         </is>
       </c>
       <c r="G139" s="15" t="inlineStr">
@@ -11544,12 +11549,12 @@
       </c>
       <c r="H139" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson covers transformations of the parabola y = x^2 in completed-square form</t>
         </is>
       </c>
       <c r="J139" s="15" t="inlineStr">
@@ -11559,7 +11564,7 @@
       </c>
       <c r="K139" s="15" t="inlineStr">
         <is>
-          <t>Explore other function families using digital tools — reciprocal y = 1/x, square root y = √x, cubic y = x³, exponential y = 2ˣ and y = (1/2)ˣ; identify key features and pattern-spot the effect of parameter changes.</t>
+          <t>Completed-square form y=a(x-h)^2+k; a controls dilation/reflection, h horizontal translation, k vertical translation; turning point at (h,k); base vs transformed parabola (SVG); Slider widget; completed-square treated as a parameter tool, not a solving technique.</t>
         </is>
       </c>
       <c r="L139" s="15" t="inlineStr">
@@ -11569,7 +11574,7 @@
       </c>
       <c r="M139" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_15,y9_alg_16</t>
+          <t>y9_alg_10,y9_alg_16</t>
         </is>
       </c>
       <c r="N139" s="15" t="inlineStr">
@@ -11579,14 +11584,14 @@
       </c>
       <c r="Q139" s="15" t="inlineStr">
         <is>
-          <t>Taster lesson — students will see each family more formally in Y10/11. Focus is on parameter-variation skill, not deep treatment.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="16">
       <c r="A140" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_01</t>
+          <t>y9_alg_18</t>
         </is>
       </c>
       <c r="B140" s="15" t="n">
@@ -11594,50 +11599,55 @@
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Algebra</t>
         </is>
       </c>
       <c r="D140" s="15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E140" s="15" t="inlineStr">
         <is>
-          <t>surface_area_of_right_prisms</t>
+          <t>families_of_functions</t>
         </is>
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_01_surface_area_of_right_prisms_v2.html</t>
+          <t>y9_alg_18_families_of_functions_v2.html</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M01</t>
+          <t>AC9M9A06</t>
         </is>
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Partial - this lesson is a taster of the reciprocal, square-root, cubic and exponential families</t>
         </is>
       </c>
       <c r="J140" s="15" t="inlineStr">
         <is>
-          <t>Spatial relationships in 1, 2 and 3 dimensions can be quantified using appropriate units to solve problems in various contexts</t>
+          <t>The parameters of quadratics and other functions determine the features of the related graph and can be adjusted depending on the purpose, context and application</t>
         </is>
       </c>
       <c r="K140" s="15" t="inlineStr">
         <is>
-          <t>Use nets to derive surface-area formulas for rectangular and triangular right prisms; calculate surface area by summing component face areas; verify by re-drawing the net in a different layout.</t>
+          <t>A guided tour of the reciprocal y=1/x, square root y=root x, cubic y=x^3, and exponentials y=2^x and y=(1/2)^x; signature shapes and key features; vary one parameter; Multiple Representations match (rule/graph/name/shape); kept light as a taster.</t>
         </is>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>y9_alg_16,y9_alg_17</t>
         </is>
       </c>
       <c r="N140" s="15" t="inlineStr">
@@ -11647,14 +11657,14 @@
       </c>
       <c r="Q140" s="15" t="inlineStr">
         <is>
-          <t>Surface area is new in Y9 — Y8 covered volume of prisms (mea_03/04) but not SA.</t>
+          <t>NEW gap-fill: A06 elaboration 3 (function families) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="16">
       <c r="A141" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_02</t>
+          <t>y9_mea_01</t>
         </is>
       </c>
       <c r="B141" s="15" t="n">
@@ -11666,16 +11676,16 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="15" t="inlineStr">
         <is>
-          <t>surface_area_and_volume_of_cylinders</t>
+          <t>surface_area_of_right_prisms</t>
         </is>
       </c>
       <c r="F141" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_02_surface_area_and_volume_of_cylinders_v2.html</t>
+          <t>y9_mea_01_surface_area_of_right_prisms_v2.html</t>
         </is>
       </c>
       <c r="G141" s="15" t="inlineStr">
@@ -11685,7 +11695,7 @@
       </c>
       <c r="H141" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I141" s="15" t="inlineStr">
@@ -11700,7 +11710,7 @@
       </c>
       <c r="K141" s="15" t="inlineStr">
         <is>
-          <t>Apply formulas V = πr²h and SA = 2πr² + 2πrh for a cylinder; derive the curved-surface area by unrolling the cylinder into a rectangle of dimensions 2πr by h; can-cooler material problems.</t>
+          <t>Use nets to derive surface-area formulas for rectangular and triangular right prisms; calculate surface area by summing component face areas; verify by re-drawing the net in a different layout.</t>
         </is>
       </c>
       <c r="L141" s="15" t="inlineStr">
@@ -11708,11 +11718,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M141" s="15" t="inlineStr">
-        <is>
-          <t>y9_mea_01</t>
-        </is>
-      </c>
+      <c r="M141" s="15" t="n"/>
       <c r="N141" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -11720,14 +11726,14 @@
       </c>
       <c r="Q141" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: the unrolling visualisation is essential for retention. Cylinder is the first non-prism solid Y9 students meet formally.</t>
+          <t>Surface area is new in Y9 — Y8 covered volume of prisms (mea_03/04) but not SA.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="16">
       <c r="A142" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_03</t>
+          <t>y9_mea_02</t>
         </is>
       </c>
       <c r="B142" s="15" t="n">
@@ -11739,16 +11745,16 @@
         </is>
       </c>
       <c r="D142" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" s="15" t="inlineStr">
         <is>
-          <t>optimising_surface_area_and_volume</t>
+          <t>surface_area_and_volume_of_cylinders</t>
         </is>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_03_optimising_surface_area_and_volume_v2.html</t>
+          <t>y9_mea_02_surface_area_and_volume_of_cylinders_v2.html</t>
         </is>
       </c>
       <c r="G142" s="15" t="inlineStr">
@@ -11758,7 +11764,7 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
@@ -11773,17 +11779,17 @@
       </c>
       <c r="K142" s="15" t="inlineStr">
         <is>
-          <t>Investigate optimisation problems — prisms with the same volume but different surface areas; can-cooler material minimisation; conjecture and test which shapes give the smallest surface area for a given volume; First Nations objects/technologies as SA-volume contexts.</t>
+          <t>Apply formulas V = πr²h and SA = 2πr² + 2πrh for a cylinder; derive the curved-surface area by unrolling the cylinder into a rectangle of dimensions 2πr by h; can-cooler material problems.</t>
         </is>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_01,y9_mea_02</t>
+          <t>y9_mea_01</t>
         </is>
       </c>
       <c r="N142" s="15" t="inlineStr">
@@ -11793,14 +11799,14 @@
       </c>
       <c r="Q142" s="15" t="inlineStr">
         <is>
-          <t>Investigation-style lesson — practice should include some open-response conjecture-and-test items.</t>
+          <t>Watershed lesson: the unrolling visualisation is essential for retention. Cylinder is the first non-prism solid Y9 students meet formally.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="16">
       <c r="A143" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_04</t>
+          <t>y9_mea_03</t>
         </is>
       </c>
       <c r="B143" s="15" t="n">
@@ -11812,31 +11818,31 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E143" s="15" t="inlineStr">
         <is>
-          <t>introducing_scientific_notation</t>
+          <t>optimising_surface_area_and_volume</t>
         </is>
       </c>
       <c r="F143" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_04_introducing_scientific_notation_v2.html</t>
+          <t>y9_mea_03_optimising_surface_area_and_volume_v2.html</t>
         </is>
       </c>
       <c r="G143" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M02, AC9M9A01</t>
+          <t>AC9M9M01</t>
         </is>
       </c>
       <c r="H143" s="15" t="inlineStr">
         <is>
-          <t>1 (M02); 7 (A01)</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
-          <t>Strict + cross-tag</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="J143" s="15" t="inlineStr">
@@ -11846,17 +11852,17 @@
       </c>
       <c r="K143" s="15" t="inlineStr">
         <is>
-          <t>Convert numbers between standard form and scientific notation a × 10ⁿ where 1 ≤ a &lt; 10; represent very large quantities (4.6 × 10⁹ for the age of the Earth) and very small ones (5.68 × 10⁻²¹ for the mass of a sugar molecule); connect to SI prefixes from pico- to tera-.</t>
+          <t>Investigate optimisation problems — prisms with the same volume but different surface areas; can-cooler material minimisation; conjecture and test which shapes give the smallest surface area for a given volume; First Nations objects/technologies as SA-volume contexts.</t>
         </is>
       </c>
       <c r="L143" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M143" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_01</t>
+          <t>y9_mea_01,y9_mea_02</t>
         </is>
       </c>
       <c r="N143" s="15" t="inlineStr">
@@ -11866,14 +11872,14 @@
       </c>
       <c r="Q143" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand prereq: needs y9_alg_01 negative exponents. Important sequencing — Algebra first, then Measurement.</t>
+          <t>Investigation-style lesson — practice should include some open-response conjecture-and-test items.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="16">
       <c r="A144" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_05</t>
+          <t>y9_mea_04</t>
         </is>
       </c>
       <c r="B144" s="15" t="n">
@@ -11885,31 +11891,31 @@
         </is>
       </c>
       <c r="D144" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E144" s="15" t="inlineStr">
         <is>
-          <t>operations_with_scientific_notation</t>
+          <t>introducing_scientific_notation</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_05_operations_with_scientific_notation_v2.html</t>
+          <t>y9_mea_04_introducing_scientific_notation_v2.html</t>
         </is>
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M02</t>
+          <t>AC9M9M02, AC9M9A01</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1 (M02); 7 (A01)</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Strict + cross-tag</t>
         </is>
       </c>
       <c r="J144" s="15" t="inlineStr">
@@ -11919,7 +11925,7 @@
       </c>
       <c r="K144" s="15" t="inlineStr">
         <is>
-          <t>Multiply and divide numbers in scientific notation using exponent laws; estimate orders of magnitude for products and quotients; record measurements to an accuracy appropriate to the measuring instrument (cylinder vs pipette).</t>
+          <t>Convert numbers between standard form and scientific notation a × 10ⁿ where 1 ≤ a &lt; 10; represent very large quantities (4.6 × 10⁹ for the age of the Earth) and very small ones (5.68 × 10⁻²¹ for the mass of a sugar molecule); connect to SI prefixes from pico- to tera-.</t>
         </is>
       </c>
       <c r="L144" s="15" t="inlineStr">
@@ -11929,19 +11935,24 @@
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_04</t>
+          <t>y9_alg_01</t>
         </is>
       </c>
       <c r="N144" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Cross-strand prereq: needs y9_alg_01 negative exponents. Important sequencing — Algebra first, then Measurement.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="16">
       <c r="A145" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_06</t>
+          <t>y9_mea_05</t>
         </is>
       </c>
       <c r="B145" s="15" t="n">
@@ -11953,26 +11964,26 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E145" s="15" t="inlineStr">
         <is>
-          <t>applying_pythagoras_and_trig_to_spatial_problems</t>
+          <t>operations_with_scientific_notation</t>
         </is>
       </c>
       <c r="F145" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_06_applying_pythagoras_and_trig_to_spatial_problems_v2.html</t>
+          <t>y9_mea_05_operations_with_scientific_notation_v2.html</t>
         </is>
       </c>
       <c r="G145" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M03</t>
+          <t>AC9M9M02</t>
         </is>
       </c>
       <c r="H145" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I145" s="15" t="inlineStr">
@@ -11987,7 +11998,7 @@
       </c>
       <c r="K145" s="15" t="inlineStr">
         <is>
-          <t>Apply Pythagoras' theorem and trigonometric ratios together in spatial problems — surveying, ramp design, building diagonals; multi-step problems where Pythagoras gives one side and trig gives an angle, or vice versa; distance between Cartesian points as a Pythagoras application.</t>
+          <t>Multiply and divide numbers in scientific notation using exponent laws; estimate orders of magnitude for products and quotients; record measurements to an accuracy appropriate to the measuring instrument (cylinder vs pipette).</t>
         </is>
       </c>
       <c r="L145" s="15" t="inlineStr">
@@ -11997,7 +12008,7 @@
       </c>
       <c r="M145" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_03</t>
+          <t>y9_mea_04</t>
         </is>
       </c>
       <c r="N145" s="15" t="inlineStr">
@@ -12005,16 +12016,12 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q145" s="15" t="inlineStr">
-        <is>
-          <t>Cross-strand prereq: needs y9_spa_03 (sin/cos/tan defined). Important sequencing — Space SP01 must come before this. M03 elaboration 2 (distance) also covered in y9_alg_07.</t>
-        </is>
-      </c>
+      <c r="Q145" s="15" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" s="16">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_07</t>
+          <t>y9_mea_06</t>
         </is>
       </c>
       <c r="B146" s="15" t="n">
@@ -12026,16 +12033,16 @@
         </is>
       </c>
       <c r="D146" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E146" s="15" t="inlineStr">
         <is>
-          <t>scale_factor_effect_on_area_and_volume</t>
+          <t>applying_pythagoras_and_trig_to_spatial_problems</t>
         </is>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_07_scale_factor_effect_on_area_and_volume_v2.html</t>
+          <t>y9_mea_06_applying_pythagoras_and_trig_to_spatial_problems_v2.html</t>
         </is>
       </c>
       <c r="G146" s="15" t="inlineStr">
@@ -12045,7 +12052,7 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
@@ -12060,7 +12067,7 @@
       </c>
       <c r="K146" s="15" t="inlineStr">
         <is>
-          <t>Investigate the effect of scale factor k on area (× k²) and volume (× k³) for similar figures; apply to scaled models, photographs and original objects; estimate actual measurements from images using proportional reasoning.</t>
+          <t>Apply Pythagoras' theorem and trigonometric ratios together in spatial problems — surveying, ramp design, building diagonals; multi-step problems where Pythagoras gives one side and trig gives an angle, or vice versa; distance between Cartesian points as a Pythagoras application.</t>
         </is>
       </c>
       <c r="L146" s="15" t="inlineStr">
@@ -12070,7 +12077,7 @@
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_05</t>
+          <t>y9_spa_03</t>
         </is>
       </c>
       <c r="N146" s="15" t="inlineStr">
@@ -12080,14 +12087,14 @@
       </c>
       <c r="Q146" s="15" t="inlineStr">
         <is>
-          <t>Overlaps with y9_spa_05 — M03 focus is on similar right triangles and applications; SP02 focus is on the enlargement transformation itself. Cross-tag noted.</t>
+          <t>Cross-strand prereq: needs y9_spa_03 (sin/cos/tan defined). Important sequencing — Space SP01 must come before this. M03 elaboration 2 (distance) also covered in y9_alg_07.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="16">
       <c r="A147" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_08</t>
+          <t>y9_mea_07</t>
         </is>
       </c>
       <c r="B147" s="15" t="n">
@@ -12099,16 +12106,16 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E147" s="15" t="inlineStr">
         <is>
-          <t>integrated_spatial_problem_solving</t>
+          <t>scale_factor_effect_on_area_and_volume</t>
         </is>
       </c>
       <c r="F147" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_08_integrated_spatial_problem_solving_v2.html</t>
+          <t>y9_mea_07_scale_factor_effect_on_area_and_volume_v2.html</t>
         </is>
       </c>
       <c r="G147" s="15" t="inlineStr">
@@ -12118,7 +12125,7 @@
       </c>
       <c r="H147" s="15" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I147" s="15" t="inlineStr">
@@ -12133,17 +12140,17 @@
       </c>
       <c r="K147" s="15" t="inlineStr">
         <is>
-          <t>Integrate similarity, Pythagoras' theorem, rates and algebra in extended problems — Biltmore stick design for measuring tree height and diameter; the triangle inequality and related conjectures for acute/obtuse triangles; minimal information sets to determine a triangle.</t>
+          <t>Investigate the effect of scale factor k on area (× k²) and volume (× k³) for similar figures; apply to scaled models, photographs and original objects; estimate actual measurements from images using proportional reasoning.</t>
         </is>
       </c>
       <c r="L147" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M147" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_06,y9_mea_07</t>
+          <t>y9_spa_05</t>
         </is>
       </c>
       <c r="N147" s="15" t="inlineStr">
@@ -12153,14 +12160,14 @@
       </c>
       <c r="Q147" s="15" t="inlineStr">
         <is>
-          <t>Integration lesson — open-ended practice fits the conjecture/investigation flavour.</t>
+          <t>Overlaps with y9_spa_05 — M03 focus is on similar right triangles and applications; SP02 focus is on the enlargement transformation itself. Cross-tag noted.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="16">
       <c r="A148" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_09</t>
+          <t>y9_mea_08</t>
         </is>
       </c>
       <c r="B148" s="15" t="n">
@@ -12172,26 +12179,26 @@
         </is>
       </c>
       <c r="D148" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E148" s="15" t="inlineStr">
         <is>
-          <t>absolute_relative_and_percentage_error</t>
+          <t>integrated_spatial_problem_solving</t>
         </is>
       </c>
       <c r="F148" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_09_absolute_relative_and_percentage_error_v2.html</t>
+          <t>y9_mea_08_integrated_spatial_problem_solving_v2.html</t>
         </is>
       </c>
       <c r="G148" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M04</t>
+          <t>AC9M9M03</t>
         </is>
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
@@ -12201,29 +12208,39 @@
       </c>
       <c r="J148" s="15" t="inlineStr">
         <is>
-          <t>Calculations are affected by sources of error and should be interpreted in the context of the problem</t>
+          <t>Spatial relationships in 1, 2 and 3 dimensions can be quantified using appropriate units to solve problems in various contexts</t>
         </is>
       </c>
       <c r="K148" s="15" t="inlineStr">
         <is>
-          <t>Calculate absolute error |measured − exact|, relative error (absolute error ÷ exact value), and percentage error; use absolute value notation in the error formula; recognise that all measurements are estimates with associated uncertainty.</t>
+          <t>Integrate similarity, Pythagoras' theorem, rates and algebra in extended problems — Biltmore stick design for measuring tree height and diameter; the triangle inequality and related conjectures for acute/obtuse triangles; minimal information sets to determine a triangle.</t>
         </is>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>y9_mea_06,y9_mea_07</t>
         </is>
       </c>
       <c r="N148" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Integration lesson — open-ended practice fits the conjecture/investigation flavour.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="16">
       <c r="A149" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_10</t>
+          <t>y9_mea_09</t>
         </is>
       </c>
       <c r="B149" s="15" t="n">
@@ -12235,16 +12252,16 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149" s="15" t="inlineStr">
         <is>
-          <t>applying_error_to_real_contexts</t>
+          <t>absolute_relative_and_percentage_error</t>
         </is>
       </c>
       <c r="F149" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_10_applying_error_to_real_contexts_v2.html</t>
+          <t>y9_mea_09_absolute_relative_and_percentage_error_v2.html</t>
         </is>
       </c>
       <c r="G149" s="15" t="inlineStr">
@@ -12254,7 +12271,7 @@
       </c>
       <c r="H149" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I149" s="15" t="inlineStr">
@@ -12269,19 +12286,15 @@
       </c>
       <c r="K149" s="15" t="inlineStr">
         <is>
-          <t>Apply error analysis to real contexts — percentage error in predicted vs actual event attendance; budgeted vs actual expenditure; give suitable lower and upper bounds for measurement values in practical contexts.</t>
+          <t>Calculate absolute error |measured − exact|, relative error (absolute error ÷ exact value), and percentage error; use absolute value notation in the error formula; recognise that all measurements are estimates with associated uncertainty.</t>
         </is>
       </c>
       <c r="L149" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
-        </is>
-      </c>
-      <c r="M149" s="15" t="inlineStr">
-        <is>
-          <t>y9_mea_09</t>
-        </is>
-      </c>
+          <t>auto-marked</t>
+        </is>
+      </c>
+      <c r="M149" s="15" t="n"/>
       <c r="N149" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -12291,7 +12304,7 @@
     <row r="150" ht="15" customHeight="1" s="16">
       <c r="A150" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_11</t>
+          <t>y9_mea_10</t>
         </is>
       </c>
       <c r="B150" s="15" t="n">
@@ -12303,26 +12316,26 @@
         </is>
       </c>
       <c r="D150" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E150" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_direct_proportion</t>
+          <t>applying_error_to_real_contexts</t>
         </is>
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_11_modelling_with_direct_proportion_v2.html</t>
+          <t>y9_mea_10_applying_error_to_real_contexts_v2.html</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>AC9M9M05</t>
+          <t>AC9M9M04</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
@@ -12332,12 +12345,12 @@
       </c>
       <c r="J150" s="15" t="inlineStr">
         <is>
-          <t>Mathematical modelling can be used to represent and solve problems involving proportion, rates, ratios and scale, including in financial contexts</t>
+          <t>Calculations are affected by sources of error and should be interpreted in the context of the problem</t>
         </is>
       </c>
       <c r="K150" s="15" t="inlineStr">
         <is>
-          <t>Model direct-proportion situations — pro rata pay rates, currency exchange, multiple quotes for a job, Hooke's law from physics; investigate situations where proportion is not maintained (image editing/distortion); building and construction standards for staircases and escalators.</t>
+          <t>Apply error analysis to real contexts — percentage error in predicted vs actual event attendance; budgeted vs actual expenditure; give suitable lower and upper bounds for measurement values in practical contexts.</t>
         </is>
       </c>
       <c r="L150" s="15" t="inlineStr">
@@ -12345,21 +12358,22 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>y9_mea_09</t>
+        </is>
+      </c>
       <c r="N150" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q150" s="15" t="inlineStr">
-        <is>
-          <t>Extends Y8 mea_14 scale and proportion work; Y9 adds the formal modelling cycle.</t>
-        </is>
-      </c>
+      <c r="Q150" s="15" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1" s="16">
       <c r="A151" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_12</t>
+          <t>y9_mea_11</t>
         </is>
       </c>
       <c r="B151" s="15" t="n">
@@ -12371,16 +12385,16 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E151" s="15" t="inlineStr">
         <is>
-          <t>applied_rate_modelling</t>
+          <t>modelling_with_direct_proportion</t>
         </is>
       </c>
       <c r="F151" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_12_applied_rate_modelling_v2.html</t>
+          <t>y9_mea_11_modelling_with_direct_proportion_v2.html</t>
         </is>
       </c>
       <c r="G151" s="15" t="inlineStr">
@@ -12390,7 +12404,7 @@
       </c>
       <c r="H151" s="15" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I151" s="15" t="inlineStr">
@@ -12405,7 +12419,7 @@
       </c>
       <c r="K151" s="15" t="inlineStr">
         <is>
-          <t>Model applied rate contexts — density, birth rate, flow rate, heart rate; vehicle acceleration and deceleration; explore fire-spread rate techniques in First Nations Australians' land management under varying fuel types, wind, temperature and humidity.</t>
+          <t>Model direct-proportion situations — pro rata pay rates, currency exchange, multiple quotes for a job, Hooke's law from physics; investigate situations where proportion is not maintained (image editing/distortion); building and construction standards for staircases and escalators.</t>
         </is>
       </c>
       <c r="L151" s="15" t="inlineStr">
@@ -12413,21 +12427,22 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M151" s="15" t="inlineStr">
-        <is>
-          <t>y9_mea_11</t>
-        </is>
-      </c>
+      <c r="M151" s="15" t="n"/>
       <c r="N151" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Extends Y8 mea_14 scale and proportion work; Y9 adds the formal modelling cycle.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="16">
       <c r="A152" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_01</t>
+          <t>y9_mea_12</t>
         </is>
       </c>
       <c r="B152" s="15" t="n">
@@ -12435,30 +12450,30 @@
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="D152" s="15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E152" s="15" t="inlineStr">
         <is>
-          <t>naming_sides_in_right_angled_triangles</t>
+          <t>applied_rate_modelling</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_01_naming_sides_in_right_angled_triangles_v2.html</t>
+          <t>y9_mea_12_applied_rate_modelling_v2.html</t>
         </is>
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>AC9M9SP01</t>
+          <t>AC9M9M05</t>
         </is>
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
@@ -12468,17 +12483,22 @@
       </c>
       <c r="J152" s="15" t="inlineStr">
         <is>
-          <t>Trigonometric ratios are an application of the property of similarity for right-angled triangles</t>
+          <t>Mathematical modelling can be used to represent and solve problems involving proportion, rates, ratios and scale, including in financial contexts</t>
         </is>
       </c>
       <c r="K152" s="15" t="inlineStr">
         <is>
-          <t>Identify and label the hypotenuse, the side opposite a given angle, and the side adjacent to a given angle in any right-angled triangle; recognise that 'opposite' and 'adjacent' depend on the chosen reference angle; the hypotenuse is always opposite the right angle.</t>
+          <t>Model applied rate contexts — density, birth rate, flow rate, heart rate; vehicle acceleration and deceleration; explore fire-spread rate techniques in First Nations Australians' land management under varying fuel types, wind, temperature and humidity.</t>
         </is>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>y9_mea_11</t>
         </is>
       </c>
       <c r="N152" s="15" t="inlineStr">
@@ -12486,16 +12506,12 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q152" s="15" t="inlineStr">
-        <is>
-          <t>Watershed lesson: getting the labels right is the foundation for all of trigonometry. Misnaming sides is the #1 trig misconception.</t>
-        </is>
-      </c>
+      <c r="Q152" s="15" t="n"/>
     </row>
     <row r="153" ht="15" customHeight="1" s="16">
       <c r="A153" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_02</t>
+          <t>y9_spa_01</t>
         </is>
       </c>
       <c r="B153" s="15" t="n">
@@ -12507,16 +12523,16 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="15" t="inlineStr">
         <is>
-          <t>discovering_constant_trig_ratios</t>
+          <t>naming_sides_in_right_angled_triangles</t>
         </is>
       </c>
       <c r="F153" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_02_discovering_constant_trig_ratios_v2.html</t>
+          <t>y9_spa_01_naming_sides_in_right_angled_triangles_v2.html</t>
         </is>
       </c>
       <c r="G153" s="15" t="inlineStr">
@@ -12526,7 +12542,7 @@
       </c>
       <c r="H153" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I153" s="15" t="inlineStr">
@@ -12541,19 +12557,15 @@
       </c>
       <c r="K153" s="15" t="inlineStr">
         <is>
-          <t>Investigate nested similar right-angled triangles with a fixed acute angle; measure side ratios systematically and observe that opposite/hypotenuse, adjacent/hypotenuse and opposite/adjacent stay constant for that angle; connect to the unit-hypotenuse triangle.</t>
+          <t>Identify and label the hypotenuse, the side opposite a given angle, and the side adjacent to a given angle in any right-angled triangle; recognise that 'opposite' and 'adjacent' depend on the chosen reference angle; the hypotenuse is always opposite the right angle.</t>
         </is>
       </c>
       <c r="L153" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
-        </is>
-      </c>
-      <c r="M153" s="15" t="inlineStr">
-        <is>
-          <t>y9_spa_01</t>
-        </is>
-      </c>
+          <t>auto-marked</t>
+        </is>
+      </c>
+      <c r="M153" s="15" t="n"/>
       <c r="N153" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -12561,14 +12573,14 @@
       </c>
       <c r="Q153" s="15" t="inlineStr">
         <is>
-          <t>Investigation lesson — practice should include some measure-and-tabulate items. The 'constancy' insight earns the formal definitions in spa_03.</t>
+          <t>Watershed lesson: getting the labels right is the foundation for all of trigonometry. Misnaming sides is the #1 trig misconception.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="16">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_03</t>
+          <t>y9_spa_02</t>
         </is>
       </c>
       <c r="B154" s="15" t="n">
@@ -12580,16 +12592,16 @@
         </is>
       </c>
       <c r="D154" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="15" t="inlineStr">
         <is>
-          <t>defining_sin_cos_tan</t>
+          <t>discovering_constant_trig_ratios</t>
         </is>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_03_defining_sin_cos_tan_v2.html</t>
+          <t>y9_spa_02_discovering_constant_trig_ratios_v2.html</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
@@ -12599,7 +12611,7 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
@@ -12614,17 +12626,17 @@
       </c>
       <c r="K154" s="15" t="inlineStr">
         <is>
-          <t>Define sin θ = opposite/hypotenuse, cos θ = adjacent/hypotenuse, tan θ = opposite/adjacent; read sin, cos, tan values from a calculator for any acute angle; connect tan θ to the gradient of a line passing through the origin.</t>
+          <t>Investigate nested similar right-angled triangles with a fixed acute angle; measure side ratios systematically and observe that opposite/hypotenuse, adjacent/hypotenuse and opposite/adjacent stay constant for that angle; connect to the unit-hypotenuse triangle.</t>
         </is>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_02</t>
+          <t>y9_spa_01</t>
         </is>
       </c>
       <c r="N154" s="15" t="inlineStr">
@@ -12634,14 +12646,14 @@
       </c>
       <c r="Q154" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: formal trig definitions. Mnemonics (SOH-CAH-TOA) introduced here. Cross-strand prereq for y9_mea_06.</t>
+          <t>Investigation lesson — practice should include some measure-and-tabulate items. The 'constancy' insight earns the formal definitions in spa_03.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="16">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_04</t>
+          <t>y9_spa_03</t>
         </is>
       </c>
       <c r="B155" s="15" t="n">
@@ -12653,26 +12665,26 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E155" s="15" t="inlineStr">
         <is>
-          <t>enlargement_transformation</t>
+          <t>defining_sin_cos_tan</t>
         </is>
       </c>
       <c r="F155" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_04_enlargement_transformation_v2.html</t>
+          <t>y9_spa_03_defining_sin_cos_tan_v2.html</t>
         </is>
       </c>
       <c r="G155" s="15" t="inlineStr">
         <is>
-          <t>AC9M9SP02</t>
+          <t>AC9M9SP01</t>
         </is>
       </c>
       <c r="H155" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I155" s="15" t="inlineStr">
@@ -12687,7 +12699,7 @@
       </c>
       <c r="K155" s="15" t="inlineStr">
         <is>
-          <t>Apply the enlargement transformation to shapes using a centre of enlargement and a scale factor; recognise that corresponding angles are equal and corresponding sides are in a fixed ratio; solve enlargement problems using similarity.</t>
+          <t>Define sin θ = opposite/hypotenuse, cos θ = adjacent/hypotenuse, tan θ = opposite/adjacent; read sin, cos, tan values from a calculator for any acute angle; connect tan θ to the gradient of a line passing through the origin.</t>
         </is>
       </c>
       <c r="L155" s="15" t="inlineStr">
@@ -12695,6 +12707,11 @@
           <t>auto-marked</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>y9_spa_02</t>
+        </is>
+      </c>
       <c r="N155" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -12702,14 +12719,14 @@
       </c>
       <c r="Q155" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 spa_01/03 similarity work.</t>
+          <t>Watershed lesson: formal trig definitions. Mnemonics (SOH-CAH-TOA) introduced here. Cross-strand prereq for y9_mea_06.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="16">
       <c r="A156" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_05</t>
+          <t>y9_spa_04</t>
         </is>
       </c>
       <c r="B156" s="15" t="n">
@@ -12721,16 +12738,16 @@
         </is>
       </c>
       <c r="D156" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>scale_factor_effect_on_area_and_volume</t>
+          <t>enlargement_transformation</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_05_scale_factor_effect_on_area_and_volume_v2.html</t>
+          <t>y9_spa_04_enlargement_transformation_v2.html</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
@@ -12740,7 +12757,7 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
@@ -12755,7 +12772,7 @@
       </c>
       <c r="K156" s="15" t="inlineStr">
         <is>
-          <t>Investigate how enlargement by scale factor k affects area (× k²) and volume (× k³); compare side lengths, areas and volumes of similar squares and cubes for k = 2, 3, and fractional k; generalise the pattern to any similar 2D and 3D shape.</t>
+          <t>Apply the enlargement transformation to shapes using a centre of enlargement and a scale factor; recognise that corresponding angles are equal and corresponding sides are in a fixed ratio; solve enlargement problems using similarity.</t>
         </is>
       </c>
       <c r="L156" s="15" t="inlineStr">
@@ -12763,11 +12780,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M156" s="15" t="inlineStr">
-        <is>
-          <t>y9_spa_04</t>
-        </is>
-      </c>
+      <c r="M156" s="15" t="n"/>
       <c r="N156" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -12775,14 +12788,14 @@
       </c>
       <c r="Q156" s="15" t="inlineStr">
         <is>
-          <t>Overlaps with y9_mea_07 — same content from the spatial-transformation angle. Both kept; complementary framings.</t>
+          <t>Builds on Y8 spa_01/03 similarity work.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="16">
       <c r="A157" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_06</t>
+          <t>y9_spa_05</t>
         </is>
       </c>
       <c r="B157" s="15" t="n">
@@ -12794,26 +12807,26 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E157" s="15" t="inlineStr">
         <is>
-          <t>algorithms_for_triangle_properties</t>
+          <t>scale_factor_effect_on_area_and_volume</t>
         </is>
       </c>
       <c r="F157" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_06_algorithms_for_triangle_properties_v2.html</t>
+          <t>y9_spa_05_scale_factor_effect_on_area_and_volume_v2.html</t>
         </is>
       </c>
       <c r="G157" s="15" t="inlineStr">
         <is>
-          <t>AC9M9SP03</t>
+          <t>AC9M9SP02</t>
         </is>
       </c>
       <c r="H157" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I157" s="15" t="inlineStr">
@@ -12828,12 +12841,17 @@
       </c>
       <c r="K157" s="15" t="inlineStr">
         <is>
-          <t>Design an algorithm (flow chart or pseudocode) that applies the triangle inequality to determine whether three given lengths can form a triangle; design an alternative algorithm to generate Pythagorean triples systematically.</t>
+          <t>Investigate how enlargement by scale factor k affects area (× k²) and volume (× k³); compare side lengths, areas and volumes of similar squares and cubes for k = 2, 3, and fractional k; generalise the pattern to any similar 2D and 3D shape.</t>
         </is>
       </c>
       <c r="L157" s="15" t="inlineStr">
         <is>
-          <t>strategy-MCQ</t>
+          <t>auto-marked</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>y9_spa_04</t>
         </is>
       </c>
       <c r="N157" s="15" t="inlineStr">
@@ -12843,14 +12861,14 @@
       </c>
       <c r="Q157" s="15" t="inlineStr">
         <is>
-          <t>Strategy-MCQ matches the decision-tree algorithm-design content.</t>
+          <t>Overlaps with y9_mea_07 — same content from the spatial-transformation angle. Both kept; complementary framings.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="16">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_07</t>
+          <t>y9_spa_06</t>
         </is>
       </c>
       <c r="B158" s="15" t="n">
@@ -12862,16 +12880,16 @@
         </is>
       </c>
       <c r="D158" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E158" s="15" t="inlineStr">
         <is>
-          <t>algorithms_for_geometric_constructions</t>
+          <t>algorithms_for_triangle_properties</t>
         </is>
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_07_algorithms_for_geometric_constructions_v2.html</t>
+          <t>y9_spa_06_algorithms_for_triangle_properties_v2.html</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
@@ -12881,7 +12899,7 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
@@ -12896,7 +12914,7 @@
       </c>
       <c r="K158" s="15" t="inlineStr">
         <is>
-          <t>Design an algorithm using pseudocode or a flow chart to construct or bisect an angle with compass and straightedge; describe each step precisely; test for correctness on multiple cases; extend to algorithms for animated geometric constructions or visual proofs.</t>
+          <t>Design an algorithm (flow chart or pseudocode) that applies the triangle inequality to determine whether three given lengths can form a triangle; design an alternative algorithm to generate Pythagorean triples systematically.</t>
         </is>
       </c>
       <c r="L158" s="15" t="inlineStr">
@@ -12904,21 +12922,22 @@
           <t>strategy-MCQ</t>
         </is>
       </c>
-      <c r="M158" s="15" t="inlineStr">
-        <is>
-          <t>y9_spa_06</t>
-        </is>
-      </c>
+      <c r="M158" s="15" t="n"/>
       <c r="N158" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Strategy-MCQ matches the decision-tree algorithm-design content.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="16">
       <c r="A159" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_01</t>
+          <t>y9_spa_07</t>
         </is>
       </c>
       <c r="B159" s="15" t="n">
@@ -12926,30 +12945,30 @@
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E159" s="15" t="inlineStr">
         <is>
-          <t>analysing_statistical_reports</t>
+          <t>algorithms_for_geometric_constructions</t>
         </is>
       </c>
       <c r="F159" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_01_analysing_statistical_reports_v2.html</t>
+          <t>y9_spa_07_algorithms_for_geometric_constructions_v2.html</t>
         </is>
       </c>
       <c r="G159" s="15" t="inlineStr">
         <is>
-          <t>AC9M9ST01</t>
+          <t>AC9M9SP03</t>
         </is>
       </c>
       <c r="H159" s="15" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I159" s="15" t="inlineStr">
@@ -12959,12 +12978,12 @@
       </c>
       <c r="J159" s="15" t="inlineStr">
         <is>
-          <t>Statistical reports provide data and analysis to support conclusions and acknowledge the strength of the evidence</t>
+          <t>Trigonometric ratios are an application of the property of similarity for right-angled triangles</t>
         </is>
       </c>
       <c r="K159" s="15" t="inlineStr">
         <is>
-          <t>Analyse statistical reports from media and government sources — link claims to the displays and statistics that support them; investigate how data was obtained, sample size and representativeness; environmental and international examples including Australia–Asia trade statistics and public-opinion surveys.</t>
+          <t>Design an algorithm using pseudocode or a flow chart to construct or bisect an angle with compass and straightedge; describe each step precisely; test for correctness on multiple cases; extend to algorithms for animated geometric constructions or visual proofs.</t>
         </is>
       </c>
       <c r="L159" s="15" t="inlineStr">
@@ -12972,21 +12991,22 @@
           <t>strategy-MCQ</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>y9_spa_06</t>
+        </is>
+      </c>
       <c r="N159" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q159" s="15" t="inlineStr">
-        <is>
-          <t>Strategy-MCQ suits 'which claim is supported?' question type. Two SA CUs sit under this descriptor — emphasis here is on the reports/evidence-strength angle.</t>
-        </is>
-      </c>
+      <c r="Q159" s="15" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="16">
       <c r="A160" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_02</t>
+          <t>y9_sta_01</t>
         </is>
       </c>
       <c r="B160" s="15" t="n">
@@ -12998,26 +13018,26 @@
         </is>
       </c>
       <c r="D160" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="15" t="inlineStr">
         <is>
-          <t>sampling_methods_and_misleading_representations</t>
+          <t>analysing_statistical_reports</t>
         </is>
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_02_sampling_methods_and_misleading_representations_v2.html</t>
+          <t>y9_sta_01_analysing_statistical_reports_v2.html</t>
         </is>
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>AC9M9ST02</t>
+          <t>AC9M9ST01</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
@@ -13027,12 +13047,12 @@
       </c>
       <c r="J160" s="15" t="inlineStr">
         <is>
-          <t>Sampling methods can affect and bias the results of data collection</t>
+          <t>Statistical reports provide data and analysis to support conclusions and acknowledge the strength of the evidence</t>
         </is>
       </c>
       <c r="K160" s="15" t="inlineStr">
         <is>
-          <t>Investigate how different sampling methods and choices of representation can support a particular viewpoint or mislead the reader; analyse infographics for visual bias; consider the impact of decreased landline usage on survey data; explore potential cultural bias in reports about First Nations Australians.</t>
+          <t>Analyse statistical reports from media and government sources — link claims to the displays and statistics that support them; investigate how data was obtained, sample size and representativeness; environmental and international examples including Australia–Asia trade statistics and public-opinion surveys.</t>
         </is>
       </c>
       <c r="L160" s="15" t="inlineStr">
@@ -13040,11 +13060,7 @@
           <t>strategy-MCQ</t>
         </is>
       </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>y9_sta_01</t>
-        </is>
-      </c>
+      <c r="M160" s="15" t="n"/>
       <c r="N160" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -13052,14 +13068,14 @@
       </c>
       <c r="Q160" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 sta_02 bias work; Y9 adds the visualisation/representation angle.</t>
+          <t>Strategy-MCQ suits 'which claim is supported?' question type. Two SA CUs sit under this descriptor — emphasis here is on the reports/evidence-strength angle.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" s="16">
       <c r="A161" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_03</t>
+          <t>y9_sta_02</t>
         </is>
       </c>
       <c r="B161" s="15" t="n">
@@ -13071,26 +13087,26 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" s="15" t="inlineStr">
         <is>
-          <t>comparing_distributions_visually</t>
+          <t>sampling_methods_and_misleading_representations</t>
         </is>
       </c>
       <c r="F161" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_03_comparing_distributions_visually_v2.html</t>
+          <t>y9_sta_02_sampling_methods_and_misleading_representations_v2.html</t>
         </is>
       </c>
       <c r="G161" s="15" t="inlineStr">
         <is>
-          <t>AC9M9ST03</t>
+          <t>AC9M9ST02</t>
         </is>
       </c>
       <c r="H161" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I161" s="15" t="inlineStr">
@@ -13100,17 +13116,22 @@
       </c>
       <c r="J161" s="15" t="inlineStr">
         <is>
-          <t>Different representations of data distributions can be used to compare features such as centre, shape and spread</t>
+          <t>Sampling methods can affect and bias the results of data collection</t>
         </is>
       </c>
       <c r="K161" s="15" t="inlineStr">
         <is>
-          <t>Compare two data sets using parallel dot plots and back-to-back stem-and-leaf plots; describe similarities and differences in centre, spread and shape using terms like positive skew, negative skew, symmetric, bi-modal.</t>
+          <t>Investigate how different sampling methods and choices of representation can support a particular viewpoint or mislead the reader; analyse infographics for visual bias; consider the impact of decreased landline usage on survey data; explore potential cultural bias in reports about First Nations Australians.</t>
         </is>
       </c>
       <c r="L161" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>strategy-MCQ</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>y9_sta_01</t>
         </is>
       </c>
       <c r="N161" s="15" t="inlineStr">
@@ -13120,14 +13141,14 @@
       </c>
       <c r="Q161" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 sta_04/05 sampling and distribution work.</t>
+          <t>Builds on Y8 sta_02 bias work; Y9 adds the visualisation/representation angle.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="16">
       <c r="A162" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_04</t>
+          <t>y9_sta_03</t>
         </is>
       </c>
       <c r="B162" s="15" t="n">
@@ -13139,16 +13160,16 @@
         </is>
       </c>
       <c r="D162" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E162" s="15" t="inlineStr">
         <is>
-          <t>grouped_histograms_and_distribution_shape</t>
+          <t>comparing_distributions_visually</t>
         </is>
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_04_grouped_histograms_and_distribution_shape_v2.html</t>
+          <t>y9_sta_03_comparing_distributions_visually_v2.html</t>
         </is>
       </c>
       <c r="G162" s="15" t="inlineStr">
@@ -13158,7 +13179,7 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
@@ -13173,7 +13194,7 @@
       </c>
       <c r="K162" s="15" t="inlineStr">
         <is>
-          <t>Construct and interpret grouped histograms — age-grouped health data such as lung cancer, leukaemia, stroke; describe distribution shape and explain its connection to the relative positions of mean and median; explore Closing the Gap report data.</t>
+          <t>Compare two data sets using parallel dot plots and back-to-back stem-and-leaf plots; describe similarities and differences in centre, spread and shape using terms like positive skew, negative skew, symmetric, bi-modal.</t>
         </is>
       </c>
       <c r="L162" s="15" t="inlineStr">
@@ -13181,21 +13202,22 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M162" s="15" t="inlineStr">
-        <is>
-          <t>y9_sta_03</t>
-        </is>
-      </c>
+      <c r="M162" s="15" t="n"/>
       <c r="N162" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Builds on Y8 sta_04/05 sampling and distribution work.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="16">
       <c r="A163" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_05</t>
+          <t>y9_sta_04</t>
         </is>
       </c>
       <c r="B163" s="15" t="n">
@@ -13207,26 +13229,26 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E163" s="15" t="inlineStr">
         <is>
-          <t>choosing_the_right_data_display</t>
+          <t>grouped_histograms_and_distribution_shape</t>
         </is>
       </c>
       <c r="F163" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_05_choosing_the_right_data_display_v2.html</t>
+          <t>y9_sta_04_grouped_histograms_and_distribution_shape_v2.html</t>
         </is>
       </c>
       <c r="G163" s="15" t="inlineStr">
         <is>
-          <t>AC9M9ST04</t>
+          <t>AC9M9ST03</t>
         </is>
       </c>
       <c r="H163" s="15" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I163" s="15" t="inlineStr">
@@ -13241,17 +13263,17 @@
       </c>
       <c r="K163" s="15" t="inlineStr">
         <is>
-          <t>Match the data display to the data type — categorical (bar chart, stacked bar chart) vs numerical (histogram, dot plot, stem-and-leaf); compare displays of the same data using mean, median and range; critique infographic choices for the statistical questions they purport to answer.</t>
+          <t>Construct and interpret grouped histograms — age-grouped health data such as lung cancer, leukaemia, stroke; describe distribution shape and explain its connection to the relative positions of mean and median; explore Closing the Gap report data.</t>
         </is>
       </c>
       <c r="L163" s="15" t="inlineStr">
         <is>
-          <t>matching</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M163" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_04</t>
+          <t>y9_sta_03</t>
         </is>
       </c>
       <c r="N163" s="15" t="inlineStr">
@@ -13259,16 +13281,12 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q163" s="15" t="inlineStr">
-        <is>
-          <t>Matching practice — display ↔ data type ↔ purpose pairings.</t>
-        </is>
-      </c>
+      <c r="Q163" s="15" t="n"/>
     </row>
     <row r="164" ht="15" customHeight="1" s="16">
       <c r="A164" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_06</t>
+          <t>y9_sta_05</t>
         </is>
       </c>
       <c r="B164" s="15" t="n">
@@ -13280,21 +13298,21 @@
         </is>
       </c>
       <c r="D164" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E164" s="15" t="inlineStr">
         <is>
-          <t>full_statistical_investigation_with_secondary_data</t>
+          <t>choosing_the_right_data_display</t>
         </is>
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_06_full_statistical_investigation_with_secondary_data_v2.html</t>
+          <t>y9_sta_05_choosing_the_right_data_display_v2.html</t>
         </is>
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>AC9M9ST05</t>
+          <t>AC9M9ST04</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
@@ -13309,22 +13327,22 @@
       </c>
       <c r="J164" s="15" t="inlineStr">
         <is>
-          <t>Statistical reports provide data and analysis to support conclusions and acknowledge the strength of the evidence</t>
+          <t>Different representations of data distributions can be used to compare features such as centre, shape and spread</t>
         </is>
       </c>
       <c r="K164" s="15" t="inlineStr">
         <is>
-          <t>Plan and conduct a full statistical investigation using primary or secondary data sources such as the ABS — pose a question, collect or extract data, choose displays, analyse, report findings with explicit acknowledgement of uncertainty; investigation contexts include consumer spending habits, tropical-fruit plantation siting, and reconciliation data.</t>
+          <t>Match the data display to the data type — categorical (bar chart, stacked bar chart) vs numerical (histogram, dot plot, stem-and-leaf); compare displays of the same data using mean, median and range; critique infographic choices for the statistical questions they purport to answer.</t>
         </is>
       </c>
       <c r="L164" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>matching</t>
         </is>
       </c>
       <c r="M164" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_05</t>
+          <t>y9_sta_04</t>
         </is>
       </c>
       <c r="N164" s="15" t="inlineStr">
@@ -13334,14 +13352,14 @@
       </c>
       <c r="Q164" s="15" t="inlineStr">
         <is>
-          <t>Capstone — extends Y7 sta_05 and Y8 sta_06 with explicit secondary-source work.</t>
+          <t>Matching practice — display ↔ data type ↔ purpose pairings.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" s="16">
       <c r="A165" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_01</t>
+          <t>y9_sta_06</t>
         </is>
       </c>
       <c r="B165" s="15" t="n">
@@ -13349,30 +13367,30 @@
       </c>
       <c r="C165" s="15" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E165" s="15" t="inlineStr">
         <is>
-          <t>two_step_compound_events</t>
+          <t>full_statistical_investigation_with_secondary_data</t>
         </is>
       </c>
       <c r="F165" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_01_two_step_compound_events_v2.html</t>
+          <t>y9_sta_06_full_statistical_investigation_with_secondary_data_v2.html</t>
         </is>
       </c>
       <c r="G165" s="15" t="inlineStr">
         <is>
-          <t>AC9M9P01</t>
+          <t>AC9M9ST05</t>
         </is>
       </c>
       <c r="H165" s="15" t="inlineStr">
         <is>
-          <t>1,2,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I165" s="15" t="inlineStr">
@@ -13382,17 +13400,22 @@
       </c>
       <c r="J165" s="15" t="inlineStr">
         <is>
-          <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
+          <t>Statistical reports provide data and analysis to support conclusions and acknowledge the strength of the evidence</t>
         </is>
       </c>
       <c r="K165" s="15" t="inlineStr">
         <is>
-          <t>Use lists and arrays to record outcomes of two-step compound experiments — the Heads and Tails game, drawing two team leaders from a class; calculate probabilities by counting favourable outcomes over total outcomes.</t>
+          <t>Plan and conduct a full statistical investigation using primary or secondary data sources such as the ABS — pose a question, collect or extract data, choose displays, analyse, report findings with explicit acknowledgement of uncertainty; investigation contexts include consumer spending habits, tropical-fruit plantation siting, and reconciliation data.</t>
         </is>
       </c>
       <c r="L165" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>y9_sta_05</t>
         </is>
       </c>
       <c r="N165" s="15" t="inlineStr">
@@ -13402,14 +13425,14 @@
       </c>
       <c r="Q165" s="15" t="inlineStr">
         <is>
-          <t>Extends Y8 pro_02/03 two-event work; Y9 emphasis is on the systematic listing of compound outcomes.</t>
+          <t>Capstone — extends Y7 sta_05 and Y8 sta_06 with explicit secondary-source work.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" s="16">
       <c r="A166" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_02</t>
+          <t>y9_pro_01</t>
         </is>
       </c>
       <c r="B166" s="15" t="n">
@@ -13421,16 +13444,16 @@
         </is>
       </c>
       <c r="D166" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" s="15" t="inlineStr">
         <is>
-          <t>tree_diagrams_with_and_without_replacement</t>
+          <t>two_step_compound_events</t>
         </is>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_02_tree_diagrams_with_and_without_replacement_v2.html</t>
+          <t>y9_pro_01_two_step_compound_events_v2.html</t>
         </is>
       </c>
       <c r="G166" s="15" t="inlineStr">
@@ -13440,7 +13463,7 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
@@ -13455,7 +13478,7 @@
       </c>
       <c r="K166" s="15" t="inlineStr">
         <is>
-          <t>Use tree diagrams to represent two- and three-step compound events; contrast experiments with and without replacement (e.g. drawing 3 cards from a deck); multiply probabilities along each path and sum across paths for the target event.</t>
+          <t>Use lists and arrays to record outcomes of two-step compound experiments — the Heads and Tails game, drawing two team leaders from a class; calculate probabilities by counting favourable outcomes over total outcomes.</t>
         </is>
       </c>
       <c r="L166" s="15" t="inlineStr">
@@ -13463,11 +13486,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M166" s="15" t="inlineStr">
-        <is>
-          <t>y9_pro_01</t>
-        </is>
-      </c>
+      <c r="M166" s="15" t="n"/>
       <c r="N166" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -13475,14 +13494,14 @@
       </c>
       <c r="Q166" s="15" t="inlineStr">
         <is>
-          <t>With/without replacement is the watershed concept — introduces conditional probability informally.</t>
+          <t>Extends Y8 pro_02/03 two-event work; Y9 emphasis is on the systematic listing of compound outcomes.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" s="16">
       <c r="A167" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_03</t>
+          <t>y9_pro_02</t>
         </is>
       </c>
       <c r="B167" s="15" t="n">
@@ -13494,26 +13513,26 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" s="15" t="inlineStr">
         <is>
-          <t>relative_frequency_for_and_or_events</t>
+          <t>tree_diagrams_with_and_without_replacement</t>
         </is>
       </c>
       <c r="F167" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_03_relative_frequency_for_and_or_events_v2.html</t>
+          <t>y9_pro_02_tree_diagrams_with_and_without_replacement_v2.html</t>
         </is>
       </c>
       <c r="G167" s="15" t="inlineStr">
         <is>
-          <t>AC9M9P02</t>
+          <t>AC9M9P01</t>
         </is>
       </c>
       <c r="H167" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I167" s="15" t="inlineStr">
@@ -13523,12 +13542,12 @@
       </c>
       <c r="J167" s="15" t="inlineStr">
         <is>
-          <t>Theoretical probabilities are based on the characteristics of an experiment and can be used to predict relative frequencies of experimental data</t>
+          <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
         </is>
       </c>
       <c r="K167" s="15" t="inlineStr">
         <is>
-          <t>Use relative frequencies from historical or experimental data to estimate probabilities of events; use Venn diagrams and two-way tables to handle events involving 'and', inclusive 'or' (A or B or both), and exclusive 'or' (A or B but not both).</t>
+          <t>Use tree diagrams to represent two- and three-step compound events; contrast experiments with and without replacement (e.g. drawing 3 cards from a deck); multiply probabilities along each path and sum across paths for the target event.</t>
         </is>
       </c>
       <c r="L167" s="15" t="inlineStr">
@@ -13538,19 +13557,24 @@
       </c>
       <c r="M167" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_02</t>
+          <t>y9_pro_01</t>
         </is>
       </c>
       <c r="N167" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>With/without replacement is the watershed concept — introduces conditional probability informally.</t>
         </is>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="16">
       <c r="A168" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_04</t>
+          <t>y9_pro_03</t>
         </is>
       </c>
       <c r="B168" s="15" t="n">
@@ -13562,26 +13586,26 @@
         </is>
       </c>
       <c r="D168" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E168" s="15" t="inlineStr">
         <is>
-          <t>simulating_compound_events_with_replacement_comparison</t>
+          <t>relative_frequency_for_and_or_events</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_04_simulating_compound_events_with_replacement_comparison_v2.html</t>
+          <t>y9_pro_03_relative_frequency_for_and_or_events_v2.html</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>AC9M9P03</t>
+          <t>AC9M9P02</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
@@ -13591,22 +13615,22 @@
       </c>
       <c r="J168" s="15" t="inlineStr">
         <is>
-          <t>The probability of compound events is related to the probability of the associated simple events and can be calculated in the context of the experiment</t>
+          <t>Theoretical probabilities are based on the characteristics of an experiment and can be used to predict relative frequencies of experimental data</t>
         </is>
       </c>
       <c r="K168" s="15" t="inlineStr">
         <is>
-          <t>Use digital random-number tools to simulate compound events; compare experimental probability with theoretical predictions; contrast results from experiments that differ only by being with or without replacement; explore the First Nations Gorri game from across Australia as a repeated-trial context.</t>
+          <t>Use relative frequencies from historical or experimental data to estimate probabilities of events; use Venn diagrams and two-way tables to handle events involving 'and', inclusive 'or' (A or B or both), and exclusive 'or' (A or B but not both).</t>
         </is>
       </c>
       <c r="L168" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M168" s="15" t="inlineStr">
         <is>
-          <t>y9_pro_02,y9_pro_03</t>
+          <t>y9_pro_02</t>
         </is>
       </c>
       <c r="N168" s="15" t="inlineStr">
@@ -13614,47 +13638,43 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q168" s="15" t="inlineStr">
-        <is>
-          <t>Builds directly on Y8 pro_04 simulation work; Y9 adds the with/without-replacement contrast.</t>
-        </is>
-      </c>
+      <c r="Q168" s="15" t="n"/>
     </row>
     <row r="169" ht="15" customHeight="1" s="16">
       <c r="A169" s="15" t="inlineStr">
         <is>
-          <t>y10_num_01</t>
+          <t>y9_pro_04</t>
         </is>
       </c>
       <c r="B169" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C169" s="15" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E169" s="15" t="inlineStr">
         <is>
-          <t>truncation_and_rounding_effects</t>
+          <t>simulating_compound_events_with_replacement_comparison</t>
         </is>
       </c>
       <c r="F169" s="15" t="inlineStr">
         <is>
-          <t>y10_num_01_truncation_and_rounding_effects_v2.html</t>
+          <t>y9_pro_04_simulating_compound_events_with_replacement_comparison_v2.html</t>
         </is>
       </c>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>AC9M10N01</t>
+          <t>AC9M9P03</t>
         </is>
       </c>
       <c r="H169" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I169" s="15" t="inlineStr">
@@ -13664,17 +13684,22 @@
       </c>
       <c r="J169" s="15" t="inlineStr">
         <is>
-          <t>Using approximations rather than exact values affects the accuracy of results in both single and multiple calculations</t>
+          <t>The probability of compound events is related to the probability of the associated simple events and can be calculated in the context of the experiment</t>
         </is>
       </c>
       <c r="K169" s="15" t="inlineStr">
         <is>
-          <t>Compare the effect of truncation versus rounding on a single calculation; recognise that exact form (surds, π, fractions) preserves accuracy where decimal approximations introduce error; identify the interval between consecutive integers containing a given irrational.</t>
+          <t>Use digital random-number tools to simulate compound events; compare experimental probability with theoretical predictions; contrast results from experiments that differ only by being with or without replacement; explore the First Nations Gorri game from across Australia as a repeated-trial context.</t>
         </is>
       </c>
       <c r="L169" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>y9_pro_02,y9_pro_03</t>
         </is>
       </c>
       <c r="N169" s="15" t="inlineStr">
@@ -13684,14 +13709,14 @@
       </c>
       <c r="Q169" s="15" t="inlineStr">
         <is>
-          <t>Foundation lesson for N01 — sets up the exact-versus-approximate distinction that drives the compound-shapes and finance work in y10_num_02 and y10_alg_16 (compound interest).</t>
+          <t>Builds directly on Y8 pro_04 simulation work; Y9 adds the with/without-replacement contrast.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="16">
       <c r="A170" s="15" t="inlineStr">
         <is>
-          <t>y10_num_02</t>
+          <t>y10_num_01</t>
         </is>
       </c>
       <c r="B170" s="15" t="n">
@@ -13703,31 +13728,31 @@
         </is>
       </c>
       <c r="D170" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" s="15" t="inlineStr">
         <is>
-          <t>compounding_approximation_in_compound_calculations</t>
+          <t>truncation_and_rounding_effects</t>
         </is>
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>y10_num_02_compounding_approximation_in_compound_calculations_v2.html</t>
+          <t>y10_num_01_truncation_and_rounding_effects_v2.html</t>
         </is>
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>AC9M10N01, AC9M10M04</t>
+          <t>AC9M10N01</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>2 (N01); 3 (M04)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>Strict + cross-tag</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="J170" s="15" t="inlineStr">
@@ -13737,19 +13762,15 @@
       </c>
       <c r="K170" s="15" t="inlineStr">
         <is>
-          <t>Investigate how rounding errors compound across multiple calculations — area of compound shapes involving circles (π approximations), surface area and volume of compound objects, repeated simple-interest calculations where each cycle's rounding shifts the final balance; quantify the discrepancy from the exact-form answer.</t>
+          <t>Compare the effect of truncation versus rounding on a single calculation; recognise that exact form (surds, π, fractions) preserves accuracy where decimal approximations introduce error; identify the interval between consecutive integers containing a given irrational.</t>
         </is>
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>y10_num_01</t>
-        </is>
-      </c>
+          <t>auto-marked</t>
+        </is>
+      </c>
+      <c r="M170" s="15" t="n"/>
       <c r="N170" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -13757,14 +13778,14 @@
       </c>
       <c r="Q170" s="15" t="inlineStr">
         <is>
-          <t>Dual-tagged: N01 e2 (Number framing — effect of approximations) and M04 e3 (Measurement framing — compounding errors in financial calculations). Mirrors the y9_mea_04 (M02+A01) and y8_num_11 (N05+M05) dual-tag pattern. Watershed habit for Y10 — exact form discipline carried over from y9_num_02.</t>
+          <t>Foundation lesson for N01 — sets up the exact-versus-approximate distinction that drives the compound-shapes and finance work in y10_num_02 and y10_alg_16 (compound interest).</t>
         </is>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" s="16">
       <c r="A171" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_01</t>
+          <t>y10_num_02</t>
         </is>
       </c>
       <c r="B171" s="15" t="n">
@@ -13772,50 +13793,55 @@
       </c>
       <c r="C171" s="15" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" s="15" t="inlineStr">
         <is>
-          <t>expanding_special_products_and_non_monic</t>
+          <t>compounding_approximation_in_compound_calculations</t>
         </is>
       </c>
       <c r="F171" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_01_expanding_special_products_and_non_monic_v2.html</t>
+          <t>y10_num_02_compounding_approximation_in_compound_calculations_v2.html</t>
         </is>
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>AC9M10A01</t>
+          <t>AC9M10N01, AC9M10M04</t>
         </is>
       </c>
       <c r="H171" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 (N01); 3 (M04)</t>
         </is>
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Strict + cross-tag</t>
         </is>
       </c>
       <c r="J171" s="15" t="inlineStr">
         <is>
-          <t>Relationships between variables can be described and modelled by linear, quadratic and exponential functions applied in many contexts including financial ones</t>
+          <t>Using approximations rather than exact values affects the accuracy of results in both single and multiple calculations</t>
         </is>
       </c>
       <c r="K171" s="15" t="inlineStr">
         <is>
-          <t>Expand binomial products of the form (ax + b)(cx + d) using the area model and the distributive property; consolidate the perfect-square patterns (a + b)² = a² + 2ab + b² and (a − b)² = a² − 2ab + b², and the difference-of-squares (a + b)(a − b) = a² − b²; identify when each special pattern applies.</t>
+          <t>Investigate how rounding errors compound across multiple calculations — area of compound shapes involving circles (π approximations), surface area and volume of compound objects, repeated simple-interest calculations where each cycle's rounding shifts the final balance; quantify the discrepancy from the exact-form answer.</t>
         </is>
       </c>
       <c r="L171" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>y10_num_01</t>
         </is>
       </c>
       <c r="N171" s="15" t="inlineStr">
@@ -13825,14 +13851,14 @@
       </c>
       <c r="Q171" s="15" t="inlineStr">
         <is>
-          <t>Builds directly on Y9 alg_03 (monic binomial products) — Y10 extends to non-monic and formalises the three special products. Area model justification carries through.</t>
+          <t>Dual-tagged: N01 e2 (Number framing — effect of approximations) and M04 e3 (Measurement framing — compounding errors in financial calculations). Mirrors the y9_mea_04 (M02+A01) and y8_num_11 (N05+M05) dual-tag pattern. Watershed habit for Y10 — exact form discipline carried over from y9_num_02.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="16">
       <c r="A172" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_02</t>
+          <t>y10_alg_01</t>
         </is>
       </c>
       <c r="B172" s="15" t="n">
@@ -13844,16 +13870,16 @@
         </is>
       </c>
       <c r="D172" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>factorising_quadratics_special_and_non_monic</t>
+          <t>expanding_special_products_and_non_monic</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_02_factorising_quadratics_special_and_non_monic_v2.html</t>
+          <t>y10_alg_01_expanding_special_products_and_non_monic_v2.html</t>
         </is>
       </c>
       <c r="G172" s="15" t="inlineStr">
@@ -13878,7 +13904,7 @@
       </c>
       <c r="K172" s="15" t="inlineStr">
         <is>
-          <t>Factorise by extracting the highest common factor first; factorise difference-of-squares a² − b² = (a + b)(a − b); factorise perfect-square trinomials; factorise non-monic quadratics ax² + bx + c using the AC (split-the-middle) method; verify every factorisation by re-expanding.</t>
+          <t>Expand binomial products of the form (ax + b)(cx + d) using the area model and the distributive property; consolidate the perfect-square patterns (a + b)² = a² + 2ab + b² and (a − b)² = a² − 2ab + b², and the difference-of-squares (a + b)(a − b) = a² − b²; identify when each special pattern applies.</t>
         </is>
       </c>
       <c r="L172" s="15" t="inlineStr">
@@ -13886,11 +13912,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M172" s="15" t="inlineStr">
-        <is>
-          <t>y10_alg_01</t>
-        </is>
-      </c>
+      <c r="M172" s="15" t="n"/>
       <c r="N172" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -13898,14 +13920,14 @@
       </c>
       <c r="Q172" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: AC method is the threshold technique for non-monic factorising. HCF-first habit prevents over-complicated splits.</t>
+          <t>Builds directly on Y9 alg_03 (monic binomial products) — Y10 extends to non-monic and formalises the three special products. Area model justification carries through.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="16">
       <c r="A173" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_03</t>
+          <t>y10_alg_02</t>
         </is>
       </c>
       <c r="B173" s="15" t="n">
@@ -13917,16 +13939,16 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" s="15" t="inlineStr">
         <is>
-          <t>completing_the_square</t>
+          <t>factorising_quadratics_special_and_non_monic</t>
         </is>
       </c>
       <c r="F173" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_03_completing_the_square_v2.html</t>
+          <t>y10_alg_02_factorising_quadratics_special_and_non_monic_v2.html</t>
         </is>
       </c>
       <c r="G173" s="15" t="inlineStr">
@@ -13951,7 +13973,7 @@
       </c>
       <c r="K173" s="15" t="inlineStr">
         <is>
-          <t>Rewrite x² + bx + c in completed-square form (x + b/2)² + (c − b²/4); extend to ax² + bx + c by first factorising out a; connect to the perfect-square expansion pattern; interpret the completed-square form geometrically as the turning point of the related parabola y = a(x − h)² + k.</t>
+          <t>Factorise by extracting the highest common factor first; factorise difference-of-squares a² − b² = (a + b)(a − b); factorise perfect-square trinomials; factorise non-monic quadratics ax² + bx + c using the AC (split-the-middle) method; verify every factorisation by re-expanding.</t>
         </is>
       </c>
       <c r="L173" s="15" t="inlineStr">
@@ -13961,7 +13983,7 @@
       </c>
       <c r="M173" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_01,y10_alg_02</t>
+          <t>y10_alg_01</t>
         </is>
       </c>
       <c r="N173" s="15" t="inlineStr">
@@ -13971,14 +13993,14 @@
       </c>
       <c r="Q173" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: completing the square is the central manipulation that unlocks the quadratic formula derivation and the turning-point form. Geometric interpretation links back to y9_alg_16 transformations of quadratics.</t>
+          <t>Watershed lesson: AC method is the threshold technique for non-monic factorising. HCF-first habit prevents over-complicated splits.</t>
         </is>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" s="16">
       <c r="A174" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_04</t>
+          <t>y10_alg_03</t>
         </is>
       </c>
       <c r="B174" s="15" t="n">
@@ -13990,16 +14012,16 @@
         </is>
       </c>
       <c r="D174" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E174" s="15" t="inlineStr">
         <is>
-          <t>solving_quadratics_and_quadratic_formula</t>
+          <t>completing_the_square</t>
         </is>
       </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_04_solving_quadratics_and_quadratic_formula_v2.html</t>
+          <t>y10_alg_03_completing_the_square_v2.html</t>
         </is>
       </c>
       <c r="G174" s="15" t="inlineStr">
@@ -14014,7 +14036,7 @@
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>Implied</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="J174" s="15" t="inlineStr">
@@ -14024,7 +14046,7 @@
       </c>
       <c r="K174" s="15" t="inlineStr">
         <is>
-          <t>Solve quadratic equations algebraically by factorising, by completing the square, and using the quadratic formula x = (−b ± √(b² − 4ac))/(2a); derive the formula from the completed-square form; recognise when the discriminant indicates no real solutions; choose an efficient method given the form of the equation.</t>
+          <t>Rewrite x² + bx + c in completed-square form (x + b/2)² + (c − b²/4); extend to ax² + bx + c by first factorising out a; connect to the perfect-square expansion pattern; interpret the completed-square form geometrically as the turning point of the related parabola y = a(x − h)² + k.</t>
         </is>
       </c>
       <c r="L174" s="15" t="inlineStr">
@@ -14034,7 +14056,7 @@
       </c>
       <c r="M174" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_02,y10_alg_03</t>
+          <t>y10_alg_01,y10_alg_02</t>
         </is>
       </c>
       <c r="N174" s="15" t="inlineStr">
@@ -14044,14 +14066,14 @@
       </c>
       <c r="Q174" s="15" t="inlineStr">
         <is>
-          <t>Implied: AC9 descriptor says 'solve equations algebraically' but no elaboration explicitly names the quadratic formula. Standard SA Y10 / Y10A content. Watershed lesson — formula derivation gives meaning rather than mystery.</t>
+          <t>Watershed lesson: completing the square is the central manipulation that unlocks the quadratic formula derivation and the turning-point form. Geometric interpretation links back to y9_alg_16 transformations of quadratics.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="16">
       <c r="A175" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_05</t>
+          <t>y10_alg_04</t>
         </is>
       </c>
       <c r="B175" s="15" t="n">
@@ -14063,16 +14085,16 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E175" s="15" t="inlineStr">
         <is>
-          <t>simplifying_with_negative_exponents_and_variables</t>
+          <t>solving_quadratics_and_quadratic_formula</t>
         </is>
       </c>
       <c r="F175" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_05_simplifying_with_negative_exponents_and_variables_v2.html</t>
+          <t>y10_alg_04_solving_quadratics_and_quadratic_formula_v2.html</t>
         </is>
       </c>
       <c r="G175" s="15" t="inlineStr">
@@ -14082,12 +14104,12 @@
       </c>
       <c r="H175" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Implied</t>
         </is>
       </c>
       <c r="J175" s="15" t="inlineStr">
@@ -14097,7 +14119,7 @@
       </c>
       <c r="K175" s="15" t="inlineStr">
         <is>
-          <t>Apply exponent laws to algebraic expressions involving both positive and negative integer exponents, e.g. (3x²y⁻¹)² ÷ (6x⁻¹y²); rewrite expressions without negative exponents using a⁻ⁿ = 1/aⁿ; solve simple equations of the form aⁿ = b algebraically using the exponent laws.</t>
+          <t>Solve quadratic equations algebraically by factorising, by completing the square, and using the quadratic formula x = (−b ± √(b² − 4ac))/(2a); derive the formula from the completed-square form; recognise when the discriminant indicates no real solutions; choose an efficient method given the form of the equation.</t>
         </is>
       </c>
       <c r="L175" s="15" t="inlineStr">
@@ -14105,6 +14127,11 @@
           <t>auto-marked</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>y10_alg_02,y10_alg_03</t>
+        </is>
+      </c>
       <c r="N175" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -14112,14 +14139,14 @@
       </c>
       <c r="Q175" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y9 alg_01 (negative exponents on numerals) and alg_02 (exponent laws with variables) — Y10 extends to multi-variable expressions with negative exponents.</t>
+          <t>Implied: AC9 descriptor says 'solve equations algebraically' but no elaboration explicitly names the quadratic formula. Standard SA Y10 / Y10A content. Watershed lesson — formula derivation gives meaning rather than mystery.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" s="16">
       <c r="A176" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_06</t>
+          <t>y10_alg_05</t>
         </is>
       </c>
       <c r="B176" s="15" t="n">
@@ -14131,26 +14158,26 @@
         </is>
       </c>
       <c r="D176" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E176" s="15" t="inlineStr">
         <is>
-          <t>solving_simultaneous_equations_graphically</t>
+          <t>simplifying_with_negative_exponents_and_variables</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_06_solving_simultaneous_equations_graphically_v2.html</t>
+          <t>y10_alg_05_simplifying_with_negative_exponents_and_variables_v2.html</t>
         </is>
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>AC9M10A02</t>
+          <t>AC9M10A01</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
@@ -14165,7 +14192,7 @@
       </c>
       <c r="K176" s="15" t="inlineStr">
         <is>
-          <t>Solve a pair of simultaneous linear equations by graphing both lines and identifying the intersection point; interpret the intersection in context (e.g. break-even point, point at which two quotes are equal); recognise the three cases — one solution, no solution (parallel lines), infinite solutions (coincident lines).</t>
+          <t>Apply exponent laws to algebraic expressions involving both positive and negative integer exponents, e.g. (3x²y⁻¹)² ÷ (6x⁻¹y²); rewrite expressions without negative exponents using a⁻ⁿ = 1/aⁿ; solve simple equations of the form aⁿ = b algebraically using the exponent laws.</t>
         </is>
       </c>
       <c r="L176" s="15" t="inlineStr">
@@ -14180,14 +14207,14 @@
       </c>
       <c r="Q176" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: graphical method is the conceptual anchor for the algebraic methods in y10_alg_07. Builds on Y9 alg_06 (gradient) and alg_15 (slope-intercept form).</t>
+          <t>Builds on Y9 alg_01 (negative exponents on numerals) and alg_02 (exponent laws with variables) — Y10 extends to multi-variable expressions with negative exponents.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" s="16">
       <c r="A177" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_07</t>
+          <t>y10_alg_06</t>
         </is>
       </c>
       <c r="B177" s="15" t="n">
@@ -14199,16 +14226,16 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E177" s="15" t="inlineStr">
         <is>
-          <t>solving_simultaneous_equations_algebraically</t>
+          <t>solving_simultaneous_equations_graphically</t>
         </is>
       </c>
       <c r="F177" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_07_solving_simultaneous_equations_algebraically_v2.html</t>
+          <t>y10_alg_06_solving_simultaneous_equations_graphically_v2.html</t>
         </is>
       </c>
       <c r="G177" s="15" t="inlineStr">
@@ -14218,7 +14245,7 @@
       </c>
       <c r="H177" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I177" s="15" t="inlineStr">
@@ -14233,7 +14260,7 @@
       </c>
       <c r="K177" s="15" t="inlineStr">
         <is>
-          <t>Solve simultaneous linear equations using the substitution method and the elimination method; choose between methods based on the form of the equations; verify each solution by substitution into both equations; relate the algebraic solution to the graphical intersection point.</t>
+          <t>Solve a pair of simultaneous linear equations by graphing both lines and identifying the intersection point; interpret the intersection in context (e.g. break-even point, point at which two quotes are equal); recognise the three cases — one solution, no solution (parallel lines), infinite solutions (coincident lines).</t>
         </is>
       </c>
       <c r="L177" s="15" t="inlineStr">
@@ -14241,11 +14268,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M177" s="15" t="inlineStr">
-        <is>
-          <t>y10_alg_06</t>
-        </is>
-      </c>
+      <c r="M177" s="15" t="n"/>
       <c r="N177" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -14253,14 +14276,14 @@
       </c>
       <c r="Q177" s="15" t="inlineStr">
         <is>
-          <t>Substitution method extends Y9 equation-solving techniques. Elimination is the new manoeuvre — flag for I Do worked example.</t>
+          <t>Watershed lesson: graphical method is the conceptual anchor for the algebraic methods in y10_alg_07. Builds on Y9 alg_06 (gradient) and alg_15 (slope-intercept form).</t>
         </is>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" s="16">
       <c r="A178" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_08</t>
+          <t>y10_alg_07</t>
         </is>
       </c>
       <c r="B178" s="15" t="n">
@@ -14272,16 +14295,16 @@
         </is>
       </c>
       <c r="D178" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E178" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_simultaneous_equations</t>
+          <t>solving_simultaneous_equations_algebraically</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_08_modelling_with_simultaneous_equations_v2.html</t>
+          <t>y10_alg_07_solving_simultaneous_equations_algebraically_v2.html</t>
         </is>
       </c>
       <c r="G178" s="15" t="inlineStr">
@@ -14291,7 +14314,7 @@
       </c>
       <c r="H178" s="15" t="inlineStr">
         <is>
-          <t>1,2,6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I178" s="15" t="inlineStr">
@@ -14306,17 +14329,17 @@
       </c>
       <c r="K178" s="15" t="inlineStr">
         <is>
-          <t>Model practical situations with simultaneous equations — comparing two job quotes (fixed call-out plus hourly rate), profit/loss break-even, mixing two priced items to a total budget; communicate solutions in everyday language such as break-even point or point-to-change-providers; explore First Nations Australian children's instructive games (e.g. Weme from the Warlpiri Peoples) and their connection to strategic reasoning.</t>
+          <t>Solve simultaneous linear equations using the substitution method and the elimination method; choose between methods based on the form of the equations; verify each solution by substitution into both equations; relate the algebraic solution to the graphical intersection point.</t>
         </is>
       </c>
       <c r="L178" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M178" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_07</t>
+          <t>y10_alg_06</t>
         </is>
       </c>
       <c r="N178" s="15" t="inlineStr">
@@ -14326,14 +14349,14 @@
       </c>
       <c r="Q178" s="15" t="inlineStr">
         <is>
-          <t>Finance context per house preference. Captures e1 (contextual lin eq), e2 (interpretation), and e6 (First Nations games).</t>
+          <t>Substitution method extends Y9 equation-solving techniques. Elimination is the new manoeuvre — flag for I Do worked example.</t>
         </is>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="16">
       <c r="A179" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_09</t>
+          <t>y10_alg_08</t>
         </is>
       </c>
       <c r="B179" s="15" t="n">
@@ -14345,16 +14368,16 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E179" s="15" t="inlineStr">
         <is>
-          <t>graphing_linear_inequalities_in_two_variables</t>
+          <t>modelling_with_simultaneous_equations</t>
         </is>
       </c>
       <c r="F179" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_09_graphing_linear_inequalities_in_two_variables_v2.html</t>
+          <t>y10_alg_08_modelling_with_simultaneous_equations_v2.html</t>
         </is>
       </c>
       <c r="G179" s="15" t="inlineStr">
@@ -14364,7 +14387,7 @@
       </c>
       <c r="H179" s="15" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>1,2,6</t>
         </is>
       </c>
       <c r="I179" s="15" t="inlineStr">
@@ -14379,17 +14402,17 @@
       </c>
       <c r="K179" s="15" t="inlineStr">
         <is>
-          <t>Graph the solution region for a single linear inequality in two variables (e.g. 2x + 3y &lt; 24); use a test point such as (0, 0) to determine which side of the line to shade; recognise the convention of solid versus dashed boundary lines for ≤/≥ versus &lt;/&gt;; test whether a given point satisfies an inequality (extending to non-linear cases like 2y &lt; x²).</t>
+          <t>Model practical situations with simultaneous equations — comparing two job quotes (fixed call-out plus hourly rate), profit/loss break-even, mixing two priced items to a total budget; communicate solutions in everyday language such as break-even point or point-to-change-providers; explore First Nations Australian children's instructive games (e.g. Weme from the Warlpiri Peoples) and their connection to strategic reasoning.</t>
         </is>
       </c>
       <c r="L179" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M179" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_06</t>
+          <t>y10_alg_07</t>
         </is>
       </c>
       <c r="N179" s="15" t="inlineStr">
@@ -14399,14 +14422,14 @@
       </c>
       <c r="Q179" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 alg_06 (single-variable inequality regions); Y10 extends to two variables and shading conventions.</t>
+          <t>Finance context per house preference. Captures e1 (contextual lin eq), e2 (interpretation), and e6 (First Nations games).</t>
         </is>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" s="16">
       <c r="A180" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_10</t>
+          <t>y10_alg_09</t>
         </is>
       </c>
       <c r="B180" s="15" t="n">
@@ -14418,16 +14441,16 @@
         </is>
       </c>
       <c r="D180" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E180" s="15" t="inlineStr">
         <is>
-          <t>systems_of_inequalities_and_feasible_regions</t>
+          <t>graphing_linear_inequalities_in_two_variables</t>
         </is>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_10_systems_of_inequalities_and_feasible_regions_v2.html</t>
+          <t>y10_alg_09_graphing_linear_inequalities_in_two_variables_v2.html</t>
         </is>
       </c>
       <c r="G180" s="15" t="inlineStr">
@@ -14437,7 +14460,7 @@
       </c>
       <c r="H180" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="I180" s="15" t="inlineStr">
@@ -14452,7 +14475,7 @@
       </c>
       <c r="K180" s="15" t="inlineStr">
         <is>
-          <t>Graph systems of two or more linear inequalities and identify the feasible region; find all integer solutions in the feasible region for budget problems such as combinations of movie trips at $12 each and ice-skating sessions at $21 each with an entertainment budget of $150 (12m + 21s ≤ 150); list integer solutions and interpret in context.</t>
+          <t>Graph the solution region for a single linear inequality in two variables (e.g. 2x + 3y &lt; 24); use a test point such as (0, 0) to determine which side of the line to shade; recognise the convention of solid versus dashed boundary lines for ≤/≥ versus &lt;/&gt;; test whether a given point satisfies an inequality (extending to non-linear cases like 2y &lt; x²).</t>
         </is>
       </c>
       <c r="L180" s="15" t="inlineStr">
@@ -14462,7 +14485,7 @@
       </c>
       <c r="M180" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_09</t>
+          <t>y10_alg_06</t>
         </is>
       </c>
       <c r="N180" s="15" t="inlineStr">
@@ -14472,14 +14495,14 @@
       </c>
       <c r="Q180" s="15" t="inlineStr">
         <is>
-          <t>Finance context per house preference. Foundation for later linear programming work in senior years.</t>
+          <t>Builds on Y8 alg_06 (single-variable inequality regions); Y10 extends to two variables and shading conventions.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="16">
       <c r="A181" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_11</t>
+          <t>y10_alg_10</t>
         </is>
       </c>
       <c r="B181" s="15" t="n">
@@ -14491,26 +14514,26 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E181" s="15" t="inlineStr">
         <is>
-          <t>introducing_exponential_functions</t>
+          <t>systems_of_inequalities_and_feasible_regions</t>
         </is>
       </c>
       <c r="F181" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_11_introducing_exponential_functions_v2.html</t>
+          <t>y10_alg_10_systems_of_inequalities_and_feasible_regions_v2.html</t>
         </is>
       </c>
       <c r="G181" s="15" t="inlineStr">
         <is>
-          <t>AC9M10A03</t>
+          <t>AC9M10A02</t>
         </is>
       </c>
       <c r="H181" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I181" s="15" t="inlineStr">
@@ -14525,7 +14548,7 @@
       </c>
       <c r="K181" s="15" t="inlineStr">
         <is>
-          <t>Recognise an exponential relation from a table of values by checking whether the ratio between consecutive values of the dependent variable is constant; contrast with the constant first-difference diagnostic for linear and constant second-difference for quadratic; plot y = aˣ for a = 2, 3, ½, ⅓ and describe the family.</t>
+          <t>Graph systems of two or more linear inequalities and identify the feasible region; find all integer solutions in the feasible region for budget problems such as combinations of movie trips at $12 each and ice-skating sessions at $21 each with an entertainment budget of $150 (12m + 21s ≤ 150); list integer solutions and interpret in context.</t>
         </is>
       </c>
       <c r="L181" s="15" t="inlineStr">
@@ -14535,7 +14558,7 @@
       </c>
       <c r="M181" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_17</t>
+          <t>y10_alg_09</t>
         </is>
       </c>
       <c r="N181" s="15" t="inlineStr">
@@ -14545,14 +14568,14 @@
       </c>
       <c r="Q181" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson: first formal treatment of exponentials as a function family. Builds on Y9 alg_17 (taster lesson — families of functions). Constant-ratio diagnostic is the key thinking tool, parallel to constant-first-difference and constant-second-difference.</t>
+          <t>Finance context per house preference. Foundation for later linear programming work in senior years.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="16">
       <c r="A182" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_12</t>
+          <t>y10_alg_11</t>
         </is>
       </c>
       <c r="B182" s="15" t="n">
@@ -14564,16 +14587,16 @@
         </is>
       </c>
       <c r="D182" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>features_of_exponential_graphs</t>
+          <t>introducing_exponential_functions</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_12_features_of_exponential_graphs_v2.html</t>
+          <t>y10_alg_11_introducing_exponential_functions_v2.html</t>
         </is>
       </c>
       <c r="G182" s="15" t="inlineStr">
@@ -14583,7 +14606,7 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
@@ -14598,17 +14621,17 @@
       </c>
       <c r="K182" s="15" t="inlineStr">
         <is>
-          <t>Identify the y-intercept (always 1 for y = aˣ), horizontal asymptote (y = 0), domain, range, and whether the function represents growth (a &gt; 1) or decay (0 &lt; a &lt; 1); explore transformations y = aˣ + k and y = aˣ⁻ʰ using graphing software; describe systematic changes in features.</t>
+          <t>Recognise an exponential relation from a table of values by checking whether the ratio between consecutive values of the dependent variable is constant; contrast with the constant first-difference diagnostic for linear and constant second-difference for quadratic; plot y = aˣ for a = 2, 3, ½, ⅓ and describe the family.</t>
         </is>
       </c>
       <c r="L182" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M182" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_11</t>
+          <t>y9_alg_17</t>
         </is>
       </c>
       <c r="N182" s="15" t="inlineStr">
@@ -14618,14 +14641,14 @@
       </c>
       <c r="Q182" s="15" t="inlineStr">
         <is>
-          <t>Investigation-style — practice can include guided parameter-variation tasks alongside auto-marked feature-identification.</t>
+          <t>Watershed lesson: first formal treatment of exponentials as a function family. Builds on Y9 alg_17 (taster lesson — families of functions). Constant-ratio diagnostic is the key thinking tool, parallel to constant-first-difference and constant-second-difference.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" s="16">
       <c r="A183" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_13</t>
+          <t>y10_alg_12</t>
         </is>
       </c>
       <c r="B183" s="15" t="n">
@@ -14637,16 +14660,16 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E183" s="15" t="inlineStr">
         <is>
-          <t>solving_exponential_equations</t>
+          <t>features_of_exponential_graphs</t>
         </is>
       </c>
       <c r="F183" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_13_solving_exponential_equations_v2.html</t>
+          <t>y10_alg_12_features_of_exponential_graphs_v2.html</t>
         </is>
       </c>
       <c r="G183" s="15" t="inlineStr">
@@ -14656,7 +14679,7 @@
       </c>
       <c r="H183" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I183" s="15" t="inlineStr">
@@ -14671,17 +14694,17 @@
       </c>
       <c r="K183" s="15" t="inlineStr">
         <is>
-          <t>Solve exponential equations by inspection (equating exponents when bases match, e.g. 2ˣ = 32); solve graphically using digital tools (intersection of y = aˣ with y = c); solve using symbolic-manipulation tools; explore First Nations Australian Ranger groups' programs that model feral-versus-native animal populations using exponential equations.</t>
+          <t>Identify the y-intercept (always 1 for y = aˣ), horizontal asymptote (y = 0), domain, range, and whether the function represents growth (a &gt; 1) or decay (0 &lt; a &lt; 1); explore transformations y = aˣ + k and y = aˣ⁻ʰ using graphing software; describe systematic changes in features.</t>
         </is>
       </c>
       <c r="L183" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M183" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_12</t>
+          <t>y10_alg_11</t>
         </is>
       </c>
       <c r="N183" s="15" t="inlineStr">
@@ -14691,14 +14714,14 @@
       </c>
       <c r="Q183" s="15" t="inlineStr">
         <is>
-          <t>No formal logarithms (those come in Year 11). Digital-tool solving is the Y10 pathway.</t>
+          <t>Investigation-style — practice can include guided parameter-variation tasks alongside auto-marked feature-identification.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" s="16">
       <c r="A184" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_14</t>
+          <t>y10_alg_13</t>
         </is>
       </c>
       <c r="B184" s="15" t="n">
@@ -14710,26 +14733,26 @@
         </is>
       </c>
       <c r="D184" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E184" s="15" t="inlineStr">
         <is>
-          <t>choosing_linear_quadratic_or_exponential_models</t>
+          <t>solving_exponential_equations</t>
         </is>
       </c>
       <c r="F184" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_14_choosing_linear_quadratic_or_exponential_models_v2.html</t>
+          <t>y10_alg_13_solving_exponential_equations_v2.html</t>
         </is>
       </c>
       <c r="G184" s="15" t="inlineStr">
         <is>
-          <t>AC9M10A04</t>
+          <t>AC9M10A03</t>
         </is>
       </c>
       <c r="H184" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I184" s="15" t="inlineStr">
@@ -14744,17 +14767,17 @@
       </c>
       <c r="K184" s="15" t="inlineStr">
         <is>
-          <t>Diagnose the appropriate function family for a context by examining a table of values — linear (constant first difference), quadratic (constant second difference), exponential (constant ratio); apply the diagnostic to data sets from finance, biology and physics; justify the choice and check the model against further data.</t>
+          <t>Solve exponential equations by inspection (equating exponents when bases match, e.g. 2ˣ = 32); solve graphically using digital tools (intersection of y = aˣ with y = c); solve using symbolic-manipulation tools; explore First Nations Australian Ranger groups' programs that model feral-versus-native animal populations using exponential equations.</t>
         </is>
       </c>
       <c r="L184" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M184" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_11</t>
+          <t>y10_alg_12</t>
         </is>
       </c>
       <c r="N184" s="15" t="inlineStr">
@@ -14764,14 +14787,14 @@
       </c>
       <c r="Q184" s="15" t="inlineStr">
         <is>
-          <t>Synthesis lesson — pulls together diagnostic skills from Y8 alg_05 (linear), Y9 alg_09 (quadratic) and y10_alg_11 (exponential).</t>
+          <t>No formal logarithms (those come in Year 11). Digital-tool solving is the Y10 pathway.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" s="16">
       <c r="A185" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_15</t>
+          <t>y10_alg_14</t>
         </is>
       </c>
       <c r="B185" s="15" t="n">
@@ -14783,16 +14806,16 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E185" s="15" t="inlineStr">
         <is>
-          <t>exponential_growth_and_decay</t>
+          <t>choosing_linear_quadratic_or_exponential_models</t>
         </is>
       </c>
       <c r="F185" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_15_exponential_growth_and_decay_v2.html</t>
+          <t>y10_alg_14_choosing_linear_quadratic_or_exponential_models_v2.html</t>
         </is>
       </c>
       <c r="G185" s="15" t="inlineStr">
@@ -14802,7 +14825,7 @@
       </c>
       <c r="H185" s="15" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I185" s="15" t="inlineStr">
@@ -14817,7 +14840,7 @@
       </c>
       <c r="K185" s="15" t="inlineStr">
         <is>
-          <t>Model situations involving constant percentage change — population growth, bacterial growth, radioactive decay; calculate doubling time and half-life; determine the approximate interval over which values of the model lie within a given range; formulate exponential equations for First Nations Australian Ranger native-versus-feral population modelling.</t>
+          <t>Diagnose the appropriate function family for a context by examining a table of values — linear (constant first difference), quadratic (constant second difference), exponential (constant ratio); apply the diagnostic to data sets from finance, biology and physics; justify the choice and check the model against further data.</t>
         </is>
       </c>
       <c r="L185" s="15" t="inlineStr">
@@ -14827,19 +14850,24 @@
       </c>
       <c r="M185" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_13</t>
+          <t>y10_alg_11</t>
         </is>
       </c>
       <c r="N185" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Synthesis lesson — pulls together diagnostic skills from Y8 alg_05 (linear), Y9 alg_09 (quadratic) and y10_alg_11 (exponential).</t>
         </is>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" s="16">
       <c r="A186" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_16</t>
+          <t>y10_alg_15</t>
         </is>
       </c>
       <c r="B186" s="15" t="n">
@@ -14851,16 +14879,16 @@
         </is>
       </c>
       <c r="D186" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E186" s="15" t="inlineStr">
         <is>
-          <t>compound_interest_modelling</t>
+          <t>exponential_growth_and_decay</t>
         </is>
       </c>
       <c r="F186" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_16_compound_interest_modelling_v2.html</t>
+          <t>y10_alg_15_exponential_growth_and_decay_v2.html</t>
         </is>
       </c>
       <c r="G186" s="15" t="inlineStr">
@@ -14870,7 +14898,7 @@
       </c>
       <c r="H186" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="I186" s="15" t="inlineStr">
@@ -14885,7 +14913,7 @@
       </c>
       <c r="K186" s="15" t="inlineStr">
         <is>
-          <t>Apply the compound interest formula A = P(1 + r/n)ⁿᵗ to authentic investment and loan scenarios; compare compound interest with simple interest over the same period; investigate the effect of compounding frequency (annual vs monthly vs daily); use authentic Australian interest rates and discuss real returns adjusted for inflation.</t>
+          <t>Model situations involving constant percentage change — population growth, bacterial growth, radioactive decay; calculate doubling time and half-life; determine the approximate interval over which values of the model lie within a given range; formulate exponential equations for First Nations Australian Ranger native-versus-feral population modelling.</t>
         </is>
       </c>
       <c r="L186" s="15" t="inlineStr">
@@ -14895,7 +14923,7 @@
       </c>
       <c r="M186" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_15</t>
+          <t>y10_alg_13</t>
         </is>
       </c>
       <c r="N186" s="15" t="inlineStr">
@@ -14903,16 +14931,12 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q186" s="15" t="inlineStr">
-        <is>
-          <t>Watershed lesson and finance flagship for Y10. Connects forward to Y10 num_02 (rounding error compounds at each cycle). Finance context per house preference.</t>
-        </is>
-      </c>
+      <c r="Q186" s="15" t="n"/>
     </row>
     <row r="187" ht="15" customHeight="1" s="16">
       <c r="A187" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_17</t>
+          <t>y10_alg_16</t>
         </is>
       </c>
       <c r="B187" s="15" t="n">
@@ -14924,16 +14948,16 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E187" s="15" t="inlineStr">
         <is>
-          <t>carbon_dating_and_applied_decay_modelling</t>
+          <t>compound_interest_modelling</t>
         </is>
       </c>
       <c r="F187" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_17_carbon_dating_and_applied_decay_modelling_v2.html</t>
+          <t>y10_alg_16_compound_interest_modelling_v2.html</t>
         </is>
       </c>
       <c r="G187" s="15" t="inlineStr">
@@ -14943,7 +14967,7 @@
       </c>
       <c r="H187" s="15" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I187" s="15" t="inlineStr">
@@ -14958,7 +14982,7 @@
       </c>
       <c r="K187" s="15" t="inlineStr">
         <is>
-          <t>Apply exponential decay models to carbon dating of First Nations Australians' artefacts and material culture; investigate population modelling for native animals on Country/Place with varying reproductive behaviour; critique the applicability of an exponential model when populations approach environmental carrying capacity.</t>
+          <t>Apply the compound interest formula A = P(1 + r/n)ⁿᵗ to authentic investment and loan scenarios; compare compound interest with simple interest over the same period; investigate the effect of compounding frequency (annual vs monthly vs daily); use authentic Australian interest rates and discuss real returns adjusted for inflation.</t>
         </is>
       </c>
       <c r="L187" s="15" t="inlineStr">
@@ -14978,14 +15002,14 @@
       </c>
       <c r="Q187" s="15" t="inlineStr">
         <is>
-          <t>Open-ended modelling lesson — practice mixes calculation with model-critique questions.</t>
+          <t>Watershed lesson and finance flagship for Y10. Connects forward to Y10 num_02 (rounding error compounds at each cycle). Finance context per house preference.</t>
         </is>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" s="16">
       <c r="A188" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_18</t>
+          <t>y10_alg_17</t>
         </is>
       </c>
       <c r="B188" s="15" t="n">
@@ -14997,26 +15021,26 @@
         </is>
       </c>
       <c r="D188" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E188" s="15" t="inlineStr">
         <is>
-          <t>intersections_of_functions_with_digital_tools</t>
+          <t>carbon_dating_and_applied_decay_modelling</t>
         </is>
       </c>
       <c r="F188" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_18_intersections_of_functions_with_digital_tools_v2.html</t>
+          <t>y10_alg_17_carbon_dating_and_applied_decay_modelling_v2.html</t>
         </is>
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>AC9M10A05</t>
+          <t>AC9M10A04</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="I188" s="15" t="inlineStr">
@@ -15031,7 +15055,7 @@
       </c>
       <c r="K188" s="15" t="inlineStr">
         <is>
-          <t>Use the zoom functionality of graphing tools to systematically refine intervals and approximate intersections of dissimilar functions (e.g. x² = 2ˣ, intersection of a linear function with a quadratic or a circle); compare graphical and algebraic solutions where both are available; recognise that some intersections have no exact closed-form solution.</t>
+          <t>Apply exponential decay models to carbon dating of First Nations Australians' artefacts and material culture; investigate population modelling for native animals on Country/Place with varying reproductive behaviour; critique the applicability of an exponential model when populations approach environmental carrying capacity.</t>
         </is>
       </c>
       <c r="L188" s="15" t="inlineStr">
@@ -15041,7 +15065,7 @@
       </c>
       <c r="M188" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_11</t>
+          <t>y10_alg_15</t>
         </is>
       </c>
       <c r="N188" s="15" t="inlineStr">
@@ -15051,14 +15075,14 @@
       </c>
       <c r="Q188" s="15" t="inlineStr">
         <is>
-          <t>Investigation lesson — practice can include screenshot-based or table-of-values items for the zoom workflow.</t>
+          <t>Open-ended modelling lesson — practice mixes calculation with model-critique questions.</t>
         </is>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" s="16">
       <c r="A189" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_19</t>
+          <t>y10_alg_18</t>
         </is>
       </c>
       <c r="B189" s="15" t="n">
@@ -15070,16 +15094,16 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E189" s="15" t="inlineStr">
         <is>
-          <t>circle_equations_and_transformations</t>
+          <t>intersections_of_functions_with_digital_tools</t>
         </is>
       </c>
       <c r="F189" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_19_circle_equations_and_transformations_v2.html</t>
+          <t>y10_alg_18_intersections_of_functions_with_digital_tools_v2.html</t>
         </is>
       </c>
       <c r="G189" s="15" t="inlineStr">
@@ -15089,7 +15113,7 @@
       </c>
       <c r="H189" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I189" s="15" t="inlineStr">
@@ -15104,17 +15128,17 @@
       </c>
       <c r="K189" s="15" t="inlineStr">
         <is>
-          <t>Recognise x² + y² = 1 as the unit circle centred at the origin; apply transformations — dilation x² + y² = r² (scaling), translation (x − h)² + (y − k)² = r²; locate the centre and radius of any circle written in standard form; sketch transformed circles on the Cartesian plane.</t>
+          <t>Use the zoom functionality of graphing tools to systematically refine intervals and approximate intersections of dissimilar functions (e.g. x² = 2ˣ, intersection of a linear function with a quadratic or a circle); compare graphical and algebraic solutions where both are available; recognise that some intersections have no exact closed-form solution.</t>
         </is>
       </c>
       <c r="L189" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M189" s="15" t="inlineStr">
         <is>
-          <t>y9_alg_07</t>
+          <t>y10_alg_11</t>
         </is>
       </c>
       <c r="N189" s="15" t="inlineStr">
@@ -15124,14 +15148,14 @@
       </c>
       <c r="Q189" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand prereq: distance formula from y9_alg_07. First analytic treatment of the circle as a relation in Cartesian form.</t>
+          <t>Investigation lesson — practice can include screenshot-based or table-of-values items for the zoom workflow.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" s="16">
       <c r="A190" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_20</t>
+          <t>y10_alg_19</t>
         </is>
       </c>
       <c r="B190" s="15" t="n">
@@ -15143,16 +15167,16 @@
         </is>
       </c>
       <c r="D190" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E190" s="15" t="inlineStr">
         <is>
-          <t>intervals_and_iterative_methods</t>
+          <t>circle_equations_and_transformations</t>
         </is>
       </c>
       <c r="F190" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_20_intervals_and_iterative_methods_v2.html</t>
+          <t>y10_alg_19_circle_equations_and_transformations_v2.html</t>
         </is>
       </c>
       <c r="G190" s="15" t="inlineStr">
@@ -15162,7 +15186,7 @@
       </c>
       <c r="H190" s="15" t="inlineStr">
         <is>
-          <t>2,5,6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I190" s="15" t="inlineStr">
@@ -15177,7 +15201,7 @@
       </c>
       <c r="K190" s="15" t="inlineStr">
         <is>
-          <t>Apply the bisection algorithm to approximate the x-intercepts of a quadratic such as f(x) = 2x² − 3x − 7; identify intervals on the real number line where a quadratic is positive or negative (sign chart); use a table of values to determine when an exponential growth or decay model exceeds or falls below a given value, e.g. share-price monitoring.</t>
+          <t>Recognise x² + y² = 1 as the unit circle centred at the origin; apply transformations — dilation x² + y² = r² (scaling), translation (x − h)² + (y − k)² = r²; locate the centre and radius of any circle written in standard form; sketch transformed circles on the Cartesian plane.</t>
         </is>
       </c>
       <c r="L190" s="15" t="inlineStr">
@@ -15187,7 +15211,7 @@
       </c>
       <c r="M190" s="15" t="inlineStr">
         <is>
-          <t>y10_alg_04,y10_alg_13</t>
+          <t>y9_alg_07</t>
         </is>
       </c>
       <c r="N190" s="15" t="inlineStr">
@@ -15197,14 +15221,14 @@
       </c>
       <c r="Q190" s="15" t="inlineStr">
         <is>
-          <t>Bisection is a computational-thinking thread — sets up senior-school numerical methods. Sign-chart skill bridges to y11/y12 inequalities.</t>
+          <t>Cross-strand prereq: distance formula from y9_alg_07. First analytic treatment of the circle as a relation in Cartesian form.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" s="16">
       <c r="A191" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_01</t>
+          <t>y10_alg_20</t>
         </is>
       </c>
       <c r="B191" s="15" t="n">
@@ -15212,30 +15236,30 @@
       </c>
       <c r="C191" s="15" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Algebra</t>
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E191" s="15" t="inlineStr">
         <is>
-          <t>surface_area_of_composite_solids</t>
+          <t>intervals_and_iterative_methods</t>
         </is>
       </c>
       <c r="F191" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_01_surface_area_of_composite_solids_v2.html</t>
+          <t>y10_alg_20_intervals_and_iterative_methods_v2.html</t>
         </is>
       </c>
       <c r="G191" s="15" t="inlineStr">
         <is>
-          <t>AC9M10M01</t>
+          <t>AC9M10A05</t>
         </is>
       </c>
       <c r="H191" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2,5,6</t>
         </is>
       </c>
       <c r="I191" s="15" t="inlineStr">
@@ -15245,12 +15269,12 @@
       </c>
       <c r="J191" s="15" t="inlineStr">
         <is>
-          <t>Attributes of 1-, 2- and 3-dimensional objects are described and measured in appropriate standardised units</t>
+          <t>Relationships between variables can be described and modelled by linear, quadratic and exponential functions applied in many contexts including financial ones</t>
         </is>
       </c>
       <c r="K191" s="15" t="inlineStr">
         <is>
-          <t>Calculate the surface area of composite solids formed from right prisms and cylinders by considering each component face and identifying hidden internal faces; carefully subtract overlapping regions where solids meet; check answers against a sketched net layout.</t>
+          <t>Apply the bisection algorithm to approximate the x-intercepts of a quadratic such as f(x) = 2x² − 3x − 7; identify intervals on the real number line where a quadratic is positive or negative (sign chart); use a table of values to determine when an exponential growth or decay model exceeds or falls below a given value, e.g. share-price monitoring.</t>
         </is>
       </c>
       <c r="L191" s="15" t="inlineStr">
@@ -15260,7 +15284,7 @@
       </c>
       <c r="M191" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_01,y9_mea_02</t>
+          <t>y10_alg_04,y10_alg_13</t>
         </is>
       </c>
       <c r="N191" s="15" t="inlineStr">
@@ -15270,14 +15294,14 @@
       </c>
       <c r="Q191" s="15" t="inlineStr">
         <is>
-          <t>Extends Y9 mea_01 (prism SA) and Y9 mea_02 (cylinder SA) to composite solids. Internal-face identification is the threshold skill.</t>
+          <t>Bisection is a computational-thinking thread — sets up senior-school numerical methods. Sign-chart skill bridges to y11/y12 inequalities.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" s="16">
       <c r="A192" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_02</t>
+          <t>y10_mea_01</t>
         </is>
       </c>
       <c r="B192" s="15" t="n">
@@ -15289,16 +15313,16 @@
         </is>
       </c>
       <c r="D192" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" s="15" t="inlineStr">
         <is>
-          <t>volume_of_composite_solids</t>
+          <t>surface_area_of_composite_solids</t>
         </is>
       </c>
       <c r="F192" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_02_volume_of_composite_solids_v2.html</t>
+          <t>y10_mea_01_surface_area_of_composite_solids_v2.html</t>
         </is>
       </c>
       <c r="G192" s="15" t="inlineStr">
@@ -15323,7 +15347,7 @@
       </c>
       <c r="K192" s="15" t="inlineStr">
         <is>
-          <t>Calculate the volume of composite solids by decomposing into right prisms and cylinders, summing component volumes; for hollow composites (e.g. pipe sections), subtract the inner volume from the outer; verify with an alternative decomposition.</t>
+          <t>Calculate the surface area of composite solids formed from right prisms and cylinders by considering each component face and identifying hidden internal faces; carefully subtract overlapping regions where solids meet; check answers against a sketched net layout.</t>
         </is>
       </c>
       <c r="L192" s="15" t="inlineStr">
@@ -15333,7 +15357,7 @@
       </c>
       <c r="M192" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_02</t>
+          <t>y9_mea_01,y9_mea_02</t>
         </is>
       </c>
       <c r="N192" s="15" t="inlineStr">
@@ -15343,14 +15367,14 @@
       </c>
       <c r="Q192" s="15" t="inlineStr">
         <is>
-          <t>Extends Y8 mea_03 (composite prism V) by adding cylinders to the toolkit.</t>
+          <t>Extends Y9 mea_01 (prism SA) and Y9 mea_02 (cylinder SA) to composite solids. Internal-face identification is the threshold skill.</t>
         </is>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" s="16">
       <c r="A193" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_03</t>
+          <t>y10_mea_02</t>
         </is>
       </c>
       <c r="B193" s="15" t="n">
@@ -15362,16 +15386,16 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_surface_area_and_volume</t>
+          <t>volume_of_composite_solids</t>
         </is>
       </c>
       <c r="F193" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_03_modelling_with_surface_area_and_volume_v2.html</t>
+          <t>y10_mea_02_volume_of_composite_solids_v2.html</t>
         </is>
       </c>
       <c r="G193" s="15" t="inlineStr">
@@ -15381,7 +15405,7 @@
       </c>
       <c r="H193" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I193" s="15" t="inlineStr">
@@ -15396,17 +15420,17 @@
       </c>
       <c r="K193" s="15" t="inlineStr">
         <is>
-          <t>Estimate surface area and volume of irregular composite objects in practical contexts; use mathematical modelling to determine the rainfall that can be saved from a roof top and the optimal shape and dimensions for rainwater storage; determine whether to hire extra freezer space for a fundraising event based on volume of ice cream required.</t>
+          <t>Calculate the volume of composite solids by decomposing into right prisms and cylinders, summing component volumes; for hollow composites (e.g. pipe sections), subtract the inner volume from the outer; verify with an alternative decomposition.</t>
         </is>
       </c>
       <c r="L193" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M193" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_01,y10_mea_02</t>
+          <t>y9_mea_02</t>
         </is>
       </c>
       <c r="N193" s="15" t="inlineStr">
@@ -15416,14 +15440,14 @@
       </c>
       <c r="Q193" s="15" t="inlineStr">
         <is>
-          <t>Full modelling cycle — formulate, solve, interpret, evaluate. Cross-references y10_num_02 (compounding rounding error in volume calculations).</t>
+          <t>Extends Y8 mea_03 (composite prism V) by adding cylinders to the toolkit.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" s="16">
       <c r="A194" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_04</t>
+          <t>y10_mea_03</t>
         </is>
       </c>
       <c r="B194" s="15" t="n">
@@ -15435,26 +15459,26 @@
         </is>
       </c>
       <c r="D194" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E194" s="15" t="inlineStr">
         <is>
-          <t>introducing_logarithmic_scales</t>
+          <t>modelling_with_surface_area_and_volume</t>
         </is>
       </c>
       <c r="F194" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_04_introducing_logarithmic_scales_v2.html</t>
+          <t>y10_mea_03_modelling_with_surface_area_and_volume_v2.html</t>
         </is>
       </c>
       <c r="G194" s="15" t="inlineStr">
         <is>
-          <t>AC9M10M02</t>
+          <t>AC9M10M01</t>
         </is>
       </c>
       <c r="H194" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I194" s="15" t="inlineStr">
@@ -15469,17 +15493,17 @@
       </c>
       <c r="K194" s="15" t="inlineStr">
         <is>
-          <t>Understand that a logarithmic scale is calibrated in terms of order of magnitude — doubling (×2 per step) or powers of 10; read values from a log-scale axis; identify and interpret data representations using log scales; discuss when a log scale is appropriate (wide range of values, percentage change, exponential growth) versus when a linear scale is preferred.</t>
+          <t>Estimate surface area and volume of irregular composite objects in practical contexts; use mathematical modelling to determine the rainfall that can be saved from a roof top and the optimal shape and dimensions for rainwater storage; determine whether to hire extra freezer space for a fundraising event based on volume of ice cream required.</t>
         </is>
       </c>
       <c r="L194" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M194" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_04</t>
+          <t>y10_mea_01,y10_mea_02</t>
         </is>
       </c>
       <c r="N194" s="15" t="inlineStr">
@@ -15489,14 +15513,14 @@
       </c>
       <c r="Q194" s="15" t="inlineStr">
         <is>
-          <t>No Y7-9 precedent — fully new topic flagged by Sam. Builds on y9_mea_04 (scientific notation) for orders-of-magnitude thinking. Conceptual lesson; no formal log algebra (deferred to Y11).</t>
+          <t>Full modelling cycle — formulate, solve, interpret, evaluate. Cross-references y10_num_02 (compounding rounding error in volume calculations).</t>
         </is>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" s="16">
       <c r="A195" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_05</t>
+          <t>y10_mea_04</t>
         </is>
       </c>
       <c r="B195" s="15" t="n">
@@ -15508,16 +15532,16 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E195" s="15" t="inlineStr">
         <is>
-          <t>applying_logarithmic_scales_in_context</t>
+          <t>introducing_logarithmic_scales</t>
         </is>
       </c>
       <c r="F195" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_05_applying_logarithmic_scales_in_context_v2.html</t>
+          <t>y10_mea_04_introducing_logarithmic_scales_v2.html</t>
         </is>
       </c>
       <c r="G195" s="15" t="inlineStr">
@@ -15527,7 +15551,7 @@
       </c>
       <c r="H195" s="15" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I195" s="15" t="inlineStr">
@@ -15542,17 +15566,17 @@
       </c>
       <c r="K195" s="15" t="inlineStr">
         <is>
-          <t>Interpret real-world logarithmic scales — Richter (earthquake magnitude), decibel (sound intensity), pH (acidity), star apparent magnitude; understand what a one-unit change represents on each scale; investigate dating of First Peoples of Australia's archaeological sites (e.g. Madjedbebe, NT) using scientific notation and measurement-accuracy considerations.</t>
+          <t>Understand that a logarithmic scale is calibrated in terms of order of magnitude — doubling (×2 per step) or powers of 10; read values from a log-scale axis; identify and interpret data representations using log scales; discuss when a log scale is appropriate (wide range of values, percentage change, exponential growth) versus when a linear scale is preferred.</t>
         </is>
       </c>
       <c r="L195" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M195" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_04</t>
+          <t>y9_mea_04</t>
         </is>
       </c>
       <c r="N195" s="15" t="inlineStr">
@@ -15562,14 +15586,14 @@
       </c>
       <c r="Q195" s="15" t="inlineStr">
         <is>
-          <t>No Y7-9 precedent. Cultural context is central — Madjedbebe dating directly elaborated in the AC9 text.</t>
+          <t>No Y7-9 precedent — fully new topic flagged by Sam. Builds on y9_mea_04 (scientific notation) for orders-of-magnitude thinking. Conceptual lesson; no formal log algebra (deferred to Y11).</t>
         </is>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" s="16">
       <c r="A196" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_06</t>
+          <t>y10_mea_05</t>
         </is>
       </c>
       <c r="B196" s="15" t="n">
@@ -15581,21 +15605,21 @@
         </is>
       </c>
       <c r="D196" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E196" s="15" t="inlineStr">
         <is>
-          <t>angles_of_elevation_and_depression</t>
+          <t>applying_logarithmic_scales_in_context</t>
         </is>
       </c>
       <c r="F196" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_06_angles_of_elevation_and_depression_v2.html</t>
+          <t>y10_mea_05_applying_logarithmic_scales_in_context_v2.html</t>
         </is>
       </c>
       <c r="G196" s="15" t="inlineStr">
         <is>
-          <t>AC9M10M03</t>
+          <t>AC9M10M02</t>
         </is>
       </c>
       <c r="H196" s="15" t="inlineStr">
@@ -15615,17 +15639,17 @@
       </c>
       <c r="K196" s="15" t="inlineStr">
         <is>
-          <t>Define angle of elevation as the angle measured upward from the horizontal to a target; define angle of depression similarly downward; apply right-angled trigonometry to find heights and distances; use a clinometer (or simulated app) to measure angles of inclination and determine the height of buildings, flagpoles or trees.</t>
+          <t>Interpret real-world logarithmic scales — Richter (earthquake magnitude), decibel (sound intensity), pH (acidity), star apparent magnitude; understand what a one-unit change represents on each scale; investigate dating of First Peoples of Australia's archaeological sites (e.g. Madjedbebe, NT) using scientific notation and measurement-accuracy considerations.</t>
         </is>
       </c>
       <c r="L196" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M196" s="15" t="inlineStr">
         <is>
-          <t>y9_spa_03</t>
+          <t>y10_mea_04</t>
         </is>
       </c>
       <c r="N196" s="15" t="inlineStr">
@@ -15635,14 +15659,14 @@
       </c>
       <c r="Q196" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand prereq: y9_spa_03 (sin/cos/tan defined). First formal treatment of elevation/depression angles.</t>
+          <t>No Y7-9 precedent. Cultural context is central — Madjedbebe dating directly elaborated in the AC9 text.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" s="16">
       <c r="A197" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_07</t>
+          <t>y10_mea_06</t>
         </is>
       </c>
       <c r="B197" s="15" t="n">
@@ -15654,16 +15678,16 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E197" s="15" t="inlineStr">
         <is>
-          <t>bearings_and_navigation</t>
+          <t>angles_of_elevation_and_depression</t>
         </is>
       </c>
       <c r="F197" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_07_bearings_and_navigation_v2.html</t>
+          <t>y10_mea_06_angles_of_elevation_and_depression_v2.html</t>
         </is>
       </c>
       <c r="G197" s="15" t="inlineStr">
@@ -15673,7 +15697,7 @@
       </c>
       <c r="H197" s="15" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I197" s="15" t="inlineStr">
@@ -15688,7 +15712,7 @@
       </c>
       <c r="K197" s="15" t="inlineStr">
         <is>
-          <t>Read and write three-figure bearings (000° to 360° measured clockwise from north); apply right-angled trigonometry to multi-leg navigation problems such as orienteering courses; determine the final bearing and estimate the distance of the closing leg of a route; explore navigation, design of technologies or surveying by First Nations Australians and connections to trigonometric reasoning.</t>
+          <t>Define angle of elevation as the angle measured upward from the horizontal to a target; define angle of depression similarly downward; apply right-angled trigonometry to find heights and distances; use a clinometer (or simulated app) to measure angles of inclination and determine the height of buildings, flagpoles or trees.</t>
         </is>
       </c>
       <c r="L197" s="15" t="inlineStr">
@@ -15708,14 +15732,14 @@
       </c>
       <c r="Q197" s="15" t="inlineStr">
         <is>
-          <t>First time bearings are formalised. Decompose multi-leg routes into right triangles for trig application.</t>
+          <t>Cross-strand prereq: y9_spa_03 (sin/cos/tan defined). First formal treatment of elevation/depression angles.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" s="16">
       <c r="A198" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_08</t>
+          <t>y10_mea_07</t>
         </is>
       </c>
       <c r="B198" s="15" t="n">
@@ -15727,16 +15751,16 @@
         </is>
       </c>
       <c r="D198" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E198" s="15" t="inlineStr">
         <is>
-          <t>three_dimensional_pythagoras_and_trig</t>
+          <t>bearings_and_navigation</t>
         </is>
       </c>
       <c r="F198" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_08_three_dimensional_pythagoras_and_trig_v2.html</t>
+          <t>y10_mea_07_bearings_and_navigation_v2.html</t>
         </is>
       </c>
       <c r="G198" s="15" t="inlineStr">
@@ -15746,7 +15770,7 @@
       </c>
       <c r="H198" s="15" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I198" s="15" t="inlineStr">
@@ -15761,7 +15785,7 @@
       </c>
       <c r="K198" s="15" t="inlineStr">
         <is>
-          <t>Decompose three-dimensional problems into two-dimensional right-angled triangles; calculate the longest internal diagonal of a rectangular prism using Pythagoras' theorem twice; calculate the angle a diagonal makes with a face; determine the smallest box needed to package an object of given length; use dynamic geometry software for crime-scene reconstruction style problems.</t>
+          <t>Read and write three-figure bearings (000° to 360° measured clockwise from north); apply right-angled trigonometry to multi-leg navigation problems such as orienteering courses; determine the final bearing and estimate the distance of the closing leg of a route; explore navigation, design of technologies or surveying by First Nations Australians and connections to trigonometric reasoning.</t>
         </is>
       </c>
       <c r="L198" s="15" t="inlineStr">
@@ -15771,7 +15795,7 @@
       </c>
       <c r="M198" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_06,y8_mea_12</t>
+          <t>y9_spa_03</t>
         </is>
       </c>
       <c r="N198" s="15" t="inlineStr">
@@ -15781,14 +15805,14 @@
       </c>
       <c r="Q198" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — major synthesis of Pythagoras and trig in three dimensions. The two-step decomposition (find a 2D diagonal, then use it as a side of another right triangle) is the key technique.</t>
+          <t>First time bearings are formalised. Decompose multi-leg routes into right triangles for trig application.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" s="16">
       <c r="A199" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_09</t>
+          <t>y10_mea_08</t>
         </is>
       </c>
       <c r="B199" s="15" t="n">
@@ -15800,26 +15824,26 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E199" s="15" t="inlineStr">
         <is>
-          <t>measurement_errors_in_research_and_instruments</t>
+          <t>three_dimensional_pythagoras_and_trig</t>
         </is>
       </c>
       <c r="F199" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_09_measurement_errors_in_research_and_instruments_v2.html</t>
+          <t>y10_mea_08_three_dimensional_pythagoras_and_trig_v2.html</t>
         </is>
       </c>
       <c r="G199" s="15" t="inlineStr">
         <is>
-          <t>AC9M10M04</t>
+          <t>AC9M10M03</t>
         </is>
       </c>
       <c r="H199" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="I199" s="15" t="inlineStr">
@@ -15829,12 +15853,12 @@
       </c>
       <c r="J199" s="15" t="inlineStr">
         <is>
-          <t>Measurement errors impact the accuracy of results</t>
+          <t>Attributes of 1-, 2- and 3-dimensional objects are described and measured in appropriate standardised units</t>
         </is>
       </c>
       <c r="K199" s="15" t="inlineStr">
         <is>
-          <t>Describe settings where measurement errors impact research results — biased findings, instrumentation limitations; analyse instruments and methods for measurement in investigations (resolution, accuracy, calibration); recognise how systematic versus random error propagates; design improvements that reduce error in a given experimental setup.</t>
+          <t>Decompose three-dimensional problems into two-dimensional right-angled triangles; calculate the longest internal diagonal of a rectangular prism using Pythagoras' theorem twice; calculate the angle a diagonal makes with a face; determine the smallest box needed to package an object of given length; use dynamic geometry software for crime-scene reconstruction style problems.</t>
         </is>
       </c>
       <c r="L199" s="15" t="inlineStr">
@@ -15844,7 +15868,7 @@
       </c>
       <c r="M199" s="15" t="inlineStr">
         <is>
-          <t>y9_mea_09</t>
+          <t>y10_mea_06,y8_mea_12</t>
         </is>
       </c>
       <c r="N199" s="15" t="inlineStr">
@@ -15854,14 +15878,14 @@
       </c>
       <c r="Q199" s="15" t="inlineStr">
         <is>
-          <t>Extends Y9 mea_09 / mea_10 (absolute/relative/percentage error) into research-design framing. M04 e3 (compounding finance errors) is covered via the cross-tag in y10_num_02.</t>
+          <t>Watershed lesson — major synthesis of Pythagoras and trig in three dimensions. The two-step decomposition (find a 2D diagonal, then use it as a side of another right triangle) is the key technique.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" s="16">
       <c r="A200" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_10</t>
+          <t>y10_mea_09</t>
         </is>
       </c>
       <c r="B200" s="15" t="n">
@@ -15873,16 +15897,16 @@
         </is>
       </c>
       <c r="D200" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E200" s="15" t="inlineStr">
         <is>
-          <t>scientific_dating_and_ethical_measurement</t>
+          <t>measurement_errors_in_research_and_instruments</t>
         </is>
       </c>
       <c r="F200" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_10_scientific_dating_and_ethical_measurement_v2.html</t>
+          <t>y10_mea_09_measurement_errors_in_research_and_instruments_v2.html</t>
         </is>
       </c>
       <c r="G200" s="15" t="inlineStr">
@@ -15892,7 +15916,7 @@
       </c>
       <c r="H200" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I200" s="15" t="inlineStr">
@@ -15907,17 +15931,17 @@
       </c>
       <c r="K200" s="15" t="inlineStr">
         <is>
-          <t>Investigate scientific measuring techniques applied to First Peoples of Australia and their artefacts — radiocarbon dating, optically stimulated luminescence, genetic sequencing; discuss measurement-error implications for archaeological claims; examine the social impact of measurement errors in cultural-heritage research.</t>
+          <t>Describe settings where measurement errors impact research results — biased findings, instrumentation limitations; analyse instruments and methods for measurement in investigations (resolution, accuracy, calibration); recognise how systematic versus random error propagates; design improvements that reduce error in a given experimental setup.</t>
         </is>
       </c>
       <c r="L200" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M200" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_09</t>
+          <t>y9_mea_09</t>
         </is>
       </c>
       <c r="N200" s="15" t="inlineStr">
@@ -15927,14 +15951,14 @@
       </c>
       <c r="Q200" s="15" t="inlineStr">
         <is>
-          <t>Companion to y10_mea_05 (Madjedbebe context). Open-ended modelling — practice can include analysis-style items alongside numeric error calculations.</t>
+          <t>Extends Y9 mea_09 / mea_10 (absolute/relative/percentage error) into research-design framing. M04 e3 (compounding finance errors) is covered via the cross-tag in y10_num_02.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" s="16">
       <c r="A201" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_11</t>
+          <t>y10_mea_10</t>
         </is>
       </c>
       <c r="B201" s="15" t="n">
@@ -15946,26 +15970,26 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E201" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_scale_drawings_and_plans</t>
+          <t>scientific_dating_and_ethical_measurement</t>
         </is>
       </c>
       <c r="F201" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_11_modelling_with_scale_drawings_and_plans_v2.html</t>
+          <t>y10_mea_10_scientific_dating_and_ethical_measurement_v2.html</t>
         </is>
       </c>
       <c r="G201" s="15" t="inlineStr">
         <is>
-          <t>AC9M10M05</t>
+          <t>AC9M10M04</t>
         </is>
       </c>
       <c r="H201" s="15" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I201" s="15" t="inlineStr">
@@ -15975,12 +15999,12 @@
       </c>
       <c r="J201" s="15" t="inlineStr">
         <is>
-          <t>Attributes of 1-, 2- and 3-dimensional objects are described and measured in appropriate standardised units</t>
+          <t>Measurement errors impact the accuracy of results</t>
         </is>
       </c>
       <c r="K201" s="15" t="inlineStr">
         <is>
-          <t>Use plans and elevation drawings to investigate changes to building designs; convert between scale and actual measurements; estimate the scale of an object such as a toy car by measuring one linear dimension and comparing with a known full-size dimension; make decisions about design changes based on scaled measurements.</t>
+          <t>Investigate scientific measuring techniques applied to First Peoples of Australia and their artefacts — radiocarbon dating, optically stimulated luminescence, genetic sequencing; discuss measurement-error implications for archaeological claims; examine the social impact of measurement errors in cultural-heritage research.</t>
         </is>
       </c>
       <c r="L201" s="15" t="inlineStr">
@@ -15990,7 +16014,7 @@
       </c>
       <c r="M201" s="15" t="inlineStr">
         <is>
-          <t>y8_mea_14</t>
+          <t>y10_mea_09</t>
         </is>
       </c>
       <c r="N201" s="15" t="inlineStr">
@@ -16000,14 +16024,14 @@
       </c>
       <c r="Q201" s="15" t="inlineStr">
         <is>
-          <t>Builds on Y8 mea_14 (scale and proportion in design). Y10 emphasis on full modelling cycle — formulate, interpret, evaluate, modify.</t>
+          <t>Companion to y10_mea_05 (Madjedbebe context). Open-ended modelling — practice can include analysis-style items alongside numeric error calculations.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" s="16">
       <c r="A202" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_12</t>
+          <t>y10_mea_11</t>
         </is>
       </c>
       <c r="B202" s="15" t="n">
@@ -16019,16 +16043,16 @@
         </is>
       </c>
       <c r="D202" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E202" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_3d_scaling_and_compliance</t>
+          <t>modelling_with_scale_drawings_and_plans</t>
         </is>
       </c>
       <c r="F202" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_12_modelling_with_3d_scaling_and_compliance_v2.html</t>
+          <t>y10_mea_11_modelling_with_scale_drawings_and_plans_v2.html</t>
         </is>
       </c>
       <c r="G202" s="15" t="inlineStr">
@@ -16038,7 +16062,7 @@
       </c>
       <c r="H202" s="15" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I202" s="15" t="inlineStr">
@@ -16053,7 +16077,7 @@
       </c>
       <c r="K202" s="15" t="inlineStr">
         <is>
-          <t>Analyse and apply scale and ratios in production-prototype contexts including 3D printing; use a 3D printer (or simulation) to produce scaled versions of actual objects; investigate compliance with building codes and standards in design and construction, e.g. tread/riser ratios for escalators in shopping centres.</t>
+          <t>Use plans and elevation drawings to investigate changes to building designs; convert between scale and actual measurements; estimate the scale of an object such as a toy car by measuring one linear dimension and comparing with a known full-size dimension; make decisions about design changes based on scaled measurements.</t>
         </is>
       </c>
       <c r="L202" s="15" t="inlineStr">
@@ -16063,7 +16087,7 @@
       </c>
       <c r="M202" s="15" t="inlineStr">
         <is>
-          <t>y10_mea_11</t>
+          <t>y8_mea_14</t>
         </is>
       </c>
       <c r="N202" s="15" t="inlineStr">
@@ -16073,14 +16097,14 @@
       </c>
       <c r="Q202" s="15" t="inlineStr">
         <is>
-          <t>Compliance context is the new addition — applies scale-factor effects on area and volume (Y9 spa_05 / mea_07) to safety regulations.</t>
+          <t>Builds on Y8 mea_14 (scale and proportion in design). Y10 emphasis on full modelling cycle — formulate, interpret, evaluate, modify.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" s="16">
       <c r="A203" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_01</t>
+          <t>y10_mea_12</t>
         </is>
       </c>
       <c r="B203" s="15" t="n">
@@ -16088,30 +16112,30 @@
       </c>
       <c r="C203" s="15" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E203" s="15" t="inlineStr">
         <is>
-          <t>demonstration_versus_proof</t>
+          <t>modelling_with_3d_scaling_and_compliance</t>
         </is>
       </c>
       <c r="F203" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_01_demonstration_versus_proof_v2.html</t>
+          <t>y10_mea_12_modelling_with_3d_scaling_and_compliance_v2.html</t>
         </is>
       </c>
       <c r="G203" s="15" t="inlineStr">
         <is>
-          <t>AC9M10SP01</t>
+          <t>AC9M10M05</t>
         </is>
       </c>
       <c r="H203" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="I203" s="15" t="inlineStr">
@@ -16121,22 +16145,22 @@
       </c>
       <c r="J203" s="15" t="inlineStr">
         <is>
-          <t>Situations involving angles, distance and direction can be quantified using geometric properties and theorems</t>
+          <t>Attributes of 1-, 2- and 3-dimensional objects are described and measured in appropriate standardised units</t>
         </is>
       </c>
       <c r="K203" s="15" t="inlineStr">
         <is>
-          <t>Distinguish a practical demonstration (e.g. placing triangles on top of each other to show congruence, tearing-and-arranging interior angles) from a formal proof (a sequence of logically connected statements that establish the result for all cases); recognise the role of assumptions, definitions and previously established theorems in a proof.</t>
+          <t>Analyse and apply scale and ratios in production-prototype contexts including 3D printing; use a 3D printer (or simulation) to produce scaled versions of actual objects; investigate compliance with building codes and standards in design and construction, e.g. tread/riser ratios for escalators in shopping centres.</t>
         </is>
       </c>
       <c r="L203" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M203" s="15" t="inlineStr">
         <is>
-          <t>y8_spa_04</t>
+          <t>y10_mea_11</t>
         </is>
       </c>
       <c r="N203" s="15" t="inlineStr">
@@ -16146,14 +16170,14 @@
       </c>
       <c r="Q203" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — what makes a proof? The shift from 'I can show it works for this triangle' to 'I have established it for all such triangles' is the threshold concept.</t>
+          <t>Compliance context is the new addition — applies scale-factor effects on area and volume (Y9 spa_05 / mea_07) to safety regulations.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" s="16">
       <c r="A204" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_02</t>
+          <t>y10_spa_01</t>
         </is>
       </c>
       <c r="B204" s="15" t="n">
@@ -16165,16 +16189,16 @@
         </is>
       </c>
       <c r="D204" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" s="15" t="inlineStr">
         <is>
-          <t>proofs_using_triangle_congruence</t>
+          <t>demonstration_versus_proof</t>
         </is>
       </c>
       <c r="F204" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_02_proofs_using_triangle_congruence_v2.html</t>
+          <t>y10_spa_01_demonstration_versus_proof_v2.html</t>
         </is>
       </c>
       <c r="G204" s="15" t="inlineStr">
@@ -16184,7 +16208,7 @@
       </c>
       <c r="H204" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I204" s="15" t="inlineStr">
@@ -16199,7 +16223,7 @@
       </c>
       <c r="K204" s="15" t="inlineStr">
         <is>
-          <t>Develop formal proofs involving congruent triangles and angle properties; communicate each proof as a sequence of logically connected statements with justifications drawn from definitions, given information and congruence tests (SSS, SAS, ASA, RHS); prove standard results such as the base angles of an isosceles triangle are equal.</t>
+          <t>Distinguish a practical demonstration (e.g. placing triangles on top of each other to show congruence, tearing-and-arranging interior angles) from a formal proof (a sequence of logically connected statements that establish the result for all cases); recognise the role of assumptions, definitions and previously established theorems in a proof.</t>
         </is>
       </c>
       <c r="L204" s="15" t="inlineStr">
@@ -16209,7 +16233,7 @@
       </c>
       <c r="M204" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_01,y8_spa_02</t>
+          <t>y8_spa_04</t>
         </is>
       </c>
       <c r="N204" s="15" t="inlineStr">
@@ -16219,14 +16243,14 @@
       </c>
       <c r="Q204" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand prereq: Y8 spa_02 (congruence tests). Builds on Y8 spa_04 (deductive properties of quadrilaterals).</t>
+          <t>Watershed lesson — what makes a proof? The shift from 'I can show it works for this triangle' to 'I have established it for all such triangles' is the threshold concept.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" s="16">
       <c r="A205" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_03</t>
+          <t>y10_spa_02</t>
         </is>
       </c>
       <c r="B205" s="15" t="n">
@@ -16238,16 +16262,16 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" s="15" t="inlineStr">
         <is>
-          <t>deducing_properties_via_similarity_and_theorems</t>
+          <t>proofs_using_triangle_congruence</t>
         </is>
       </c>
       <c r="F205" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_03_deducing_properties_via_similarity_and_theorems_v2.html</t>
+          <t>y10_spa_02_proofs_using_triangle_congruence_v2.html</t>
         </is>
       </c>
       <c r="G205" s="15" t="inlineStr">
@@ -16257,7 +16281,7 @@
       </c>
       <c r="H205" s="15" t="inlineStr">
         <is>
-          <t>3,4,5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I205" s="15" t="inlineStr">
@@ -16272,17 +16296,17 @@
       </c>
       <c r="K205" s="15" t="inlineStr">
         <is>
-          <t>Apply similarity tests in formal proofs and numerical exercises involving plane shapes; use visual proofs to justify solutions; investigate proofs of geometric theorems and apply them to solve spatial problems; use dynamic geometry software to investigate properties such as the shortest path that touches three sides of a rectangle starting and finishing at the same point, and prove the path forms a parallelogram.</t>
+          <t>Develop formal proofs involving congruent triangles and angle properties; communicate each proof as a sequence of logically connected statements with justifications drawn from definitions, given information and congruence tests (SSS, SAS, ASA, RHS); prove standard results such as the base angles of an isosceles triangle are equal.</t>
         </is>
       </c>
       <c r="L205" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M205" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_02,y8_spa_03</t>
+          <t>y10_spa_01,y8_spa_02</t>
         </is>
       </c>
       <c r="N205" s="15" t="inlineStr">
@@ -16292,14 +16316,14 @@
       </c>
       <c r="Q205" s="15" t="inlineStr">
         <is>
-          <t>Investigation lesson — practice includes both proof completion and conjecture-with-dynamic-geometry items.</t>
+          <t>Cross-strand prereq: Y8 spa_02 (congruence tests). Builds on Y8 spa_04 (deductive properties of quadrilaterals).</t>
         </is>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" s="16">
       <c r="A206" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_04</t>
+          <t>y10_spa_03</t>
         </is>
       </c>
       <c r="B206" s="15" t="n">
@@ -16311,26 +16335,26 @@
         </is>
       </c>
       <c r="D206" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E206" s="15" t="inlineStr">
         <is>
-          <t>introducing_networks_and_connectedness</t>
+          <t>deducing_properties_via_similarity_and_theorems</t>
         </is>
       </c>
       <c r="F206" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_04_introducing_networks_and_connectedness_v2.html</t>
+          <t>y10_spa_03_deducing_properties_via_similarity_and_theorems_v2.html</t>
         </is>
       </c>
       <c r="G206" s="15" t="inlineStr">
         <is>
-          <t>AC9M10SP02</t>
+          <t>AC9M10SP01</t>
         </is>
       </c>
       <c r="H206" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>3,4,5</t>
         </is>
       </c>
       <c r="I206" s="15" t="inlineStr">
@@ -16345,12 +16369,17 @@
       </c>
       <c r="K206" s="15" t="inlineStr">
         <is>
-          <t>Investigate how networks (graphs) can model authentic situations — recognise what the nodes (vertices) represent and what the edges represent; describe the connectedness of a network; tackle the Seven Bridges of Königsberg problem — can each bridge be crossed exactly once? — and connect to the concept of degree of a vertex.</t>
+          <t>Apply similarity tests in formal proofs and numerical exercises involving plane shapes; use visual proofs to justify solutions; investigate proofs of geometric theorems and apply them to solve spatial problems; use dynamic geometry software to investigate properties such as the shortest path that touches three sides of a rectangle starting and finishing at the same point, and prove the path forms a parallelogram.</t>
         </is>
       </c>
       <c r="L206" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>y10_spa_02,y8_spa_03</t>
         </is>
       </c>
       <c r="N206" s="15" t="inlineStr">
@@ -16360,14 +16389,14 @@
       </c>
       <c r="Q206" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — no Y7-9 precedent (Sam-flagged). Graph theory is genuinely new territory. Königsberg is the classical entry point.</t>
+          <t>Investigation lesson — practice includes both proof completion and conjecture-with-dynamic-geometry items.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" s="16">
       <c r="A207" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_05</t>
+          <t>y10_spa_04</t>
         </is>
       </c>
       <c r="B207" s="15" t="n">
@@ -16379,16 +16408,16 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E207" s="15" t="inlineStr">
         <is>
-          <t>polyhedra_and_eulers_formula</t>
+          <t>introducing_networks_and_connectedness</t>
         </is>
       </c>
       <c r="F207" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_05_polyhedra_and_eulers_formula_v2.html</t>
+          <t>y10_spa_04_introducing_networks_and_connectedness_v2.html</t>
         </is>
       </c>
       <c r="G207" s="15" t="inlineStr">
@@ -16398,7 +16427,7 @@
       </c>
       <c r="H207" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I207" s="15" t="inlineStr">
@@ -16413,7 +16442,7 @@
       </c>
       <c r="K207" s="15" t="inlineStr">
         <is>
-          <t>Represent polyhedra as networks using edges, vertices, and interior and exterior faces; record F, V and E for the five Platonic solids in a table and demonstrate Euler's formula F + V = E + 2 holds; predict F for a polyhedron given E and V; relate the formula to map colouring and planarity.</t>
+          <t>Investigate how networks (graphs) can model authentic situations — recognise what the nodes (vertices) represent and what the edges represent; describe the connectedness of a network; tackle the Seven Bridges of Königsberg problem — can each bridge be crossed exactly once? — and connect to the concept of degree of a vertex.</t>
         </is>
       </c>
       <c r="L207" s="15" t="inlineStr">
@@ -16421,11 +16450,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M207" s="15" t="inlineStr">
-        <is>
-          <t>y10_spa_04</t>
-        </is>
-      </c>
+      <c r="M207" s="15" t="n"/>
       <c r="N207" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -16433,14 +16458,14 @@
       </c>
       <c r="Q207" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand link: Y7 spa_01 (nets of prisms and pyramids) provides familiarity with the solids. Euler's formula is a famous result — flag for I Do narrative.</t>
+          <t>Watershed lesson — no Y7-9 precedent (Sam-flagged). Graph theory is genuinely new territory. Königsberg is the classical entry point.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" s="16">
       <c r="A208" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_06</t>
+          <t>y10_spa_05</t>
         </is>
       </c>
       <c r="B208" s="15" t="n">
@@ -16452,16 +16477,16 @@
         </is>
       </c>
       <c r="D208" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E208" s="15" t="inlineStr">
         <is>
-          <t>modelling_with_networks</t>
+          <t>polyhedra_and_eulers_formula</t>
         </is>
       </c>
       <c r="F208" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_06_modelling_with_networks_v2.html</t>
+          <t>y10_spa_05_polyhedra_and_eulers_formula_v2.html</t>
         </is>
       </c>
       <c r="G208" s="15" t="inlineStr">
@@ -16471,7 +16496,7 @@
       </c>
       <c r="H208" s="15" t="inlineStr">
         <is>
-          <t>4,5,6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I208" s="15" t="inlineStr">
@@ -16486,12 +16511,12 @@
       </c>
       <c r="K208" s="15" t="inlineStr">
         <is>
-          <t>Represent authentic situations as network diagrams — social networks, intranet/LAN/wireless networks of a home, electrical wiring, rail or air travel networks (London, Paris, Hong Kong), food webs in a simple ecosystem, metabolic networks; represent First Nations Australians' kinship systems using network diagrams and explore the significance of relationships to Country/Place.</t>
+          <t>Represent polyhedra as networks using edges, vertices, and interior and exterior faces; record F, V and E for the five Platonic solids in a table and demonstrate Euler's formula F + V = E + 2 holds; predict F for a polyhedron given E and V; relate the formula to map colouring and planarity.</t>
         </is>
       </c>
       <c r="L208" s="15" t="inlineStr">
         <is>
-          <t>matching</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M208" s="15" t="inlineStr">
@@ -16506,14 +16531,14 @@
       </c>
       <c r="Q208" s="15" t="inlineStr">
         <is>
-          <t>Matching practice — pair context with appropriate network type or feature.</t>
+          <t>Cross-strand link: Y7 spa_01 (nets of prisms and pyramids) provides familiarity with the solids. Euler's formula is a famous result — flag for I Do narrative.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" s="16">
       <c r="A209" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_07</t>
+          <t>y10_spa_06</t>
         </is>
       </c>
       <c r="B209" s="15" t="n">
@@ -16525,26 +16550,26 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E209" s="15" t="inlineStr">
         <is>
-          <t>algorithms_for_network_problems</t>
+          <t>modelling_with_networks</t>
         </is>
       </c>
       <c r="F209" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_07_algorithms_for_network_problems_v2.html</t>
+          <t>y10_spa_06_modelling_with_networks_v2.html</t>
         </is>
       </c>
       <c r="G209" s="15" t="inlineStr">
         <is>
-          <t>AC9M10SP03</t>
+          <t>AC9M10SP02</t>
         </is>
       </c>
       <c r="H209" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4,5,6</t>
         </is>
       </c>
       <c r="I209" s="15" t="inlineStr">
@@ -16559,12 +16584,12 @@
       </c>
       <c r="K209" s="15" t="inlineStr">
         <is>
-          <t>Apply a computational-thinking approach to problems involving networks — investigate connectedness, coverage and weighted measures (edge weights for distance or cost); design or trace algorithms for choosing the most efficient route on a road network using virtual map software; compare alternative algorithms on the same network.</t>
+          <t>Represent authentic situations as network diagrams — social networks, intranet/LAN/wireless networks of a home, electrical wiring, rail or air travel networks (London, Paris, Hong Kong), food webs in a simple ecosystem, metabolic networks; represent First Nations Australians' kinship systems using network diagrams and explore the significance of relationships to Country/Place.</t>
         </is>
       </c>
       <c r="L209" s="15" t="inlineStr">
         <is>
-          <t>strategy-MCQ</t>
+          <t>matching</t>
         </is>
       </c>
       <c r="M209" s="15" t="inlineStr">
@@ -16579,14 +16604,14 @@
       </c>
       <c r="Q209" s="15" t="inlineStr">
         <is>
-          <t>Strategy-MCQ matches the decision-tree algorithmic content, mirroring y7_spa_07, y8_spa_07, y9_spa_06/07.</t>
+          <t>Matching practice — pair context with appropriate network type or feature.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" s="16">
       <c r="A210" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_08</t>
+          <t>y10_spa_07</t>
         </is>
       </c>
       <c r="B210" s="15" t="n">
@@ -16598,16 +16623,16 @@
         </is>
       </c>
       <c r="D210" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E210" s="15" t="inlineStr">
         <is>
-          <t>algorithms_for_spatial_design</t>
+          <t>algorithms_for_network_problems</t>
         </is>
       </c>
       <c r="F210" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_08_algorithms_for_spatial_design_v2.html</t>
+          <t>y10_spa_07_algorithms_for_network_problems_v2.html</t>
         </is>
       </c>
       <c r="G210" s="15" t="inlineStr">
@@ -16617,7 +16642,7 @@
       </c>
       <c r="H210" s="15" t="inlineStr">
         <is>
-          <t>1,3,4,5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I210" s="15" t="inlineStr">
@@ -16632,7 +16657,7 @@
       </c>
       <c r="K210" s="15" t="inlineStr">
         <is>
-          <t>Design and make scale models of three-dimensional objects using digital tools (e.g. 3D-printable puzzle components using tessellations); define and decompose spatial problems and create algorithms — for example, a floor plan that limits congestion at checkouts; test algorithms in pseudocode or flow charts; produce self-similar patterns and validate algorithms with multiple test cases; explore geospatial technologies used by First Nations Australians' communities.</t>
+          <t>Apply a computational-thinking approach to problems involving networks — investigate connectedness, coverage and weighted measures (edge weights for distance or cost); design or trace algorithms for choosing the most efficient route on a road network using virtual map software; compare alternative algorithms on the same network.</t>
         </is>
       </c>
       <c r="L210" s="15" t="inlineStr">
@@ -16642,7 +16667,7 @@
       </c>
       <c r="M210" s="15" t="inlineStr">
         <is>
-          <t>y10_spa_07</t>
+          <t>y10_spa_04</t>
         </is>
       </c>
       <c r="N210" s="15" t="inlineStr">
@@ -16652,14 +16677,14 @@
       </c>
       <c r="Q210" s="15" t="inlineStr">
         <is>
-          <t>Strategy-MCQ for the algorithm-choice content. Broad capstone — covers four elaborations spanning 3D modelling, floor planning, fractal generation and First Nations geospatial techniques.</t>
+          <t>Strategy-MCQ matches the decision-tree algorithmic content, mirroring y7_spa_07, y8_spa_07, y9_spa_06/07.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" s="16">
       <c r="A211" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_01</t>
+          <t>y10_spa_08</t>
         </is>
       </c>
       <c r="B211" s="15" t="n">
@@ -16667,30 +16692,30 @@
       </c>
       <c r="C211" s="15" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E211" s="15" t="inlineStr">
         <is>
-          <t>analysing_statistical_claims_in_media</t>
+          <t>algorithms_for_spatial_design</t>
         </is>
       </c>
       <c r="F211" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_01_analysing_statistical_claims_in_media_v2.html</t>
+          <t>y10_spa_08_algorithms_for_spatial_design_v2.html</t>
         </is>
       </c>
       <c r="G211" s="15" t="inlineStr">
         <is>
-          <t>AC9M10ST01</t>
+          <t>AC9M10SP03</t>
         </is>
       </c>
       <c r="H211" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4,5</t>
         </is>
       </c>
       <c r="I211" s="15" t="inlineStr">
@@ -16700,12 +16725,12 @@
       </c>
       <c r="J211" s="15" t="inlineStr">
         <is>
-          <t>Claims and inferences based on data should acknowledge ethical considerations and potential sources of bias</t>
+          <t>Situations involving angles, distance and direction can be quantified using geometric properties and theorems</t>
         </is>
       </c>
       <c r="K211" s="15" t="inlineStr">
         <is>
-          <t>Identify potentially misleading representations in the media — graphs with broken axes, scales that do not start at zero, nonlinear scales presented as linear; recognise when data is not related to the claim, not representative of the population, or is being used selectively; investigate the source and size of the sample from which the data was collected and assess whether it is appropriately representative.</t>
+          <t>Design and make scale models of three-dimensional objects using digital tools (e.g. 3D-printable puzzle components using tessellations); define and decompose spatial problems and create algorithms — for example, a floor plan that limits congestion at checkouts; test algorithms in pseudocode or flow charts; produce self-similar patterns and validate algorithms with multiple test cases; explore geospatial technologies used by First Nations Australians' communities.</t>
         </is>
       </c>
       <c r="L211" s="15" t="inlineStr">
@@ -16715,7 +16740,7 @@
       </c>
       <c r="M211" s="15" t="inlineStr">
         <is>
-          <t>y9_sta_01</t>
+          <t>y10_spa_07</t>
         </is>
       </c>
       <c r="N211" s="15" t="inlineStr">
@@ -16725,14 +16750,14 @@
       </c>
       <c r="Q211" s="15" t="inlineStr">
         <is>
-          <t>Strategy-MCQ suits 'is this claim supported?' question type. Extends Y9 sta_01 (analysing statistical reports) with the Y10 ethical/misleading-representation focus.</t>
+          <t>Strategy-MCQ for the algorithm-choice content. Broad capstone — covers four elaborations spanning 3D modelling, floor planning, fractal generation and First Nations geospatial techniques.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" s="16">
       <c r="A212" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_02</t>
+          <t>y10_sta_01</t>
         </is>
       </c>
       <c r="B212" s="15" t="n">
@@ -16744,16 +16769,16 @@
         </is>
       </c>
       <c r="D212" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E212" s="15" t="inlineStr">
         <is>
-          <t>ethical_considerations_and_indigenous_data_sovereignty</t>
+          <t>analysing_statistical_claims_in_media</t>
         </is>
       </c>
       <c r="F212" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_02_ethical_considerations_and_indigenous_data_sovereignty_v2.html</t>
+          <t>y10_sta_01_analysing_statistical_claims_in_media_v2.html</t>
         </is>
       </c>
       <c r="G212" s="15" t="inlineStr">
@@ -16763,7 +16788,7 @@
       </c>
       <c r="H212" s="15" t="inlineStr">
         <is>
-          <t>3,4,5</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I212" s="15" t="inlineStr">
@@ -16778,17 +16803,17 @@
       </c>
       <c r="K212" s="15" t="inlineStr">
         <is>
-          <t>Investigate population rates and discuss ethical considerations when presenting infection rates and cases per head of population; use secondary data to predict the number of people likely to be infected with a flu strain or to experience medication side effects; apply the concept of Indigenous Data Sovereignty to critique and evaluate the Australian Government's Closing the Gap report.</t>
+          <t>Identify potentially misleading representations in the media — graphs with broken axes, scales that do not start at zero, nonlinear scales presented as linear; recognise when data is not related to the claim, not representative of the population, or is being used selectively; investigate the source and size of the sample from which the data was collected and assess whether it is appropriately representative.</t>
         </is>
       </c>
       <c r="L212" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>strategy-MCQ</t>
         </is>
       </c>
       <c r="M212" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_01</t>
+          <t>y9_sta_01</t>
         </is>
       </c>
       <c r="N212" s="15" t="inlineStr">
@@ -16798,14 +16823,14 @@
       </c>
       <c r="Q212" s="15" t="inlineStr">
         <is>
-          <t>Open-ended modelling — the Indigenous Data Sovereignty content invites discussion responses alongside numeric work.</t>
+          <t>Strategy-MCQ suits 'is this claim supported?' question type. Extends Y9 sta_01 (analysing statistical reports) with the Y10 ethical/misleading-representation focus.</t>
         </is>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" s="16">
       <c r="A213" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_03</t>
+          <t>y10_sta_02</t>
         </is>
       </c>
       <c r="B213" s="15" t="n">
@@ -16817,26 +16842,26 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E213" s="15" t="inlineStr">
         <is>
-          <t>five_number_summary_and_box_plots</t>
+          <t>ethical_considerations_and_indigenous_data_sovereignty</t>
         </is>
       </c>
       <c r="F213" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_03_five_number_summary_and_box_plots_v2.html</t>
+          <t>y10_sta_02_ethical_considerations_and_indigenous_data_sovereignty_v2.html</t>
         </is>
       </c>
       <c r="G213" s="15" t="inlineStr">
         <is>
-          <t>AC9M10ST02</t>
+          <t>AC9M10ST01</t>
         </is>
       </c>
       <c r="H213" s="15" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>3,4,5</t>
         </is>
       </c>
       <c r="I213" s="15" t="inlineStr">
@@ -16846,22 +16871,22 @@
       </c>
       <c r="J213" s="15" t="inlineStr">
         <is>
-          <t>Data can be represented in different ways to establish relationships, while considering accuracy and bias</t>
+          <t>Claims and inferences based on data should acknowledge ethical considerations and potential sources of bias</t>
         </is>
       </c>
       <c r="K213" s="15" t="inlineStr">
         <is>
-          <t>Find the five-number summary (minimum, lower quartile Q1, median, upper quartile Q3, maximum) for a numerical data set; calculate the interquartile range IQR = Q3 − Q1; construct a box plot from the five-number summary; interpret each component of the plot and identify outliers using the 1.5 × IQR convention.</t>
+          <t>Investigate population rates and discuss ethical considerations when presenting infection rates and cases per head of population; use secondary data to predict the number of people likely to be infected with a flu strain or to experience medication side effects; apply the concept of Indigenous Data Sovereignty to critique and evaluate the Australian Government's Closing the Gap report.</t>
         </is>
       </c>
       <c r="L213" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M213" s="15" t="inlineStr">
         <is>
-          <t>y7_sta_01,y8_sta_03</t>
+          <t>y10_sta_01</t>
         </is>
       </c>
       <c r="N213" s="15" t="inlineStr">
@@ -16871,14 +16896,14 @@
       </c>
       <c r="Q213" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — no Y7-9 precedent for box plots. Cross-strand prereqs: Y7 sta_01 (median, mode, range) and Y8 sta_03 (sampling methods).</t>
+          <t>Open-ended modelling — the Indigenous Data Sovereignty content invites discussion responses alongside numeric work.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" s="16">
       <c r="A214" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_04</t>
+          <t>y10_sta_03</t>
         </is>
       </c>
       <c r="B214" s="15" t="n">
@@ -16890,16 +16915,16 @@
         </is>
       </c>
       <c r="D214" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E214" s="15" t="inlineStr">
         <is>
-          <t>comparing_distributions_with_box_plots</t>
+          <t>five_number_summary_and_box_plots</t>
         </is>
       </c>
       <c r="F214" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_04_comparing_distributions_with_box_plots_v2.html</t>
+          <t>y10_sta_03_five_number_summary_and_box_plots_v2.html</t>
         </is>
       </c>
       <c r="G214" s="15" t="inlineStr">
@@ -16909,7 +16934,7 @@
       </c>
       <c r="H214" s="15" t="inlineStr">
         <is>
-          <t>2,3,5</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I214" s="15" t="inlineStr">
@@ -16924,7 +16949,7 @@
       </c>
       <c r="K214" s="15" t="inlineStr">
         <is>
-          <t>Compare two or more distributions for continuous numerical variables using parallel box plots; discuss shape (symmetry, skew, modality), centre and spread; use digital tools to compare box plots with histograms, cumulative frequency graphs and dot plots of the same data; comment on which display answers a given statistical question most effectively.</t>
+          <t>Find the five-number summary (minimum, lower quartile Q1, median, upper quartile Q3, maximum) for a numerical data set; calculate the interquartile range IQR = Q3 − Q1; construct a box plot from the five-number summary; interpret each component of the plot and identify outliers using the 1.5 × IQR convention.</t>
         </is>
       </c>
       <c r="L214" s="15" t="inlineStr">
@@ -16934,7 +16959,7 @@
       </c>
       <c r="M214" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_03</t>
+          <t>y7_sta_01,y8_sta_03</t>
         </is>
       </c>
       <c r="N214" s="15" t="inlineStr">
@@ -16944,14 +16969,14 @@
       </c>
       <c r="Q214" s="15" t="inlineStr">
         <is>
-          <t>Builds directly on y10_sta_03 — the comparison skill is the practical pay-off of box plot fluency.</t>
+          <t>Watershed lesson — no Y7-9 precedent for box plots. Cross-strand prereqs: Y7 sta_01 (median, mode, range) and Y8 sta_03 (sampling methods).</t>
         </is>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" s="16">
       <c r="A215" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_05</t>
+          <t>y10_sta_04</t>
         </is>
       </c>
       <c r="B215" s="15" t="n">
@@ -16963,26 +16988,26 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E215" s="15" t="inlineStr">
         <is>
-          <t>constructing_and_interpreting_scatterplots</t>
+          <t>comparing_distributions_with_box_plots</t>
         </is>
       </c>
       <c r="F215" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_05_constructing_and_interpreting_scatterplots_v2.html</t>
+          <t>y10_sta_04_comparing_distributions_with_box_plots_v2.html</t>
         </is>
       </c>
       <c r="G215" s="15" t="inlineStr">
         <is>
-          <t>AC9M10ST03</t>
+          <t>AC9M10ST02</t>
         </is>
       </c>
       <c r="H215" s="15" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,3,5</t>
         </is>
       </c>
       <c r="I215" s="15" t="inlineStr">
@@ -16997,7 +17022,7 @@
       </c>
       <c r="K215" s="15" t="inlineStr">
         <is>
-          <t>Construct a scatterplot from a bivariate data set; describe the association between the two numerical variables in terms of direction (positive, negative, none), strength (strong, moderate, weak) and linearity (linear, non-linear); investigate the relationship between two variables of spear throwers used by Australian First Nations Peoples and construct a scatterplot to compare and draw conclusions.</t>
+          <t>Compare two or more distributions for continuous numerical variables using parallel box plots; discuss shape (symmetry, skew, modality), centre and spread; use digital tools to compare box plots with histograms, cumulative frequency graphs and dot plots of the same data; comment on which display answers a given statistical question most effectively.</t>
         </is>
       </c>
       <c r="L215" s="15" t="inlineStr">
@@ -17007,7 +17032,7 @@
       </c>
       <c r="M215" s="15" t="inlineStr">
         <is>
-          <t>y7_alg_09</t>
+          <t>y10_sta_03</t>
         </is>
       </c>
       <c r="N215" s="15" t="inlineStr">
@@ -17017,14 +17042,14 @@
       </c>
       <c r="Q215" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — no Y7-9 precedent for bivariate data. Cross-strand prereq: Y7 alg_09 (Cartesian plotting).</t>
+          <t>Builds directly on y10_sta_03 — the comparison skill is the practical pay-off of box plot fluency.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" s="16">
       <c r="A216" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_06</t>
+          <t>y10_sta_05</t>
         </is>
       </c>
       <c r="B216" s="15" t="n">
@@ -17036,16 +17061,16 @@
         </is>
       </c>
       <c r="D216" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E216" s="15" t="inlineStr">
         <is>
-          <t>line_of_best_fit_and_association_versus_causation</t>
+          <t>constructing_and_interpreting_scatterplots</t>
         </is>
       </c>
       <c r="F216" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_06_line_of_best_fit_and_association_versus_causation_v2.html</t>
+          <t>y10_sta_05_constructing_and_interpreting_scatterplots_v2.html</t>
         </is>
       </c>
       <c r="G216" s="15" t="inlineStr">
@@ -17055,7 +17080,7 @@
       </c>
       <c r="H216" s="15" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I216" s="15" t="inlineStr">
@@ -17070,17 +17095,17 @@
       </c>
       <c r="K216" s="15" t="inlineStr">
         <is>
-          <t>Informally draw a line of good fit by eye on a scatterplot; use the line to make predictions and discuss the reliability of those predictions (interpolation versus extrapolation); use statistical evidence to make, justify and critique claims about association between variables in contexts such as climate change, migration, online shopping and social media; distinguish association from cause-and-effect.</t>
+          <t>Construct a scatterplot from a bivariate data set; describe the association between the two numerical variables in terms of direction (positive, negative, none), strength (strong, moderate, weak) and linearity (linear, non-linear); investigate the relationship between two variables of spear throwers used by Australian First Nations Peoples and construct a scatterplot to compare and draw conclusions.</t>
         </is>
       </c>
       <c r="L216" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M216" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_05</t>
+          <t>y7_alg_09</t>
         </is>
       </c>
       <c r="N216" s="15" t="inlineStr">
@@ -17090,14 +17115,14 @@
       </c>
       <c r="Q216" s="15" t="inlineStr">
         <is>
-          <t>Association-vs-causation discussion benefits from open-ended responses alongside the auto-marked line-fitting work.</t>
+          <t>Watershed lesson — no Y7-9 precedent for bivariate data. Cross-strand prereq: Y7 alg_09 (Cartesian plotting).</t>
         </is>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" s="16">
       <c r="A217" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_07</t>
+          <t>y10_sta_06</t>
         </is>
       </c>
       <c r="B217" s="15" t="n">
@@ -17109,26 +17134,26 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E217" s="15" t="inlineStr">
         <is>
-          <t>two_way_tables_for_categorical_relationships</t>
+          <t>line_of_best_fit_and_association_versus_causation</t>
         </is>
       </c>
       <c r="F217" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_07_two_way_tables_for_categorical_relationships_v2.html</t>
+          <t>y10_sta_06_line_of_best_fit_and_association_versus_causation_v2.html</t>
         </is>
       </c>
       <c r="G217" s="15" t="inlineStr">
         <is>
-          <t>AC9M10ST04</t>
+          <t>AC9M10ST03</t>
         </is>
       </c>
       <c r="H217" s="15" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I217" s="15" t="inlineStr">
@@ -17143,17 +17168,17 @@
       </c>
       <c r="K217" s="15" t="inlineStr">
         <is>
-          <t>Construct two-way tables to record responses to questions involving categorical variables — e.g. a five-point Likert-scale survey crossed against junior versus senior respondents; use percentages and proportions within rows and columns to identify patterns and possible associations between the categorical variables; conduct a school-context investigation such as a litter survey crossed with day-of-week or weather.</t>
+          <t>Informally draw a line of good fit by eye on a scatterplot; use the line to make predictions and discuss the reliability of those predictions (interpolation versus extrapolation); use statistical evidence to make, justify and critique claims about association between variables in contexts such as climate change, migration, online shopping and social media; distinguish association from cause-and-effect.</t>
         </is>
       </c>
       <c r="L217" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M217" s="15" t="inlineStr">
         <is>
-          <t>y8_pro_02</t>
+          <t>y10_sta_05</t>
         </is>
       </c>
       <c r="N217" s="15" t="inlineStr">
@@ -17163,14 +17188,14 @@
       </c>
       <c r="Q217" s="15" t="inlineStr">
         <is>
-          <t>Extends Y8 pro_02 (two-way tables for probability) into the statistical/categorical-association framing. Statistical inference rather than probability calculation.</t>
+          <t>Association-vs-causation discussion benefits from open-ended responses alongside the auto-marked line-fitting work.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" s="16">
       <c r="A218" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_08</t>
+          <t>y10_sta_07</t>
         </is>
       </c>
       <c r="B218" s="15" t="n">
@@ -17182,26 +17207,26 @@
         </is>
       </c>
       <c r="D218" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E218" s="15" t="inlineStr">
         <is>
-          <t>full_bivariate_statistical_investigation</t>
+          <t>two_way_tables_for_categorical_relationships</t>
         </is>
       </c>
       <c r="F218" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_08_full_bivariate_statistical_investigation_v2.html</t>
+          <t>y10_sta_07_two_way_tables_for_categorical_relationships_v2.html</t>
         </is>
       </c>
       <c r="G218" s="15" t="inlineStr">
         <is>
-          <t>AC9M10ST05</t>
+          <t>AC9M10ST04</t>
         </is>
       </c>
       <c r="H218" s="15" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I218" s="15" t="inlineStr">
@@ -17216,17 +17241,17 @@
       </c>
       <c r="K218" s="15" t="inlineStr">
         <is>
-          <t>Plan and conduct a full bivariate statistical investigation — design a study that collects bivariate data over time via observation, experiment or measurement; graph, interpret and analyse the data; report findings with explicit acknowledgement of limitations including interpolation and extrapolation; investigate contexts such as the vaccines-immunity relationship, anecdotal claims about climate or housing affordability, and biodiversity changes in Australia before and after colonisation.</t>
+          <t>Construct two-way tables to record responses to questions involving categorical variables — e.g. a five-point Likert-scale survey crossed against junior versus senior respondents; use percentages and proportions within rows and columns to identify patterns and possible associations between the categorical variables; conduct a school-context investigation such as a litter survey crossed with day-of-week or weather.</t>
         </is>
       </c>
       <c r="L218" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M218" s="15" t="inlineStr">
         <is>
-          <t>y10_sta_04,y10_sta_06</t>
+          <t>y8_pro_02</t>
         </is>
       </c>
       <c r="N218" s="15" t="inlineStr">
@@ -17236,14 +17261,14 @@
       </c>
       <c r="Q218" s="15" t="inlineStr">
         <is>
-          <t>Capstone — extends Y7 sta_05, Y8 sta_06 and Y9 sta_06 statistical investigation lessons with explicit bivariate-data focus.</t>
+          <t>Extends Y8 pro_02 (two-way tables for probability) into the statistical/categorical-association framing. Statistical inference rather than probability calculation.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" s="16">
       <c r="A219" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_01</t>
+          <t>y10_sta_08</t>
         </is>
       </c>
       <c r="B219" s="15" t="n">
@@ -17251,30 +17276,30 @@
       </c>
       <c r="C219" s="15" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E219" s="15" t="inlineStr">
         <is>
-          <t>introducing_conditional_probability_language</t>
+          <t>full_bivariate_statistical_investigation</t>
         </is>
       </c>
       <c r="F219" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_01_introducing_conditional_probability_language_v2.html</t>
+          <t>y10_sta_08_full_bivariate_statistical_investigation_v2.html</t>
         </is>
       </c>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>AC9M10P01</t>
+          <t>AC9M10ST05</t>
         </is>
       </c>
       <c r="H219" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I219" s="15" t="inlineStr">
@@ -17284,22 +17309,22 @@
       </c>
       <c r="J219" s="15" t="inlineStr">
         <is>
-          <t>Conditional probability can be described and interpreted for multiple events and applied in real-life contexts</t>
+          <t>Data can be represented in different ways to establish relationships, while considering accuracy and bias</t>
         </is>
       </c>
       <c r="K219" s="15" t="inlineStr">
         <is>
-          <t>Interpret conditional statements using the language of probability — "if A then B", "the probability of A given B", "of those who…", "knowing that"; use two-way tables and Venn diagrams to read off conditional probabilities directly; identify common mistakes in conditional language (P(A|B) versus P(B|A) confusion).</t>
+          <t>Plan and conduct a full bivariate statistical investigation — design a study that collects bivariate data over time via observation, experiment or measurement; graph, interpret and analyse the data; report findings with explicit acknowledgement of limitations including interpolation and extrapolation; investigate contexts such as the vaccines-immunity relationship, anecdotal claims about climate or housing affordability, and biodiversity changes in Australia before and after colonisation.</t>
         </is>
       </c>
       <c r="L219" s="15" t="inlineStr">
         <is>
-          <t>auto-marked</t>
+          <t>auto-marked + open-ended</t>
         </is>
       </c>
       <c r="M219" s="15" t="inlineStr">
         <is>
-          <t>y8_pro_02</t>
+          <t>y10_sta_04,y10_sta_06</t>
         </is>
       </c>
       <c r="N219" s="15" t="inlineStr">
@@ -17309,14 +17334,14 @@
       </c>
       <c r="Q219" s="15" t="inlineStr">
         <is>
-          <t>Watershed lesson — first formal treatment of conditional probability (Sam-flagged). Builds on Y8 pro_02 (two-way tables and Venn diagrams) and Y9 pro_03 (relative frequency for 'and'/'or' events).</t>
+          <t>Capstone — extends Y7 sta_05, Y8 sta_06 and Y9 sta_06 statistical investigation lessons with explicit bivariate-data focus.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" s="16">
       <c r="A220" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_02</t>
+          <t>y10_pro_01</t>
         </is>
       </c>
       <c r="B220" s="15" t="n">
@@ -17328,16 +17353,16 @@
         </is>
       </c>
       <c r="D220" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220" s="15" t="inlineStr">
         <is>
-          <t>dependent_and_independent_events_with_tree_diagrams</t>
+          <t>introducing_conditional_probability_language</t>
         </is>
       </c>
       <c r="F220" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_02_dependent_and_independent_events_with_tree_diagrams_v2.html</t>
+          <t>y10_pro_01_introducing_conditional_probability_language_v2.html</t>
         </is>
       </c>
       <c r="G220" s="15" t="inlineStr">
@@ -17347,7 +17372,7 @@
       </c>
       <c r="H220" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I220" s="15" t="inlineStr">
@@ -17362,7 +17387,7 @@
       </c>
       <c r="K220" s="15" t="inlineStr">
         <is>
-          <t>Use arrays and tree diagrams to represent, interpret and compare probabilities of dependent and independent events; recognise when two events are independent (P(A and B) = P(A) × P(B)) versus dependent (multiply along branch but probability changes between stages); contrast with-replacement (independent) and without-replacement (dependent) scenarios.</t>
+          <t>Interpret conditional statements using the language of probability — "if A then B", "the probability of A given B", "of those who…", "knowing that"; use two-way tables and Venn diagrams to read off conditional probabilities directly; identify common mistakes in conditional language (P(A|B) versus P(B|A) confusion).</t>
         </is>
       </c>
       <c r="L220" s="15" t="inlineStr">
@@ -17372,7 +17397,7 @@
       </c>
       <c r="M220" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_01,y9_pro_02</t>
+          <t>y8_pro_02</t>
         </is>
       </c>
       <c r="N220" s="15" t="inlineStr">
@@ -17382,14 +17407,14 @@
       </c>
       <c r="Q220" s="15" t="inlineStr">
         <is>
-          <t>Cross-strand prereq: Y9 pro_02 (tree diagrams with/without replacement) — Y9 work was informal, Y10 formalises the dependent/independent distinction.</t>
+          <t>Watershed lesson — first formal treatment of conditional probability (Sam-flagged). Builds on Y8 pro_02 (two-way tables and Venn diagrams) and Y9 pro_03 (relative frequency for 'and'/'or' events).</t>
         </is>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="16">
       <c r="A221" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_03</t>
+          <t>y10_pro_02</t>
         </is>
       </c>
       <c r="B221" s="15" t="n">
@@ -17401,26 +17426,26 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E221" s="15" t="inlineStr">
         <is>
-          <t>simulations_with_and_without_replacement</t>
+          <t>dependent_and_independent_events_with_tree_diagrams</t>
         </is>
       </c>
       <c r="F221" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_03_simulations_with_and_without_replacement_v2.html</t>
+          <t>y10_pro_02_dependent_and_independent_events_with_tree_diagrams_v2.html</t>
         </is>
       </c>
       <c r="G221" s="15" t="inlineStr">
         <is>
-          <t>AC9M10P02</t>
+          <t>AC9M10P01</t>
         </is>
       </c>
       <c r="H221" s="15" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I221" s="15" t="inlineStr">
@@ -17430,22 +17455,22 @@
       </c>
       <c r="J221" s="15" t="inlineStr">
         <is>
-          <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
+          <t>Conditional probability can be described and interpreted for multiple events and applied in real-life contexts</t>
         </is>
       </c>
       <c r="K221" s="15" t="inlineStr">
         <is>
-          <t>Use digital simulations to draw samples of different sizes with and without replacement from a known population; identify the sample size at which the difference between with- and without-replacement methods becomes negligible (rule of thumb: population at least 10× sample size); recognise how event dependence affects the way probability is calculated.</t>
+          <t>Use arrays and tree diagrams to represent, interpret and compare probabilities of dependent and independent events; recognise when two events are independent (P(A and B) = P(A) × P(B)) versus dependent (multiply along branch but probability changes between stages); contrast with-replacement (independent) and without-replacement (dependent) scenarios.</t>
         </is>
       </c>
       <c r="L221" s="15" t="inlineStr">
         <is>
-          <t>auto-marked + open-ended</t>
+          <t>auto-marked</t>
         </is>
       </c>
       <c r="M221" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_02</t>
+          <t>y10_pro_01,y9_pro_02</t>
         </is>
       </c>
       <c r="N221" s="15" t="inlineStr">
@@ -17455,14 +17480,14 @@
       </c>
       <c r="Q221" s="15" t="inlineStr">
         <is>
-          <t>Practical extension of y10_pro_02 — the simulation makes the abstract dependence/independence distinction concrete.</t>
+          <t>Cross-strand prereq: Y9 pro_02 (tree diagrams with/without replacement) — Y9 work was informal, Y10 formalises the dependent/independent distinction.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" s="16">
       <c r="A222" s="15" t="inlineStr">
         <is>
-          <t>y10_pro_04</t>
+          <t>y10_pro_03</t>
         </is>
       </c>
       <c r="B222" s="15" t="n">
@@ -17474,67 +17499,136 @@
         </is>
       </c>
       <c r="D222" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E222" s="15" t="inlineStr">
+        <is>
+          <t>simulations_with_and_without_replacement</t>
+        </is>
+      </c>
+      <c r="F222" s="15" t="inlineStr">
+        <is>
+          <t>y10_pro_03_simulations_with_and_without_replacement_v2.html</t>
+        </is>
+      </c>
+      <c r="G222" s="15" t="inlineStr">
+        <is>
+          <t>AC9M10P02</t>
+        </is>
+      </c>
+      <c r="H222" s="15" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I222" s="15" t="inlineStr">
+        <is>
+          <t>Strict</t>
+        </is>
+      </c>
+      <c r="J222" s="15" t="inlineStr">
+        <is>
+          <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
+        </is>
+      </c>
+      <c r="K222" s="15" t="inlineStr">
+        <is>
+          <t>Use digital simulations to draw samples of different sizes with and without replacement from a known population; identify the sample size at which the difference between with- and without-replacement methods becomes negligible (rule of thumb: population at least 10× sample size); recognise how event dependence affects the way probability is calculated.</t>
+        </is>
+      </c>
+      <c r="L222" s="15" t="inlineStr">
+        <is>
+          <t>auto-marked + open-ended</t>
+        </is>
+      </c>
+      <c r="M222" s="15" t="inlineStr">
+        <is>
+          <t>y10_pro_02</t>
+        </is>
+      </c>
+      <c r="N222" s="15" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q222" s="15" t="inlineStr">
+        <is>
+          <t>Practical extension of y10_pro_02 — the simulation makes the abstract dependence/independence distinction concrete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="15" customHeight="1" s="16">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>y10_pro_04</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>10</v>
+      </c>
+      <c r="C223" s="15" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
         <v>4</v>
       </c>
-      <c r="E222" s="15" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>counter_intuitive_and_decision_simulations</t>
         </is>
       </c>
-      <c r="F222" s="15" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>y10_pro_04_counter_intuitive_and_decision_simulations_v2.html</t>
         </is>
       </c>
-      <c r="G222" s="15" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>AC9M10P02</t>
         </is>
       </c>
-      <c r="H222" s="15" t="inlineStr">
+      <c r="H223" t="inlineStr">
         <is>
           <t>3,4,5</t>
         </is>
       </c>
-      <c r="I222" s="15" t="inlineStr">
+      <c r="I223" s="15" t="inlineStr">
         <is>
           <t>Strict</t>
         </is>
       </c>
-      <c r="J222" s="15" t="inlineStr">
+      <c r="J223" t="inlineStr">
         <is>
           <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
         </is>
       </c>
-      <c r="K222" s="15" t="inlineStr">
+      <c r="K223" t="inlineStr">
         <is>
           <t>Use simulations to gather data on counter-intuitive probability situations — the Monty Hall (three-door) problem and the birthday problem; identify situations in real life where probability simulations support decision-making such as queueing theory, insurance risk pricing and supply-and-demand for a product; use simulation to predict the number of people likely to be infected with a flu strain or virus.</t>
         </is>
       </c>
-      <c r="L222" s="15" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M222" s="15" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t>y10_pro_03</t>
         </is>
       </c>
-      <c r="N222" s="15" t="inlineStr">
+      <c r="N223" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q222" s="15" t="inlineStr">
+      <c r="Q223" t="inlineStr">
         <is>
           <t>Capstone probability lesson for Y10 — combines famous counter-intuitive problems with applied decision-making contexts. Builds on simulation work from Y7 pro_03, Y8 pro_04, Y9 pro_04.</t>
         </is>
       </c>
-    </row>
-    <row r="223" ht="15" customHeight="1" s="16">
-      <c r="C223" s="15" t="n"/>
-      <c r="I223" s="15" t="n"/>
     </row>
     <row r="224" ht="15" customHeight="1" s="16">
       <c r="C224" s="15" t="n"/>

--- a/lessonmap.xlsx
+++ b/lessonmap.xlsx
@@ -10849,12 +10849,22 @@
       </c>
       <c r="N129" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_07_gradient_of_a_line_segment_v2.html</t>
         </is>
       </c>
       <c r="Q129" s="15" t="inlineStr">
         <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03. Gradient given its own lesson under the 18-plan.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-03. Gradient given its own lesson under the 18-plan.</t>
         </is>
       </c>
     </row>
@@ -10922,12 +10932,22 @@
       </c>
       <c r="N130" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03. Builds on Y8 Pythagoras (y8_mea_11).</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_08_midpoint_and_distance_v2.html</t>
+        </is>
+      </c>
+      <c r="Q130" s="15" t="inlineStr">
+        <is>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-03. Builds on Y8 Pythagoras (y8_mea_11).</t>
         </is>
       </c>
     </row>
@@ -10995,12 +11015,22 @@
       </c>
       <c r="N131" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_09_parallel_and_perpendicular_lines_v2.html</t>
         </is>
       </c>
       <c r="Q131" s="15" t="inlineStr">
         <is>
-          <t>NEW gap-fill: A03 elaboration 2 (parallel/perpendicular) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03.</t>
+          <t>NEW gap-fill: A03 elaboration 2 (parallel/perpendicular) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-03.</t>
         </is>
       </c>
     </row>
@@ -11068,12 +11098,22 @@
       </c>
       <c r="N132" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_10_graphing_quadratic_functions_v2.html</t>
         </is>
       </c>
       <c r="Q132" s="15" t="inlineStr">
         <is>
-          <t>Watershed: first formal non-linear function. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-03.</t>
+          <t>Watershed: first formal non-linear function. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-03.</t>
         </is>
       </c>
     </row>
@@ -11141,12 +11181,22 @@
       </c>
       <c r="N133" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_11_solving_quadratics_graphically_v2.html</t>
         </is>
       </c>
       <c r="Q133" s="15" t="inlineStr">
         <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Moon-phase elaboration 7 added. Batch y9-alg-04.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Moon-phase elaboration 7 added. Batch y9-alg-04.</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11264,22 @@
       </c>
       <c r="N134" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_12_solving_monic_quadratics_algebraically_v2.html</t>
         </is>
       </c>
       <c r="Q134" s="15" t="inlineStr">
         <is>
-          <t>Parabola figure added (fix - was the one solving lesson with no figure). Null factor law folded in here. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-04.</t>
+          <t>Parabola figure added (fix - was the one solving lesson with no figure). Null factor law folded in here. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-04.</t>
         </is>
       </c>
     </row>
@@ -11287,12 +11347,22 @@
       </c>
       <c r="N135" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_13_modelling_with_linear_functions_v2.html</t>
         </is>
       </c>
       <c r="Q135" s="15" t="inlineStr">
         <is>
-          <t>A05 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
+          <t>A05 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11360,12 +11430,22 @@
       </c>
       <c r="N136" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_14_modelling_with_quadratic_functions_v2.html</t>
         </is>
       </c>
       <c r="Q136" s="15" t="inlineStr">
         <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11433,12 +11513,22 @@
       </c>
       <c r="N137" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_15_choosing_linear_or_quadratic_models_v2.html</t>
         </is>
       </c>
       <c r="Q137" s="15" t="inlineStr">
         <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-05.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-05.</t>
         </is>
       </c>
     </row>
@@ -11506,12 +11596,22 @@
       </c>
       <c r="N138" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_16_transformations_of_linear_graphs_v2.html</t>
         </is>
       </c>
       <c r="Q138" s="15" t="inlineStr">
         <is>
-          <t>A06 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
+          <t>A06 restored to 3 lessons under the 18-plan (was 1 combined lesson). Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
@@ -11579,12 +11679,22 @@
       </c>
       <c r="N139" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_17_transformations_of_quadratic_graphs_v2.html</t>
         </is>
       </c>
       <c r="Q139" s="15" t="inlineStr">
         <is>
-          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
+          <t>Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
@@ -11645,19 +11755,29 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
+      <c r="M140" s="15" t="inlineStr">
         <is>
           <t>y9_alg_16,y9_alg_17</t>
         </is>
       </c>
       <c r="N140" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-9/algebra/y9_alg_18_families_of_functions_v2.html</t>
         </is>
       </c>
       <c r="Q140" s="15" t="inlineStr">
         <is>
-          <t>NEW gap-fill: A06 elaboration 3 (function families) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Status Planned; tags/elaborations to be confirmed from file &lt;meta&gt; at build closeout. Batch y9-alg-06.</t>
+          <t>NEW gap-fill: A06 elaboration 3 (function families) was uncovered in the earlier 13-lesson build. Re-mapped 2026-06-01 to the 18-lesson Y9 Algebra plan (go-18 decision). Built and published; metadata confirmed present in file &lt;meta&gt; per generation summary. Batch y9-alg-06.</t>
         </is>
       </c>
     </row>
@@ -11943,7 +12063,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr">
+      <c r="Q144" s="15" t="inlineStr">
         <is>
           <t>Cross-strand prereq: needs y9_alg_01 negative exponents. Important sequencing — Algebra first, then Measurement.</t>
         </is>
@@ -12221,7 +12341,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
+      <c r="M148" s="15" t="inlineStr">
         <is>
           <t>y9_mea_06,y9_mea_07</t>
         </is>
@@ -12231,7 +12351,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr">
+      <c r="Q148" s="15" t="inlineStr">
         <is>
           <t>Integration lesson — open-ended practice fits the conjecture/investigation flavour.</t>
         </is>
@@ -12358,7 +12478,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
+      <c r="M150" s="15" t="inlineStr">
         <is>
           <t>y9_mea_09</t>
         </is>
@@ -12433,7 +12553,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr">
+      <c r="Q151" s="15" t="inlineStr">
         <is>
           <t>Extends Y8 mea_14 scale and proportion work; Y9 adds the formal modelling cycle.</t>
         </is>
@@ -12496,7 +12616,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
+      <c r="M152" s="15" t="inlineStr">
         <is>
           <t>y9_mea_11</t>
         </is>
@@ -12707,7 +12827,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
+      <c r="M155" s="15" t="inlineStr">
         <is>
           <t>y9_spa_02</t>
         </is>
@@ -12849,7 +12969,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
+      <c r="M157" s="15" t="inlineStr">
         <is>
           <t>y9_spa_04</t>
         </is>
@@ -12928,7 +13048,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
+      <c r="Q158" s="15" t="inlineStr">
         <is>
           <t>Strategy-MCQ matches the decision-tree algorithm-design content.</t>
         </is>
@@ -12991,7 +13111,7 @@
           <t>strategy-MCQ</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
+      <c r="M159" s="15" t="inlineStr">
         <is>
           <t>y9_spa_06</t>
         </is>
@@ -13129,7 +13249,7 @@
           <t>strategy-MCQ</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
+      <c r="M161" s="15" t="inlineStr">
         <is>
           <t>y9_sta_01</t>
         </is>
@@ -13208,7 +13328,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr">
+      <c r="Q162" s="15" t="inlineStr">
         <is>
           <t>Builds on Y8 sta_04/05 sampling and distribution work.</t>
         </is>
@@ -13413,7 +13533,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr">
+      <c r="M165" s="15" t="inlineStr">
         <is>
           <t>y9_sta_05</t>
         </is>
@@ -13565,7 +13685,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
+      <c r="Q167" s="15" t="inlineStr">
         <is>
           <t>With/without replacement is the watershed concept — introduces conditional probability informally.</t>
         </is>
@@ -13697,7 +13817,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr">
+      <c r="M169" s="15" t="inlineStr">
         <is>
           <t>y9_pro_02,y9_pro_03</t>
         </is>
@@ -13839,7 +13959,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
+      <c r="M171" s="15" t="inlineStr">
         <is>
           <t>y10_num_01</t>
         </is>
@@ -14127,7 +14247,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
+      <c r="M175" s="15" t="inlineStr">
         <is>
           <t>y10_alg_02,y10_alg_03</t>
         </is>
@@ -14858,7 +14978,7 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr">
+      <c r="Q185" s="15" t="inlineStr">
         <is>
           <t>Synthesis lesson — pulls together diagnostic skills from Y8 alg_05 (linear), Y9 alg_09 (quadratic) and y10_alg_11 (exponential).</t>
         </is>
@@ -16377,7 +16497,7 @@
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
+      <c r="M206" s="15" t="inlineStr">
         <is>
           <t>y10_spa_02,y8_spa_03</t>
         </is>
@@ -17558,12 +17678,12 @@
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" s="16">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="15" t="inlineStr">
         <is>
           <t>y10_pro_04</t>
         </is>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="15" t="n">
         <v>10</v>
       </c>
       <c r="C223" s="15" t="inlineStr">
@@ -17571,25 +17691,25 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="15" t="inlineStr">
         <is>
           <t>counter_intuitive_and_decision_simulations</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" s="15" t="inlineStr">
         <is>
           <t>y10_pro_04_counter_intuitive_and_decision_simulations_v2.html</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G223" s="15" t="inlineStr">
         <is>
           <t>AC9M10P02</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H223" s="15" t="inlineStr">
         <is>
           <t>3,4,5</t>
         </is>
@@ -17599,32 +17719,32 @@
           <t>Strict</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
+      <c r="J223" s="15" t="inlineStr">
         <is>
           <t>The likelihood of an event occurring can be affected by another event that has already taken place</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K223" s="15" t="inlineStr">
         <is>
           <t>Use simulations to gather data on counter-intuitive probability situations — the Monty Hall (three-door) problem and the birthday problem; identify situations in real life where probability simulations support decision-making such as queueing theory, insurance risk pricing and supply-and-demand for a product; use simulation to predict the number of people likely to be infected with a flu strain or virus.</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="L223" s="15" t="inlineStr">
         <is>
           <t>auto-marked + open-ended</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
+      <c r="M223" s="15" t="inlineStr">
         <is>
           <t>y10_pro_03</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr">
+      <c r="N223" s="15" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="Q223" t="inlineStr">
+      <c r="Q223" s="15" t="inlineStr">
         <is>
           <t>Capstone probability lesson for Y10 — combines famous counter-intuitive problems with applied decision-making contexts. Builds on simulation work from Y7 pro_03, Y8 pro_04, Y9 pro_04.</t>
         </is>

--- a/lessonmap.xlsx
+++ b/lessonmap.xlsx
@@ -10344,7 +10344,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="M123" s="15" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -10354,12 +10354,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O123" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="P123" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_01_index_laws_product_quotient_power_v2.html</t>
         </is>
@@ -10437,17 +10437,17 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="O124" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="P124" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_02_zero_and_negative_indices_v2.html</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="Q124" s="15" t="inlineStr">
         <is>
           <t>Built 2026-05-31 (remote batch y9-alg-01). Covers planned-01 negative_integer_exponents content.</t>
         </is>
@@ -10510,7 +10510,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M125" s="15" t="inlineStr">
         <is>
           <t>y9_alg_02</t>
         </is>
@@ -10520,12 +10520,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O125" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="P125" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_03_index_laws_with_variables_v2.html</t>
         </is>
@@ -10603,12 +10603,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O126" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P126" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_04_expanding_binomial_products_v2.html</t>
         </is>
@@ -10686,12 +10686,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O127" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="P127" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_05_special_products_v2.html</t>
         </is>
@@ -10759,7 +10759,7 @@
           <t>auto-marked</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="M128" s="15" t="inlineStr">
         <is>
           <t>y9_alg_05</t>
         </is>
@@ -10769,12 +10769,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O128" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P128" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-9/algebra/y9_alg_06_factorising_monic_quadratics_v2.html</t>
         </is>
@@ -13820,7 +13820,17 @@
       </c>
       <c r="N171" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_01_expanding_special_products_and_non_monic_v2.html</t>
         </is>
       </c>
       <c r="Q171" s="15" t="inlineStr">
@@ -13893,7 +13903,17 @@
       </c>
       <c r="N172" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_02_factorising_quadratics_special_and_non_monic_v2.html</t>
         </is>
       </c>
       <c r="Q172" s="15" t="inlineStr">
@@ -13966,7 +13986,17 @@
       </c>
       <c r="N173" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_03_completing_the_square_v2.html</t>
         </is>
       </c>
       <c r="Q173" s="15" t="inlineStr">
@@ -14039,7 +14069,17 @@
       </c>
       <c r="N174" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_04_solving_quadratics_and_quadratic_formula_v2.html</t>
         </is>
       </c>
       <c r="Q174" s="15" t="inlineStr">
@@ -14107,7 +14147,17 @@
       </c>
       <c r="N175" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_05_simplifying_with_negative_exponents_and_variables_v2.html</t>
         </is>
       </c>
       <c r="Q175" s="15" t="inlineStr">
@@ -14175,7 +14225,17 @@
       </c>
       <c r="N176" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_06_solving_simultaneous_equations_graphically_v2.html</t>
         </is>
       </c>
       <c r="Q176" s="15" t="inlineStr">
@@ -14248,7 +14308,17 @@
       </c>
       <c r="N177" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_07_solving_simultaneous_equations_algebraically_v2.html</t>
         </is>
       </c>
       <c r="Q177" s="15" t="inlineStr">
@@ -14321,7 +14391,17 @@
       </c>
       <c r="N178" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_08_modelling_with_simultaneous_equations_v2.html</t>
         </is>
       </c>
       <c r="Q178" s="15" t="inlineStr">
@@ -14394,7 +14474,17 @@
       </c>
       <c r="N179" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_09_graphing_linear_inequalities_in_two_variables_v2.html</t>
         </is>
       </c>
       <c r="Q179" s="15" t="inlineStr">
@@ -14467,7 +14557,17 @@
       </c>
       <c r="N180" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_10_systems_of_inequalities_and_feasible_regions_v2.html</t>
         </is>
       </c>
       <c r="Q180" s="15" t="inlineStr">

--- a/lessonmap.xlsx
+++ b/lessonmap.xlsx
@@ -13823,12 +13823,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
+      <c r="O171" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
+      <c r="P171" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_01_expanding_special_products_and_non_monic_v2.html</t>
         </is>
@@ -13906,12 +13906,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
+      <c r="O172" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr">
+      <c r="P172" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_02_factorising_quadratics_special_and_non_monic_v2.html</t>
         </is>
@@ -13989,12 +13989,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
+      <c r="O173" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr">
+      <c r="P173" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_03_completing_the_square_v2.html</t>
         </is>
@@ -14072,12 +14072,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
+      <c r="O174" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr">
+      <c r="P174" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_04_solving_quadratics_and_quadratic_formula_v2.html</t>
         </is>
@@ -14150,12 +14150,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr">
+      <c r="O175" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr">
+      <c r="P175" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_05_simplifying_with_negative_exponents_and_variables_v2.html</t>
         </is>
@@ -14228,12 +14228,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
+      <c r="O176" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr">
+      <c r="P176" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_06_solving_simultaneous_equations_graphically_v2.html</t>
         </is>
@@ -14311,12 +14311,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr">
+      <c r="O177" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr">
+      <c r="P177" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_07_solving_simultaneous_equations_algebraically_v2.html</t>
         </is>
@@ -14394,12 +14394,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr">
+      <c r="O178" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr">
+      <c r="P178" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_08_modelling_with_simultaneous_equations_v2.html</t>
         </is>
@@ -14477,12 +14477,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr">
+      <c r="O179" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr">
+      <c r="P179" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_09_graphing_linear_inequalities_in_two_variables_v2.html</t>
         </is>
@@ -14560,12 +14560,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
+      <c r="O180" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr">
+      <c r="P180" s="15" t="inlineStr">
         <is>
           <t>https://seager94.github.io/year-10/algebra/y10_alg_10_systems_of_inequalities_and_feasible_regions_v2.html</t>
         </is>
@@ -14640,7 +14640,17 @@
       </c>
       <c r="N181" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_11_introducing_exponential_functions_v2.html</t>
         </is>
       </c>
       <c r="Q181" s="15" t="inlineStr">
@@ -14713,7 +14723,17 @@
       </c>
       <c r="N182" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_12_features_of_exponential_graphs_v2.html</t>
         </is>
       </c>
       <c r="Q182" s="15" t="inlineStr">
@@ -14786,7 +14806,17 @@
       </c>
       <c r="N183" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_13_solving_exponential_equations_v2.html</t>
         </is>
       </c>
       <c r="Q183" s="15" t="inlineStr">
@@ -14859,7 +14889,17 @@
       </c>
       <c r="N184" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_14_choosing_linear_quadratic_or_exponential_models_v2.html</t>
         </is>
       </c>
       <c r="Q184" s="15" t="inlineStr">
@@ -14932,7 +14972,17 @@
       </c>
       <c r="N185" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_15_exponential_growth_and_decay_v2.html</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15050,17 @@
       </c>
       <c r="N186" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_16_compound_interest_modelling_v2.html</t>
         </is>
       </c>
       <c r="Q186" s="15" t="inlineStr">
@@ -15073,7 +15133,17 @@
       </c>
       <c r="N187" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_17_carbon_dating_and_applied_decay_modelling_v2.html</t>
         </is>
       </c>
       <c r="Q187" s="15" t="inlineStr">
@@ -15146,7 +15216,17 @@
       </c>
       <c r="N188" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_18_intersections_of_functions_with_digital_tools_v2.html</t>
         </is>
       </c>
       <c r="Q188" s="15" t="inlineStr">
@@ -15219,7 +15299,17 @@
       </c>
       <c r="N189" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_19_circle_equations_and_transformations_v2.html</t>
         </is>
       </c>
       <c r="Q189" s="15" t="inlineStr">
@@ -15292,7 +15382,17 @@
       </c>
       <c r="N190" s="15" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>https://seager94.github.io/year-10/algebra/y10_alg_20_intervals_and_iterative_methods_v2.html</t>
         </is>
       </c>
       <c r="Q190" s="15" t="inlineStr">

--- a/lessonmap.xlsx
+++ b/lessonmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdavi\projects\seager94.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB84C048-9052-4CA4-9E74-A90C999118E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4CA65C-DFA6-430A-9882-24FFD80CA077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4734" uniqueCount="1984">
   <si>
     <t>Lesson Map — AC9 Mathematics 7-10</t>
   </si>
@@ -5987,6 +5987,12 @@
   </si>
   <si>
     <t>y10_spa_02,y8_space_03</t>
+  </si>
+  <si>
+    <t>https://seager94.github.io/year-8/statistics/y8_sta_01_census_vs_sample_v2.html</t>
+  </si>
+  <si>
+    <t>https://seager94.github.io/year-8/statistics/y8_sta_02_identifying_and_avoiding_bias_v2.html</t>
   </si>
 </sst>
 </file>
@@ -6095,7 +6101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6119,6 +6125,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12132,7 +12139,13 @@
         <v>403</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>411</v>
+        <v>66</v>
+      </c>
+      <c r="O111" s="13">
+        <v>46213</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1982</v>
       </c>
       <c r="Q111" s="1" t="s">
         <v>767</v>
@@ -12179,7 +12192,13 @@
         <v>761</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>411</v>
+        <v>66</v>
+      </c>
+      <c r="O112" s="13">
+        <v>46213</v>
+      </c>
+      <c r="P112" t="s">
+        <v>1983</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26410,7 +26429,7 @@
       </c>
       <c r="B5" s="1">
         <f>COUNTIF(Lessons!N2:N1000,"Planned")</f>
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26446,7 +26465,7 @@
       </c>
       <c r="B9" s="1">
         <f>COUNTIF(Lessons!N2:N1000,"Published")</f>
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
